--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -23,7 +23,7 @@
     <sheet name="Magazzino_Cassa" sheetId="8" r:id="rId8"/>
     <sheet name="Liste" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B15" s="4">
         <f>Magazzino_Cassa!B6</f>
-        <v>520</v>
+        <v>275</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -2943,7 +2943,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" style="1" customWidth="1"/>
@@ -2996,6 +2996,11 @@
       <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Anticipo da rimborsare</t>
+        </is>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3">
@@ -3009,14 +3014,14 @@
         <v>25</v>
       </c>
       <c r="D4" s="4">
-        <v>270</v>
+        <v>25</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" ref="E4:E18" si="0">D4-C4</f>
-        <v>245</v>
+        <f>D4-C4</f>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="str">
-        <f t="shared" ref="F4:F18" si="1">IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</f>
+        <f>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</f>
         <v>Pagata</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -3025,7 +3030,14 @@
       <c r="H4" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Quota effettiva 25 euro; extra 245 euro registrato come anticipo da rimborsare.</t>
+        </is>
+      </c>
+      <c r="J4" s="4">
+        <v>245</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="3">
@@ -17957,7 +17969,7 @@
       </c>
       <c r="B6" s="4">
         <f>SUM(Persone_Quote!D4:D18)</f>
-        <v>520</v>
+        <v>275</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>31</v>
@@ -18175,7 +18187,7 @@
         <v>28</v>
       </c>
       <c r="B16" s="4">
-        <f>B6+B12-B10-B15</f>
+        <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
         <v>-64</v>
       </c>
       <c r="C16" s="3" t="s">

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5695FC6-6A4E-3846-9906-7B4493BBD653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17AF042D-F245-A246-A359-A85622947A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="Magazzino_Cassa" sheetId="8" r:id="rId8"/>
     <sheet name="Liste" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="194">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -614,6 +615,15 @@
   </si>
   <si>
     <t>La Dashboard mostra cassa disponibile, quote incassate, patch in magazzino, ricavi totali e ricavi separati tra esterni/interni.</t>
+  </si>
+  <si>
+    <t>Anticipo da rimborsare</t>
+  </si>
+  <si>
+    <t>Quota effettiva 25 euro; extra 245 euro registrato come anticipo da rimborsare.</t>
+  </si>
+  <si>
+    <t>Pagata</t>
   </si>
 </sst>
 </file>
@@ -783,32 +793,32 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,68 +833,11 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <fill>
@@ -894,6 +847,10 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFEE2E2"/>
@@ -1188,6 +1145,59 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1622,7 +1632,7 @@
                 <c:formatCode>\€\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>520</c:v>
+                  <c:v>275</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>36</c:v>
@@ -1968,35 +1978,35 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="39"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="38"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="35">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="34">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="33">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="SpeseCategoriaTable" displayName="SpeseCategoriaTable" ref="A3:H203" headerRowDxfId="33" dataDxfId="32" totalsRowDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="SpeseCategoriaTable" displayName="SpeseCategoriaTable" ref="A3:H203" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Data" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Categoria" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Descrizione" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Importo" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Pagato da" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Metodo" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Approvata?" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Note" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Data" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Categoria" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Descrizione" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Importo" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Pagato da" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Metodo" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Approvata?" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Note" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2188,179 +2198,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
     </row>
     <row r="3" spans="1:12" ht="32" customHeight="1"/>
     <row r="4" spans="1:12" ht="20" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13" t="s">
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A5" s="14">
+      <c r="A5" s="18">
         <f>Magazzino_Cassa!B16</f>
-        <v>-64</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="14">
+        <v>-100</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="18">
         <f>Magazzino_Cassa!B6</f>
-        <v>520</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="18">
+        <v>275</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="19">
         <f>Magazzino_Cassa!B14</f>
         <v>184</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="14">
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="18">
         <f>Magazzino_Cassa!B12</f>
         <v>36</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13" t="s">
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13" t="s">
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A9" s="14">
+      <c r="A9" s="18">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="14">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="18">
         <f>Magazzino_Cassa!B13</f>
         <v>27.900000000000002</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="15" t="str">
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="21" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>11/15</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="14">
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="18">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="11" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -2506,7 +2516,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>-64</v>
+        <v>-100</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>29</v>
@@ -2585,20 +2595,20 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12" ht="64" customHeight="1">
       <c r="A24" s="6" t="s">
@@ -2626,12 +2636,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2639,12 +2643,18 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>B19&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>B19&gt;=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2665,14 +2675,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -2783,12 +2793,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -2952,23 +2962,24 @@
     <col min="5" max="6" width="14" style="1" customWidth="1"/>
     <col min="7" max="8" width="16" style="1" customWidth="1"/>
     <col min="9" max="9" width="36" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="1"/>
+    <col min="10" max="10" width="10.1640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="37.25" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-    </row>
-    <row r="3" spans="1:9" ht="32" customHeight="1">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+    </row>
+    <row r="3" spans="1:10" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>75</v>
       </c>
@@ -2996,13 +3007,11 @@
       <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Anticipo da rimborsare</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3030,16 +3039,14 @@
       <c r="H4" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Quota effettiva 25 euro; extra 245 euro registrato come anticipo da rimborsare.</t>
-        </is>
+      <c r="I4" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="J4" s="4">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3054,12 +3061,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F5" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>150</v>
@@ -3069,7 +3074,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3084,18 +3089,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="F6" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Da pagare</v>
+      <c r="F6" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3110,12 +3113,10 @@
         <v>25</v>
       </c>
       <c r="E7" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F7" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>150</v>
@@ -3125,7 +3126,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -3140,12 +3141,10 @@
         <v>25</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F8" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>150</v>
@@ -3155,7 +3154,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3170,18 +3169,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="F9" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Da pagare</v>
+      <c r="F9" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -3196,12 +3193,10 @@
         <v>25</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F10" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>150</v>
@@ -3211,7 +3206,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -3226,18 +3221,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="F11" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Da pagare</v>
+      <c r="F11" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -3252,12 +3245,10 @@
         <v>25</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F12" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>150</v>
@@ -3267,7 +3258,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3282,12 +3273,10 @@
         <v>25</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F13" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>150</v>
@@ -3297,7 +3286,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3312,12 +3301,10 @@
         <v>25</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F14" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>150</v>
@@ -3327,7 +3314,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3342,12 +3329,10 @@
         <v>25</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F15" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>150</v>
@@ -3357,7 +3342,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3372,12 +3357,10 @@
         <v>25</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F16" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>156</v>
@@ -3402,12 +3385,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="F17" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Da pagare</v>
+      <c r="F17" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="3"/>
@@ -3428,12 +3409,10 @@
         <v>25</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Pagata</v>
+      <c r="F18" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>156</v>
@@ -3448,13 +3427,13 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:F18">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>F4="Pagata"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>F4="Da pagare"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="3">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>F4="Parziale"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3494,17 +3473,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="3" spans="1:9" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -7352,13 +7331,13 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="H4:H203">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>H4="Pagato"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>H4="Da pagare"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>H4="Parziale"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7401,19 +7380,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -7463,7 +7442,7 @@
       <c r="D4" s="5">
         <v>2</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="13">
         <v>15</v>
       </c>
       <c r="F4" s="4">
@@ -7473,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f>IF(F4="","",F4-G4)</f>
+        <f t="shared" ref="H4:H67" si="0">IF(F4="","",F4-G4)</f>
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -7495,7 +7474,7 @@
       <c r="D5" s="5">
         <v>2</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="13">
         <v>15</v>
       </c>
       <c r="F5" s="4">
@@ -7505,7 +7484,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f>IF(F5="","",F5-G5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -7527,7 +7506,7 @@
       <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="13">
         <v>15</v>
       </c>
       <c r="F6" s="4">
@@ -7537,7 +7516,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f>IF(F6="","",F6-G6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -7559,7 +7538,7 @@
       <c r="D7" s="5">
         <v>2</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="13">
         <v>15</v>
       </c>
       <c r="F7" s="4">
@@ -7569,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f>IF(F7="","",F7-G7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -7591,7 +7570,7 @@
       <c r="D8" s="5">
         <v>2</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="13">
         <v>15</v>
       </c>
       <c r="F8" s="4">
@@ -7601,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f>IF(F8="","",F8-G8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -7623,7 +7602,7 @@
       <c r="D9" s="5">
         <v>2</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="13">
         <v>15</v>
       </c>
       <c r="F9" s="4">
@@ -7633,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f>IF(F9="","",F9-G9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -7655,7 +7634,7 @@
       <c r="D10" s="5">
         <v>1</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="13">
         <v>15</v>
       </c>
       <c r="F10" s="4">
@@ -7665,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f>IF(F10="","",F10-G10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -7687,11 +7666,11 @@
       <c r="D11" s="5">
         <v>2</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="13">
         <v>12</v>
       </c>
       <c r="F11" s="4">
-        <f>IF(OR(D11="",E11=""),"",D11*E11)</f>
+        <f t="shared" ref="F11:F74" si="1">IF(OR(D11="",E11=""),"",D11*E11)</f>
         <v>24</v>
       </c>
       <c r="G11" s="4">
@@ -7699,7 +7678,7 @@
         <v>5.4</v>
       </c>
       <c r="H11" s="4">
-        <f>IF(F11="","",F11-G11)</f>
+        <f t="shared" si="0"/>
         <v>18.600000000000001</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -7723,11 +7702,11 @@
       <c r="D12" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="13">
         <v>12</v>
       </c>
       <c r="F12" s="4">
-        <f>IF(OR(D12="",E12=""),"",D12*E12)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="G12" s="4">
@@ -7735,7 +7714,7 @@
         <v>2.7</v>
       </c>
       <c r="H12" s="4">
-        <f>IF(F12="","",F12-G12)</f>
+        <f t="shared" si="0"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -7755,9 +7734,9 @@
         <v>100</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="21"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="4" t="str">
-        <f>IF(OR(D13="",E13=""),"",D13*E13)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G13" s="4" t="str">
@@ -7765,7 +7744,7 @@
         <v/>
       </c>
       <c r="H13" s="4" t="str">
-        <f>IF(F13="","",F13-G13)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I13" s="3" t="s">
@@ -7781,9 +7760,9 @@
         <v>100</v>
       </c>
       <c r="D14" s="5"/>
-      <c r="E14" s="21"/>
+      <c r="E14" s="13"/>
       <c r="F14" s="4" t="str">
-        <f>IF(OR(D14="",E14=""),"",D14*E14)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G14" s="4" t="str">
@@ -7791,7 +7770,7 @@
         <v/>
       </c>
       <c r="H14" s="4" t="str">
-        <f>IF(F14="","",F14-G14)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I14" s="3" t="s">
@@ -7807,9 +7786,9 @@
         <v>100</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="21"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="4" t="str">
-        <f>IF(OR(D15="",E15=""),"",D15*E15)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G15" s="4" t="str">
@@ -7817,7 +7796,7 @@
         <v/>
       </c>
       <c r="H15" s="4" t="str">
-        <f>IF(F15="","",F15-G15)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I15" s="3" t="s">
@@ -7833,9 +7812,9 @@
         <v>100</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="21"/>
+      <c r="E16" s="13"/>
       <c r="F16" s="4" t="str">
-        <f>IF(OR(D16="",E16=""),"",D16*E16)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G16" s="4" t="str">
@@ -7843,7 +7822,7 @@
         <v/>
       </c>
       <c r="H16" s="4" t="str">
-        <f>IF(F16="","",F16-G16)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I16" s="3" t="s">
@@ -7859,9 +7838,9 @@
         <v>100</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="21"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="4" t="str">
-        <f>IF(OR(D17="",E17=""),"",D17*E17)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G17" s="4" t="str">
@@ -7869,7 +7848,7 @@
         <v/>
       </c>
       <c r="H17" s="4" t="str">
-        <f>IF(F17="","",F17-G17)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I17" s="3" t="s">
@@ -7885,9 +7864,9 @@
         <v>100</v>
       </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="21"/>
+      <c r="E18" s="13"/>
       <c r="F18" s="4" t="str">
-        <f>IF(OR(D18="",E18=""),"",D18*E18)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G18" s="4" t="str">
@@ -7895,7 +7874,7 @@
         <v/>
       </c>
       <c r="H18" s="4" t="str">
-        <f>IF(F18="","",F18-G18)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I18" s="3" t="s">
@@ -7911,9 +7890,9 @@
         <v>100</v>
       </c>
       <c r="D19" s="5"/>
-      <c r="E19" s="21"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="4" t="str">
-        <f>IF(OR(D19="",E19=""),"",D19*E19)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G19" s="4" t="str">
@@ -7921,7 +7900,7 @@
         <v/>
       </c>
       <c r="H19" s="4" t="str">
-        <f>IF(F19="","",F19-G19)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I19" s="3" t="s">
@@ -7937,9 +7916,9 @@
         <v>100</v>
       </c>
       <c r="D20" s="5"/>
-      <c r="E20" s="21"/>
+      <c r="E20" s="13"/>
       <c r="F20" s="4" t="str">
-        <f>IF(OR(D20="",E20=""),"",D20*E20)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G20" s="4" t="str">
@@ -7947,7 +7926,7 @@
         <v/>
       </c>
       <c r="H20" s="4" t="str">
-        <f>IF(F20="","",F20-G20)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I20" s="3" t="s">
@@ -7963,9 +7942,9 @@
         <v>100</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="21"/>
+      <c r="E21" s="13"/>
       <c r="F21" s="4" t="str">
-        <f>IF(OR(D21="",E21=""),"",D21*E21)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G21" s="4" t="str">
@@ -7973,7 +7952,7 @@
         <v/>
       </c>
       <c r="H21" s="4" t="str">
-        <f>IF(F21="","",F21-G21)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I21" s="3" t="s">
@@ -7989,9 +7968,9 @@
         <v>100</v>
       </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="21"/>
+      <c r="E22" s="13"/>
       <c r="F22" s="4" t="str">
-        <f>IF(OR(D22="",E22=""),"",D22*E22)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G22" s="4" t="str">
@@ -7999,7 +7978,7 @@
         <v/>
       </c>
       <c r="H22" s="4" t="str">
-        <f>IF(F22="","",F22-G22)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I22" s="3" t="s">
@@ -8015,9 +7994,9 @@
         <v>100</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="21"/>
+      <c r="E23" s="13"/>
       <c r="F23" s="4" t="str">
-        <f>IF(OR(D23="",E23=""),"",D23*E23)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G23" s="4" t="str">
@@ -8025,7 +8004,7 @@
         <v/>
       </c>
       <c r="H23" s="4" t="str">
-        <f>IF(F23="","",F23-G23)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I23" s="3" t="s">
@@ -8041,9 +8020,9 @@
         <v>100</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="21"/>
+      <c r="E24" s="13"/>
       <c r="F24" s="4" t="str">
-        <f>IF(OR(D24="",E24=""),"",D24*E24)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G24" s="4" t="str">
@@ -8051,7 +8030,7 @@
         <v/>
       </c>
       <c r="H24" s="4" t="str">
-        <f>IF(F24="","",F24-G24)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I24" s="3" t="s">
@@ -8067,9 +8046,9 @@
         <v>100</v>
       </c>
       <c r="D25" s="5"/>
-      <c r="E25" s="21"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="4" t="str">
-        <f>IF(OR(D25="",E25=""),"",D25*E25)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G25" s="4" t="str">
@@ -8077,7 +8056,7 @@
         <v/>
       </c>
       <c r="H25" s="4" t="str">
-        <f>IF(F25="","",F25-G25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I25" s="3" t="s">
@@ -8093,9 +8072,9 @@
         <v>100</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="21"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="4" t="str">
-        <f>IF(OR(D26="",E26=""),"",D26*E26)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G26" s="4" t="str">
@@ -8103,7 +8082,7 @@
         <v/>
       </c>
       <c r="H26" s="4" t="str">
-        <f>IF(F26="","",F26-G26)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I26" s="3" t="s">
@@ -8119,9 +8098,9 @@
         <v>100</v>
       </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="21"/>
+      <c r="E27" s="13"/>
       <c r="F27" s="4" t="str">
-        <f>IF(OR(D27="",E27=""),"",D27*E27)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G27" s="4" t="str">
@@ -8129,7 +8108,7 @@
         <v/>
       </c>
       <c r="H27" s="4" t="str">
-        <f>IF(F27="","",F27-G27)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I27" s="3" t="s">
@@ -8145,9 +8124,9 @@
         <v>100</v>
       </c>
       <c r="D28" s="5"/>
-      <c r="E28" s="21"/>
+      <c r="E28" s="13"/>
       <c r="F28" s="4" t="str">
-        <f>IF(OR(D28="",E28=""),"",D28*E28)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G28" s="4" t="str">
@@ -8155,7 +8134,7 @@
         <v/>
       </c>
       <c r="H28" s="4" t="str">
-        <f>IF(F28="","",F28-G28)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I28" s="3" t="s">
@@ -8171,9 +8150,9 @@
         <v>100</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="21"/>
+      <c r="E29" s="13"/>
       <c r="F29" s="4" t="str">
-        <f>IF(OR(D29="",E29=""),"",D29*E29)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G29" s="4" t="str">
@@ -8181,7 +8160,7 @@
         <v/>
       </c>
       <c r="H29" s="4" t="str">
-        <f>IF(F29="","",F29-G29)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I29" s="3" t="s">
@@ -8197,9 +8176,9 @@
         <v>100</v>
       </c>
       <c r="D30" s="5"/>
-      <c r="E30" s="21"/>
+      <c r="E30" s="13"/>
       <c r="F30" s="4" t="str">
-        <f>IF(OR(D30="",E30=""),"",D30*E30)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G30" s="4" t="str">
@@ -8207,7 +8186,7 @@
         <v/>
       </c>
       <c r="H30" s="4" t="str">
-        <f>IF(F30="","",F30-G30)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I30" s="3" t="s">
@@ -8223,9 +8202,9 @@
         <v>100</v>
       </c>
       <c r="D31" s="5"/>
-      <c r="E31" s="21"/>
+      <c r="E31" s="13"/>
       <c r="F31" s="4" t="str">
-        <f>IF(OR(D31="",E31=""),"",D31*E31)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G31" s="4" t="str">
@@ -8233,7 +8212,7 @@
         <v/>
       </c>
       <c r="H31" s="4" t="str">
-        <f>IF(F31="","",F31-G31)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I31" s="3" t="s">
@@ -8249,9 +8228,9 @@
         <v>100</v>
       </c>
       <c r="D32" s="5"/>
-      <c r="E32" s="21"/>
+      <c r="E32" s="13"/>
       <c r="F32" s="4" t="str">
-        <f>IF(OR(D32="",E32=""),"",D32*E32)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G32" s="4" t="str">
@@ -8259,7 +8238,7 @@
         <v/>
       </c>
       <c r="H32" s="4" t="str">
-        <f>IF(F32="","",F32-G32)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I32" s="3" t="s">
@@ -8275,9 +8254,9 @@
         <v>100</v>
       </c>
       <c r="D33" s="5"/>
-      <c r="E33" s="21"/>
+      <c r="E33" s="13"/>
       <c r="F33" s="4" t="str">
-        <f>IF(OR(D33="",E33=""),"",D33*E33)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G33" s="4" t="str">
@@ -8285,7 +8264,7 @@
         <v/>
       </c>
       <c r="H33" s="4" t="str">
-        <f>IF(F33="","",F33-G33)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I33" s="3" t="s">
@@ -8301,9 +8280,9 @@
         <v>100</v>
       </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="21"/>
+      <c r="E34" s="13"/>
       <c r="F34" s="4" t="str">
-        <f>IF(OR(D34="",E34=""),"",D34*E34)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G34" s="4" t="str">
@@ -8311,7 +8290,7 @@
         <v/>
       </c>
       <c r="H34" s="4" t="str">
-        <f>IF(F34="","",F34-G34)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I34" s="3" t="s">
@@ -8327,9 +8306,9 @@
         <v>100</v>
       </c>
       <c r="D35" s="5"/>
-      <c r="E35" s="21"/>
+      <c r="E35" s="13"/>
       <c r="F35" s="4" t="str">
-        <f>IF(OR(D35="",E35=""),"",D35*E35)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G35" s="4" t="str">
@@ -8337,7 +8316,7 @@
         <v/>
       </c>
       <c r="H35" s="4" t="str">
-        <f>IF(F35="","",F35-G35)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I35" s="3" t="s">
@@ -8353,9 +8332,9 @@
         <v>100</v>
       </c>
       <c r="D36" s="5"/>
-      <c r="E36" s="21"/>
+      <c r="E36" s="13"/>
       <c r="F36" s="4" t="str">
-        <f>IF(OR(D36="",E36=""),"",D36*E36)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G36" s="4" t="str">
@@ -8363,7 +8342,7 @@
         <v/>
       </c>
       <c r="H36" s="4" t="str">
-        <f>IF(F36="","",F36-G36)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I36" s="3" t="s">
@@ -8379,9 +8358,9 @@
         <v>100</v>
       </c>
       <c r="D37" s="5"/>
-      <c r="E37" s="21"/>
+      <c r="E37" s="13"/>
       <c r="F37" s="4" t="str">
-        <f>IF(OR(D37="",E37=""),"",D37*E37)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G37" s="4" t="str">
@@ -8389,7 +8368,7 @@
         <v/>
       </c>
       <c r="H37" s="4" t="str">
-        <f>IF(F37="","",F37-G37)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I37" s="3" t="s">
@@ -8405,9 +8384,9 @@
         <v>100</v>
       </c>
       <c r="D38" s="5"/>
-      <c r="E38" s="21"/>
+      <c r="E38" s="13"/>
       <c r="F38" s="4" t="str">
-        <f>IF(OR(D38="",E38=""),"",D38*E38)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G38" s="4" t="str">
@@ -8415,7 +8394,7 @@
         <v/>
       </c>
       <c r="H38" s="4" t="str">
-        <f>IF(F38="","",F38-G38)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I38" s="3" t="s">
@@ -8431,9 +8410,9 @@
         <v>100</v>
       </c>
       <c r="D39" s="5"/>
-      <c r="E39" s="21"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="4" t="str">
-        <f>IF(OR(D39="",E39=""),"",D39*E39)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G39" s="4" t="str">
@@ -8441,7 +8420,7 @@
         <v/>
       </c>
       <c r="H39" s="4" t="str">
-        <f>IF(F39="","",F39-G39)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I39" s="3" t="s">
@@ -8457,9 +8436,9 @@
         <v>100</v>
       </c>
       <c r="D40" s="5"/>
-      <c r="E40" s="21"/>
+      <c r="E40" s="13"/>
       <c r="F40" s="4" t="str">
-        <f>IF(OR(D40="",E40=""),"",D40*E40)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G40" s="4" t="str">
@@ -8467,7 +8446,7 @@
         <v/>
       </c>
       <c r="H40" s="4" t="str">
-        <f>IF(F40="","",F40-G40)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I40" s="3" t="s">
@@ -8483,9 +8462,9 @@
         <v>100</v>
       </c>
       <c r="D41" s="5"/>
-      <c r="E41" s="21"/>
+      <c r="E41" s="13"/>
       <c r="F41" s="4" t="str">
-        <f>IF(OR(D41="",E41=""),"",D41*E41)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G41" s="4" t="str">
@@ -8493,7 +8472,7 @@
         <v/>
       </c>
       <c r="H41" s="4" t="str">
-        <f>IF(F41="","",F41-G41)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I41" s="3" t="s">
@@ -8509,9 +8488,9 @@
         <v>100</v>
       </c>
       <c r="D42" s="5"/>
-      <c r="E42" s="21"/>
+      <c r="E42" s="13"/>
       <c r="F42" s="4" t="str">
-        <f>IF(OR(D42="",E42=""),"",D42*E42)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G42" s="4" t="str">
@@ -8519,7 +8498,7 @@
         <v/>
       </c>
       <c r="H42" s="4" t="str">
-        <f>IF(F42="","",F42-G42)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I42" s="3" t="s">
@@ -8535,9 +8514,9 @@
         <v>100</v>
       </c>
       <c r="D43" s="5"/>
-      <c r="E43" s="21"/>
+      <c r="E43" s="13"/>
       <c r="F43" s="4" t="str">
-        <f>IF(OR(D43="",E43=""),"",D43*E43)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G43" s="4" t="str">
@@ -8545,7 +8524,7 @@
         <v/>
       </c>
       <c r="H43" s="4" t="str">
-        <f>IF(F43="","",F43-G43)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I43" s="3" t="s">
@@ -8561,9 +8540,9 @@
         <v>100</v>
       </c>
       <c r="D44" s="5"/>
-      <c r="E44" s="21"/>
+      <c r="E44" s="13"/>
       <c r="F44" s="4" t="str">
-        <f>IF(OR(D44="",E44=""),"",D44*E44)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G44" s="4" t="str">
@@ -8571,7 +8550,7 @@
         <v/>
       </c>
       <c r="H44" s="4" t="str">
-        <f>IF(F44="","",F44-G44)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I44" s="3" t="s">
@@ -8587,9 +8566,9 @@
         <v>100</v>
       </c>
       <c r="D45" s="5"/>
-      <c r="E45" s="21"/>
+      <c r="E45" s="13"/>
       <c r="F45" s="4" t="str">
-        <f>IF(OR(D45="",E45=""),"",D45*E45)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G45" s="4" t="str">
@@ -8597,7 +8576,7 @@
         <v/>
       </c>
       <c r="H45" s="4" t="str">
-        <f>IF(F45="","",F45-G45)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I45" s="3" t="s">
@@ -8613,9 +8592,9 @@
         <v>100</v>
       </c>
       <c r="D46" s="5"/>
-      <c r="E46" s="21"/>
+      <c r="E46" s="13"/>
       <c r="F46" s="4" t="str">
-        <f>IF(OR(D46="",E46=""),"",D46*E46)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G46" s="4" t="str">
@@ -8623,7 +8602,7 @@
         <v/>
       </c>
       <c r="H46" s="4" t="str">
-        <f>IF(F46="","",F46-G46)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I46" s="3" t="s">
@@ -8639,9 +8618,9 @@
         <v>100</v>
       </c>
       <c r="D47" s="5"/>
-      <c r="E47" s="21"/>
+      <c r="E47" s="13"/>
       <c r="F47" s="4" t="str">
-        <f>IF(OR(D47="",E47=""),"",D47*E47)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G47" s="4" t="str">
@@ -8649,7 +8628,7 @@
         <v/>
       </c>
       <c r="H47" s="4" t="str">
-        <f>IF(F47="","",F47-G47)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I47" s="3" t="s">
@@ -8665,9 +8644,9 @@
         <v>100</v>
       </c>
       <c r="D48" s="5"/>
-      <c r="E48" s="21"/>
+      <c r="E48" s="13"/>
       <c r="F48" s="4" t="str">
-        <f>IF(OR(D48="",E48=""),"",D48*E48)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G48" s="4" t="str">
@@ -8675,7 +8654,7 @@
         <v/>
       </c>
       <c r="H48" s="4" t="str">
-        <f>IF(F48="","",F48-G48)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I48" s="3" t="s">
@@ -8691,9 +8670,9 @@
         <v>100</v>
       </c>
       <c r="D49" s="5"/>
-      <c r="E49" s="21"/>
+      <c r="E49" s="13"/>
       <c r="F49" s="4" t="str">
-        <f>IF(OR(D49="",E49=""),"",D49*E49)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G49" s="4" t="str">
@@ -8701,7 +8680,7 @@
         <v/>
       </c>
       <c r="H49" s="4" t="str">
-        <f>IF(F49="","",F49-G49)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I49" s="3" t="s">
@@ -8717,9 +8696,9 @@
         <v>100</v>
       </c>
       <c r="D50" s="5"/>
-      <c r="E50" s="21"/>
+      <c r="E50" s="13"/>
       <c r="F50" s="4" t="str">
-        <f>IF(OR(D50="",E50=""),"",D50*E50)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G50" s="4" t="str">
@@ -8727,7 +8706,7 @@
         <v/>
       </c>
       <c r="H50" s="4" t="str">
-        <f>IF(F50="","",F50-G50)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I50" s="3" t="s">
@@ -8743,9 +8722,9 @@
         <v>100</v>
       </c>
       <c r="D51" s="5"/>
-      <c r="E51" s="21"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="4" t="str">
-        <f>IF(OR(D51="",E51=""),"",D51*E51)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G51" s="4" t="str">
@@ -8753,7 +8732,7 @@
         <v/>
       </c>
       <c r="H51" s="4" t="str">
-        <f>IF(F51="","",F51-G51)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I51" s="3" t="s">
@@ -8769,9 +8748,9 @@
         <v>100</v>
       </c>
       <c r="D52" s="5"/>
-      <c r="E52" s="21"/>
+      <c r="E52" s="13"/>
       <c r="F52" s="4" t="str">
-        <f>IF(OR(D52="",E52=""),"",D52*E52)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G52" s="4" t="str">
@@ -8779,7 +8758,7 @@
         <v/>
       </c>
       <c r="H52" s="4" t="str">
-        <f>IF(F52="","",F52-G52)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I52" s="3" t="s">
@@ -8795,9 +8774,9 @@
         <v>100</v>
       </c>
       <c r="D53" s="5"/>
-      <c r="E53" s="21"/>
+      <c r="E53" s="13"/>
       <c r="F53" s="4" t="str">
-        <f>IF(OR(D53="",E53=""),"",D53*E53)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G53" s="4" t="str">
@@ -8805,7 +8784,7 @@
         <v/>
       </c>
       <c r="H53" s="4" t="str">
-        <f>IF(F53="","",F53-G53)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I53" s="3" t="s">
@@ -8821,9 +8800,9 @@
         <v>100</v>
       </c>
       <c r="D54" s="5"/>
-      <c r="E54" s="21"/>
+      <c r="E54" s="13"/>
       <c r="F54" s="4" t="str">
-        <f>IF(OR(D54="",E54=""),"",D54*E54)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G54" s="4" t="str">
@@ -8831,7 +8810,7 @@
         <v/>
       </c>
       <c r="H54" s="4" t="str">
-        <f>IF(F54="","",F54-G54)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I54" s="3" t="s">
@@ -8847,9 +8826,9 @@
         <v>100</v>
       </c>
       <c r="D55" s="5"/>
-      <c r="E55" s="21"/>
+      <c r="E55" s="13"/>
       <c r="F55" s="4" t="str">
-        <f>IF(OR(D55="",E55=""),"",D55*E55)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G55" s="4" t="str">
@@ -8857,7 +8836,7 @@
         <v/>
       </c>
       <c r="H55" s="4" t="str">
-        <f>IF(F55="","",F55-G55)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I55" s="3" t="s">
@@ -8873,9 +8852,9 @@
         <v>100</v>
       </c>
       <c r="D56" s="5"/>
-      <c r="E56" s="21"/>
+      <c r="E56" s="13"/>
       <c r="F56" s="4" t="str">
-        <f>IF(OR(D56="",E56=""),"",D56*E56)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G56" s="4" t="str">
@@ -8883,7 +8862,7 @@
         <v/>
       </c>
       <c r="H56" s="4" t="str">
-        <f>IF(F56="","",F56-G56)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I56" s="3" t="s">
@@ -8899,9 +8878,9 @@
         <v>100</v>
       </c>
       <c r="D57" s="5"/>
-      <c r="E57" s="21"/>
+      <c r="E57" s="13"/>
       <c r="F57" s="4" t="str">
-        <f>IF(OR(D57="",E57=""),"",D57*E57)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G57" s="4" t="str">
@@ -8909,7 +8888,7 @@
         <v/>
       </c>
       <c r="H57" s="4" t="str">
-        <f>IF(F57="","",F57-G57)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I57" s="3" t="s">
@@ -8925,9 +8904,9 @@
         <v>100</v>
       </c>
       <c r="D58" s="5"/>
-      <c r="E58" s="21"/>
+      <c r="E58" s="13"/>
       <c r="F58" s="4" t="str">
-        <f>IF(OR(D58="",E58=""),"",D58*E58)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G58" s="4" t="str">
@@ -8935,7 +8914,7 @@
         <v/>
       </c>
       <c r="H58" s="4" t="str">
-        <f>IF(F58="","",F58-G58)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I58" s="3" t="s">
@@ -8951,9 +8930,9 @@
         <v>100</v>
       </c>
       <c r="D59" s="5"/>
-      <c r="E59" s="21"/>
+      <c r="E59" s="13"/>
       <c r="F59" s="4" t="str">
-        <f>IF(OR(D59="",E59=""),"",D59*E59)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G59" s="4" t="str">
@@ -8961,7 +8940,7 @@
         <v/>
       </c>
       <c r="H59" s="4" t="str">
-        <f>IF(F59="","",F59-G59)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I59" s="3" t="s">
@@ -8977,9 +8956,9 @@
         <v>100</v>
       </c>
       <c r="D60" s="5"/>
-      <c r="E60" s="21"/>
+      <c r="E60" s="13"/>
       <c r="F60" s="4" t="str">
-        <f>IF(OR(D60="",E60=""),"",D60*E60)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G60" s="4" t="str">
@@ -8987,7 +8966,7 @@
         <v/>
       </c>
       <c r="H60" s="4" t="str">
-        <f>IF(F60="","",F60-G60)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I60" s="3" t="s">
@@ -9003,9 +8982,9 @@
         <v>100</v>
       </c>
       <c r="D61" s="5"/>
-      <c r="E61" s="21"/>
+      <c r="E61" s="13"/>
       <c r="F61" s="4" t="str">
-        <f>IF(OR(D61="",E61=""),"",D61*E61)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G61" s="4" t="str">
@@ -9013,7 +8992,7 @@
         <v/>
       </c>
       <c r="H61" s="4" t="str">
-        <f>IF(F61="","",F61-G61)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I61" s="3" t="s">
@@ -9029,9 +9008,9 @@
         <v>100</v>
       </c>
       <c r="D62" s="5"/>
-      <c r="E62" s="21"/>
+      <c r="E62" s="13"/>
       <c r="F62" s="4" t="str">
-        <f>IF(OR(D62="",E62=""),"",D62*E62)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G62" s="4" t="str">
@@ -9039,7 +9018,7 @@
         <v/>
       </c>
       <c r="H62" s="4" t="str">
-        <f>IF(F62="","",F62-G62)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I62" s="3" t="s">
@@ -9055,9 +9034,9 @@
         <v>100</v>
       </c>
       <c r="D63" s="5"/>
-      <c r="E63" s="21"/>
+      <c r="E63" s="13"/>
       <c r="F63" s="4" t="str">
-        <f>IF(OR(D63="",E63=""),"",D63*E63)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G63" s="4" t="str">
@@ -9065,7 +9044,7 @@
         <v/>
       </c>
       <c r="H63" s="4" t="str">
-        <f>IF(F63="","",F63-G63)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I63" s="3" t="s">
@@ -9081,9 +9060,9 @@
         <v>100</v>
       </c>
       <c r="D64" s="5"/>
-      <c r="E64" s="21"/>
+      <c r="E64" s="13"/>
       <c r="F64" s="4" t="str">
-        <f>IF(OR(D64="",E64=""),"",D64*E64)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G64" s="4" t="str">
@@ -9091,7 +9070,7 @@
         <v/>
       </c>
       <c r="H64" s="4" t="str">
-        <f>IF(F64="","",F64-G64)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I64" s="3" t="s">
@@ -9107,9 +9086,9 @@
         <v>100</v>
       </c>
       <c r="D65" s="5"/>
-      <c r="E65" s="21"/>
+      <c r="E65" s="13"/>
       <c r="F65" s="4" t="str">
-        <f>IF(OR(D65="",E65=""),"",D65*E65)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G65" s="4" t="str">
@@ -9117,7 +9096,7 @@
         <v/>
       </c>
       <c r="H65" s="4" t="str">
-        <f>IF(F65="","",F65-G65)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I65" s="3" t="s">
@@ -9133,9 +9112,9 @@
         <v>100</v>
       </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="21"/>
+      <c r="E66" s="13"/>
       <c r="F66" s="4" t="str">
-        <f>IF(OR(D66="",E66=""),"",D66*E66)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G66" s="4" t="str">
@@ -9143,7 +9122,7 @@
         <v/>
       </c>
       <c r="H66" s="4" t="str">
-        <f>IF(F66="","",F66-G66)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I66" s="3" t="s">
@@ -9159,9 +9138,9 @@
         <v>100</v>
       </c>
       <c r="D67" s="5"/>
-      <c r="E67" s="21"/>
+      <c r="E67" s="13"/>
       <c r="F67" s="4" t="str">
-        <f>IF(OR(D67="",E67=""),"",D67*E67)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G67" s="4" t="str">
@@ -9169,7 +9148,7 @@
         <v/>
       </c>
       <c r="H67" s="4" t="str">
-        <f>IF(F67="","",F67-G67)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I67" s="3" t="s">
@@ -9185,9 +9164,9 @@
         <v>100</v>
       </c>
       <c r="D68" s="5"/>
-      <c r="E68" s="21"/>
+      <c r="E68" s="13"/>
       <c r="F68" s="4" t="str">
-        <f>IF(OR(D68="",E68=""),"",D68*E68)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G68" s="4" t="str">
@@ -9195,7 +9174,7 @@
         <v/>
       </c>
       <c r="H68" s="4" t="str">
-        <f>IF(F68="","",F68-G68)</f>
+        <f t="shared" ref="H68:H131" si="2">IF(F68="","",F68-G68)</f>
         <v/>
       </c>
       <c r="I68" s="3" t="s">
@@ -9211,9 +9190,9 @@
         <v>100</v>
       </c>
       <c r="D69" s="5"/>
-      <c r="E69" s="21"/>
+      <c r="E69" s="13"/>
       <c r="F69" s="4" t="str">
-        <f>IF(OR(D69="",E69=""),"",D69*E69)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G69" s="4" t="str">
@@ -9221,7 +9200,7 @@
         <v/>
       </c>
       <c r="H69" s="4" t="str">
-        <f>IF(F69="","",F69-G69)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I69" s="3" t="s">
@@ -9237,9 +9216,9 @@
         <v>100</v>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="21"/>
+      <c r="E70" s="13"/>
       <c r="F70" s="4" t="str">
-        <f>IF(OR(D70="",E70=""),"",D70*E70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G70" s="4" t="str">
@@ -9247,7 +9226,7 @@
         <v/>
       </c>
       <c r="H70" s="4" t="str">
-        <f>IF(F70="","",F70-G70)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I70" s="3" t="s">
@@ -9263,9 +9242,9 @@
         <v>100</v>
       </c>
       <c r="D71" s="5"/>
-      <c r="E71" s="21"/>
+      <c r="E71" s="13"/>
       <c r="F71" s="4" t="str">
-        <f>IF(OR(D71="",E71=""),"",D71*E71)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G71" s="4" t="str">
@@ -9273,7 +9252,7 @@
         <v/>
       </c>
       <c r="H71" s="4" t="str">
-        <f>IF(F71="","",F71-G71)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I71" s="3" t="s">
@@ -9289,9 +9268,9 @@
         <v>100</v>
       </c>
       <c r="D72" s="5"/>
-      <c r="E72" s="21"/>
+      <c r="E72" s="13"/>
       <c r="F72" s="4" t="str">
-        <f>IF(OR(D72="",E72=""),"",D72*E72)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G72" s="4" t="str">
@@ -9299,7 +9278,7 @@
         <v/>
       </c>
       <c r="H72" s="4" t="str">
-        <f>IF(F72="","",F72-G72)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I72" s="3" t="s">
@@ -9315,9 +9294,9 @@
         <v>100</v>
       </c>
       <c r="D73" s="5"/>
-      <c r="E73" s="21"/>
+      <c r="E73" s="13"/>
       <c r="F73" s="4" t="str">
-        <f>IF(OR(D73="",E73=""),"",D73*E73)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G73" s="4" t="str">
@@ -9325,7 +9304,7 @@
         <v/>
       </c>
       <c r="H73" s="4" t="str">
-        <f>IF(F73="","",F73-G73)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I73" s="3" t="s">
@@ -9341,9 +9320,9 @@
         <v>100</v>
       </c>
       <c r="D74" s="5"/>
-      <c r="E74" s="21"/>
+      <c r="E74" s="13"/>
       <c r="F74" s="4" t="str">
-        <f>IF(OR(D74="",E74=""),"",D74*E74)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G74" s="4" t="str">
@@ -9351,7 +9330,7 @@
         <v/>
       </c>
       <c r="H74" s="4" t="str">
-        <f>IF(F74="","",F74-G74)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I74" s="3" t="s">
@@ -9367,9 +9346,9 @@
         <v>100</v>
       </c>
       <c r="D75" s="5"/>
-      <c r="E75" s="21"/>
+      <c r="E75" s="13"/>
       <c r="F75" s="4" t="str">
-        <f>IF(OR(D75="",E75=""),"",D75*E75)</f>
+        <f t="shared" ref="F75:F138" si="3">IF(OR(D75="",E75=""),"",D75*E75)</f>
         <v/>
       </c>
       <c r="G75" s="4" t="str">
@@ -9377,7 +9356,7 @@
         <v/>
       </c>
       <c r="H75" s="4" t="str">
-        <f>IF(F75="","",F75-G75)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I75" s="3" t="s">
@@ -9393,9 +9372,9 @@
         <v>100</v>
       </c>
       <c r="D76" s="5"/>
-      <c r="E76" s="21"/>
+      <c r="E76" s="13"/>
       <c r="F76" s="4" t="str">
-        <f>IF(OR(D76="",E76=""),"",D76*E76)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G76" s="4" t="str">
@@ -9403,7 +9382,7 @@
         <v/>
       </c>
       <c r="H76" s="4" t="str">
-        <f>IF(F76="","",F76-G76)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I76" s="3" t="s">
@@ -9419,9 +9398,9 @@
         <v>100</v>
       </c>
       <c r="D77" s="5"/>
-      <c r="E77" s="21"/>
+      <c r="E77" s="13"/>
       <c r="F77" s="4" t="str">
-        <f>IF(OR(D77="",E77=""),"",D77*E77)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G77" s="4" t="str">
@@ -9429,7 +9408,7 @@
         <v/>
       </c>
       <c r="H77" s="4" t="str">
-        <f>IF(F77="","",F77-G77)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I77" s="3" t="s">
@@ -9445,9 +9424,9 @@
         <v>100</v>
       </c>
       <c r="D78" s="5"/>
-      <c r="E78" s="21"/>
+      <c r="E78" s="13"/>
       <c r="F78" s="4" t="str">
-        <f>IF(OR(D78="",E78=""),"",D78*E78)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G78" s="4" t="str">
@@ -9455,7 +9434,7 @@
         <v/>
       </c>
       <c r="H78" s="4" t="str">
-        <f>IF(F78="","",F78-G78)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I78" s="3" t="s">
@@ -9471,9 +9450,9 @@
         <v>100</v>
       </c>
       <c r="D79" s="5"/>
-      <c r="E79" s="21"/>
+      <c r="E79" s="13"/>
       <c r="F79" s="4" t="str">
-        <f>IF(OR(D79="",E79=""),"",D79*E79)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G79" s="4" t="str">
@@ -9481,7 +9460,7 @@
         <v/>
       </c>
       <c r="H79" s="4" t="str">
-        <f>IF(F79="","",F79-G79)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I79" s="3" t="s">
@@ -9497,9 +9476,9 @@
         <v>100</v>
       </c>
       <c r="D80" s="5"/>
-      <c r="E80" s="21"/>
+      <c r="E80" s="13"/>
       <c r="F80" s="4" t="str">
-        <f>IF(OR(D80="",E80=""),"",D80*E80)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G80" s="4" t="str">
@@ -9507,7 +9486,7 @@
         <v/>
       </c>
       <c r="H80" s="4" t="str">
-        <f>IF(F80="","",F80-G80)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I80" s="3" t="s">
@@ -9523,9 +9502,9 @@
         <v>100</v>
       </c>
       <c r="D81" s="5"/>
-      <c r="E81" s="21"/>
+      <c r="E81" s="13"/>
       <c r="F81" s="4" t="str">
-        <f>IF(OR(D81="",E81=""),"",D81*E81)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G81" s="4" t="str">
@@ -9533,7 +9512,7 @@
         <v/>
       </c>
       <c r="H81" s="4" t="str">
-        <f>IF(F81="","",F81-G81)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I81" s="3" t="s">
@@ -9549,9 +9528,9 @@
         <v>100</v>
       </c>
       <c r="D82" s="5"/>
-      <c r="E82" s="21"/>
+      <c r="E82" s="13"/>
       <c r="F82" s="4" t="str">
-        <f>IF(OR(D82="",E82=""),"",D82*E82)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G82" s="4" t="str">
@@ -9559,7 +9538,7 @@
         <v/>
       </c>
       <c r="H82" s="4" t="str">
-        <f>IF(F82="","",F82-G82)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I82" s="3" t="s">
@@ -9575,9 +9554,9 @@
         <v>100</v>
       </c>
       <c r="D83" s="5"/>
-      <c r="E83" s="21"/>
+      <c r="E83" s="13"/>
       <c r="F83" s="4" t="str">
-        <f>IF(OR(D83="",E83=""),"",D83*E83)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G83" s="4" t="str">
@@ -9585,7 +9564,7 @@
         <v/>
       </c>
       <c r="H83" s="4" t="str">
-        <f>IF(F83="","",F83-G83)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I83" s="3" t="s">
@@ -9601,9 +9580,9 @@
         <v>100</v>
       </c>
       <c r="D84" s="5"/>
-      <c r="E84" s="21"/>
+      <c r="E84" s="13"/>
       <c r="F84" s="4" t="str">
-        <f>IF(OR(D84="",E84=""),"",D84*E84)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G84" s="4" t="str">
@@ -9611,7 +9590,7 @@
         <v/>
       </c>
       <c r="H84" s="4" t="str">
-        <f>IF(F84="","",F84-G84)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I84" s="3" t="s">
@@ -9627,9 +9606,9 @@
         <v>100</v>
       </c>
       <c r="D85" s="5"/>
-      <c r="E85" s="21"/>
+      <c r="E85" s="13"/>
       <c r="F85" s="4" t="str">
-        <f>IF(OR(D85="",E85=""),"",D85*E85)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G85" s="4" t="str">
@@ -9637,7 +9616,7 @@
         <v/>
       </c>
       <c r="H85" s="4" t="str">
-        <f>IF(F85="","",F85-G85)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I85" s="3" t="s">
@@ -9653,9 +9632,9 @@
         <v>100</v>
       </c>
       <c r="D86" s="5"/>
-      <c r="E86" s="21"/>
+      <c r="E86" s="13"/>
       <c r="F86" s="4" t="str">
-        <f>IF(OR(D86="",E86=""),"",D86*E86)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G86" s="4" t="str">
@@ -9663,7 +9642,7 @@
         <v/>
       </c>
       <c r="H86" s="4" t="str">
-        <f>IF(F86="","",F86-G86)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I86" s="3" t="s">
@@ -9679,9 +9658,9 @@
         <v>100</v>
       </c>
       <c r="D87" s="5"/>
-      <c r="E87" s="21"/>
+      <c r="E87" s="13"/>
       <c r="F87" s="4" t="str">
-        <f>IF(OR(D87="",E87=""),"",D87*E87)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G87" s="4" t="str">
@@ -9689,7 +9668,7 @@
         <v/>
       </c>
       <c r="H87" s="4" t="str">
-        <f>IF(F87="","",F87-G87)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I87" s="3" t="s">
@@ -9705,9 +9684,9 @@
         <v>100</v>
       </c>
       <c r="D88" s="5"/>
-      <c r="E88" s="21"/>
+      <c r="E88" s="13"/>
       <c r="F88" s="4" t="str">
-        <f>IF(OR(D88="",E88=""),"",D88*E88)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G88" s="4" t="str">
@@ -9715,7 +9694,7 @@
         <v/>
       </c>
       <c r="H88" s="4" t="str">
-        <f>IF(F88="","",F88-G88)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I88" s="3" t="s">
@@ -9731,9 +9710,9 @@
         <v>100</v>
       </c>
       <c r="D89" s="5"/>
-      <c r="E89" s="21"/>
+      <c r="E89" s="13"/>
       <c r="F89" s="4" t="str">
-        <f>IF(OR(D89="",E89=""),"",D89*E89)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G89" s="4" t="str">
@@ -9741,7 +9720,7 @@
         <v/>
       </c>
       <c r="H89" s="4" t="str">
-        <f>IF(F89="","",F89-G89)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I89" s="3" t="s">
@@ -9757,9 +9736,9 @@
         <v>100</v>
       </c>
       <c r="D90" s="5"/>
-      <c r="E90" s="21"/>
+      <c r="E90" s="13"/>
       <c r="F90" s="4" t="str">
-        <f>IF(OR(D90="",E90=""),"",D90*E90)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G90" s="4" t="str">
@@ -9767,7 +9746,7 @@
         <v/>
       </c>
       <c r="H90" s="4" t="str">
-        <f>IF(F90="","",F90-G90)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I90" s="3" t="s">
@@ -9783,9 +9762,9 @@
         <v>100</v>
       </c>
       <c r="D91" s="5"/>
-      <c r="E91" s="21"/>
+      <c r="E91" s="13"/>
       <c r="F91" s="4" t="str">
-        <f>IF(OR(D91="",E91=""),"",D91*E91)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G91" s="4" t="str">
@@ -9793,7 +9772,7 @@
         <v/>
       </c>
       <c r="H91" s="4" t="str">
-        <f>IF(F91="","",F91-G91)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I91" s="3" t="s">
@@ -9809,9 +9788,9 @@
         <v>100</v>
       </c>
       <c r="D92" s="5"/>
-      <c r="E92" s="21"/>
+      <c r="E92" s="13"/>
       <c r="F92" s="4" t="str">
-        <f>IF(OR(D92="",E92=""),"",D92*E92)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G92" s="4" t="str">
@@ -9819,7 +9798,7 @@
         <v/>
       </c>
       <c r="H92" s="4" t="str">
-        <f>IF(F92="","",F92-G92)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I92" s="3" t="s">
@@ -9835,9 +9814,9 @@
         <v>100</v>
       </c>
       <c r="D93" s="5"/>
-      <c r="E93" s="21"/>
+      <c r="E93" s="13"/>
       <c r="F93" s="4" t="str">
-        <f>IF(OR(D93="",E93=""),"",D93*E93)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G93" s="4" t="str">
@@ -9845,7 +9824,7 @@
         <v/>
       </c>
       <c r="H93" s="4" t="str">
-        <f>IF(F93="","",F93-G93)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I93" s="3" t="s">
@@ -9861,9 +9840,9 @@
         <v>100</v>
       </c>
       <c r="D94" s="5"/>
-      <c r="E94" s="21"/>
+      <c r="E94" s="13"/>
       <c r="F94" s="4" t="str">
-        <f>IF(OR(D94="",E94=""),"",D94*E94)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G94" s="4" t="str">
@@ -9871,7 +9850,7 @@
         <v/>
       </c>
       <c r="H94" s="4" t="str">
-        <f>IF(F94="","",F94-G94)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I94" s="3" t="s">
@@ -9887,9 +9866,9 @@
         <v>100</v>
       </c>
       <c r="D95" s="5"/>
-      <c r="E95" s="21"/>
+      <c r="E95" s="13"/>
       <c r="F95" s="4" t="str">
-        <f>IF(OR(D95="",E95=""),"",D95*E95)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G95" s="4" t="str">
@@ -9897,7 +9876,7 @@
         <v/>
       </c>
       <c r="H95" s="4" t="str">
-        <f>IF(F95="","",F95-G95)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I95" s="3" t="s">
@@ -9913,9 +9892,9 @@
         <v>100</v>
       </c>
       <c r="D96" s="5"/>
-      <c r="E96" s="21"/>
+      <c r="E96" s="13"/>
       <c r="F96" s="4" t="str">
-        <f>IF(OR(D96="",E96=""),"",D96*E96)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G96" s="4" t="str">
@@ -9923,7 +9902,7 @@
         <v/>
       </c>
       <c r="H96" s="4" t="str">
-        <f>IF(F96="","",F96-G96)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I96" s="3" t="s">
@@ -9939,9 +9918,9 @@
         <v>100</v>
       </c>
       <c r="D97" s="5"/>
-      <c r="E97" s="21"/>
+      <c r="E97" s="13"/>
       <c r="F97" s="4" t="str">
-        <f>IF(OR(D97="",E97=""),"",D97*E97)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G97" s="4" t="str">
@@ -9949,7 +9928,7 @@
         <v/>
       </c>
       <c r="H97" s="4" t="str">
-        <f>IF(F97="","",F97-G97)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I97" s="3" t="s">
@@ -9965,9 +9944,9 @@
         <v>100</v>
       </c>
       <c r="D98" s="5"/>
-      <c r="E98" s="21"/>
+      <c r="E98" s="13"/>
       <c r="F98" s="4" t="str">
-        <f>IF(OR(D98="",E98=""),"",D98*E98)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G98" s="4" t="str">
@@ -9975,7 +9954,7 @@
         <v/>
       </c>
       <c r="H98" s="4" t="str">
-        <f>IF(F98="","",F98-G98)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I98" s="3" t="s">
@@ -9991,9 +9970,9 @@
         <v>100</v>
       </c>
       <c r="D99" s="5"/>
-      <c r="E99" s="21"/>
+      <c r="E99" s="13"/>
       <c r="F99" s="4" t="str">
-        <f>IF(OR(D99="",E99=""),"",D99*E99)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G99" s="4" t="str">
@@ -10001,7 +9980,7 @@
         <v/>
       </c>
       <c r="H99" s="4" t="str">
-        <f>IF(F99="","",F99-G99)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I99" s="3" t="s">
@@ -10017,9 +9996,9 @@
         <v>100</v>
       </c>
       <c r="D100" s="5"/>
-      <c r="E100" s="21"/>
+      <c r="E100" s="13"/>
       <c r="F100" s="4" t="str">
-        <f>IF(OR(D100="",E100=""),"",D100*E100)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G100" s="4" t="str">
@@ -10027,7 +10006,7 @@
         <v/>
       </c>
       <c r="H100" s="4" t="str">
-        <f>IF(F100="","",F100-G100)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I100" s="3" t="s">
@@ -10043,9 +10022,9 @@
         <v>100</v>
       </c>
       <c r="D101" s="5"/>
-      <c r="E101" s="21"/>
+      <c r="E101" s="13"/>
       <c r="F101" s="4" t="str">
-        <f>IF(OR(D101="",E101=""),"",D101*E101)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G101" s="4" t="str">
@@ -10053,7 +10032,7 @@
         <v/>
       </c>
       <c r="H101" s="4" t="str">
-        <f>IF(F101="","",F101-G101)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I101" s="3" t="s">
@@ -10069,9 +10048,9 @@
         <v>100</v>
       </c>
       <c r="D102" s="5"/>
-      <c r="E102" s="21"/>
+      <c r="E102" s="13"/>
       <c r="F102" s="4" t="str">
-        <f>IF(OR(D102="",E102=""),"",D102*E102)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G102" s="4" t="str">
@@ -10079,7 +10058,7 @@
         <v/>
       </c>
       <c r="H102" s="4" t="str">
-        <f>IF(F102="","",F102-G102)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I102" s="3" t="s">
@@ -10095,9 +10074,9 @@
         <v>100</v>
       </c>
       <c r="D103" s="5"/>
-      <c r="E103" s="21"/>
+      <c r="E103" s="13"/>
       <c r="F103" s="4" t="str">
-        <f>IF(OR(D103="",E103=""),"",D103*E103)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G103" s="4" t="str">
@@ -10105,7 +10084,7 @@
         <v/>
       </c>
       <c r="H103" s="4" t="str">
-        <f>IF(F103="","",F103-G103)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I103" s="3" t="s">
@@ -10121,9 +10100,9 @@
         <v>100</v>
       </c>
       <c r="D104" s="5"/>
-      <c r="E104" s="21"/>
+      <c r="E104" s="13"/>
       <c r="F104" s="4" t="str">
-        <f>IF(OR(D104="",E104=""),"",D104*E104)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G104" s="4" t="str">
@@ -10131,7 +10110,7 @@
         <v/>
       </c>
       <c r="H104" s="4" t="str">
-        <f>IF(F104="","",F104-G104)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I104" s="3" t="s">
@@ -10147,9 +10126,9 @@
         <v>100</v>
       </c>
       <c r="D105" s="5"/>
-      <c r="E105" s="21"/>
+      <c r="E105" s="13"/>
       <c r="F105" s="4" t="str">
-        <f>IF(OR(D105="",E105=""),"",D105*E105)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G105" s="4" t="str">
@@ -10157,7 +10136,7 @@
         <v/>
       </c>
       <c r="H105" s="4" t="str">
-        <f>IF(F105="","",F105-G105)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I105" s="3" t="s">
@@ -10173,9 +10152,9 @@
         <v>100</v>
       </c>
       <c r="D106" s="5"/>
-      <c r="E106" s="21"/>
+      <c r="E106" s="13"/>
       <c r="F106" s="4" t="str">
-        <f>IF(OR(D106="",E106=""),"",D106*E106)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G106" s="4" t="str">
@@ -10183,7 +10162,7 @@
         <v/>
       </c>
       <c r="H106" s="4" t="str">
-        <f>IF(F106="","",F106-G106)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I106" s="3" t="s">
@@ -10199,9 +10178,9 @@
         <v>100</v>
       </c>
       <c r="D107" s="5"/>
-      <c r="E107" s="21"/>
+      <c r="E107" s="13"/>
       <c r="F107" s="4" t="str">
-        <f>IF(OR(D107="",E107=""),"",D107*E107)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G107" s="4" t="str">
@@ -10209,7 +10188,7 @@
         <v/>
       </c>
       <c r="H107" s="4" t="str">
-        <f>IF(F107="","",F107-G107)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I107" s="3" t="s">
@@ -10225,9 +10204,9 @@
         <v>100</v>
       </c>
       <c r="D108" s="5"/>
-      <c r="E108" s="21"/>
+      <c r="E108" s="13"/>
       <c r="F108" s="4" t="str">
-        <f>IF(OR(D108="",E108=""),"",D108*E108)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G108" s="4" t="str">
@@ -10235,7 +10214,7 @@
         <v/>
       </c>
       <c r="H108" s="4" t="str">
-        <f>IF(F108="","",F108-G108)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I108" s="3" t="s">
@@ -10251,9 +10230,9 @@
         <v>100</v>
       </c>
       <c r="D109" s="5"/>
-      <c r="E109" s="21"/>
+      <c r="E109" s="13"/>
       <c r="F109" s="4" t="str">
-        <f>IF(OR(D109="",E109=""),"",D109*E109)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G109" s="4" t="str">
@@ -10261,7 +10240,7 @@
         <v/>
       </c>
       <c r="H109" s="4" t="str">
-        <f>IF(F109="","",F109-G109)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I109" s="3" t="s">
@@ -10277,9 +10256,9 @@
         <v>100</v>
       </c>
       <c r="D110" s="5"/>
-      <c r="E110" s="21"/>
+      <c r="E110" s="13"/>
       <c r="F110" s="4" t="str">
-        <f>IF(OR(D110="",E110=""),"",D110*E110)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G110" s="4" t="str">
@@ -10287,7 +10266,7 @@
         <v/>
       </c>
       <c r="H110" s="4" t="str">
-        <f>IF(F110="","",F110-G110)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I110" s="3" t="s">
@@ -10303,9 +10282,9 @@
         <v>100</v>
       </c>
       <c r="D111" s="5"/>
-      <c r="E111" s="21"/>
+      <c r="E111" s="13"/>
       <c r="F111" s="4" t="str">
-        <f>IF(OR(D111="",E111=""),"",D111*E111)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G111" s="4" t="str">
@@ -10313,7 +10292,7 @@
         <v/>
       </c>
       <c r="H111" s="4" t="str">
-        <f>IF(F111="","",F111-G111)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I111" s="3" t="s">
@@ -10329,9 +10308,9 @@
         <v>100</v>
       </c>
       <c r="D112" s="5"/>
-      <c r="E112" s="21"/>
+      <c r="E112" s="13"/>
       <c r="F112" s="4" t="str">
-        <f>IF(OR(D112="",E112=""),"",D112*E112)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G112" s="4" t="str">
@@ -10339,7 +10318,7 @@
         <v/>
       </c>
       <c r="H112" s="4" t="str">
-        <f>IF(F112="","",F112-G112)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I112" s="3" t="s">
@@ -10355,9 +10334,9 @@
         <v>100</v>
       </c>
       <c r="D113" s="5"/>
-      <c r="E113" s="21"/>
+      <c r="E113" s="13"/>
       <c r="F113" s="4" t="str">
-        <f>IF(OR(D113="",E113=""),"",D113*E113)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G113" s="4" t="str">
@@ -10365,7 +10344,7 @@
         <v/>
       </c>
       <c r="H113" s="4" t="str">
-        <f>IF(F113="","",F113-G113)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I113" s="3" t="s">
@@ -10381,9 +10360,9 @@
         <v>100</v>
       </c>
       <c r="D114" s="5"/>
-      <c r="E114" s="21"/>
+      <c r="E114" s="13"/>
       <c r="F114" s="4" t="str">
-        <f>IF(OR(D114="",E114=""),"",D114*E114)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G114" s="4" t="str">
@@ -10391,7 +10370,7 @@
         <v/>
       </c>
       <c r="H114" s="4" t="str">
-        <f>IF(F114="","",F114-G114)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I114" s="3" t="s">
@@ -10407,9 +10386,9 @@
         <v>100</v>
       </c>
       <c r="D115" s="5"/>
-      <c r="E115" s="21"/>
+      <c r="E115" s="13"/>
       <c r="F115" s="4" t="str">
-        <f>IF(OR(D115="",E115=""),"",D115*E115)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G115" s="4" t="str">
@@ -10417,7 +10396,7 @@
         <v/>
       </c>
       <c r="H115" s="4" t="str">
-        <f>IF(F115="","",F115-G115)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I115" s="3" t="s">
@@ -10433,9 +10412,9 @@
         <v>100</v>
       </c>
       <c r="D116" s="5"/>
-      <c r="E116" s="21"/>
+      <c r="E116" s="13"/>
       <c r="F116" s="4" t="str">
-        <f>IF(OR(D116="",E116=""),"",D116*E116)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G116" s="4" t="str">
@@ -10443,7 +10422,7 @@
         <v/>
       </c>
       <c r="H116" s="4" t="str">
-        <f>IF(F116="","",F116-G116)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I116" s="3" t="s">
@@ -10459,9 +10438,9 @@
         <v>100</v>
       </c>
       <c r="D117" s="5"/>
-      <c r="E117" s="21"/>
+      <c r="E117" s="13"/>
       <c r="F117" s="4" t="str">
-        <f>IF(OR(D117="",E117=""),"",D117*E117)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G117" s="4" t="str">
@@ -10469,7 +10448,7 @@
         <v/>
       </c>
       <c r="H117" s="4" t="str">
-        <f>IF(F117="","",F117-G117)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I117" s="3" t="s">
@@ -10485,9 +10464,9 @@
         <v>100</v>
       </c>
       <c r="D118" s="5"/>
-      <c r="E118" s="21"/>
+      <c r="E118" s="13"/>
       <c r="F118" s="4" t="str">
-        <f>IF(OR(D118="",E118=""),"",D118*E118)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G118" s="4" t="str">
@@ -10495,7 +10474,7 @@
         <v/>
       </c>
       <c r="H118" s="4" t="str">
-        <f>IF(F118="","",F118-G118)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I118" s="3" t="s">
@@ -10511,9 +10490,9 @@
         <v>100</v>
       </c>
       <c r="D119" s="5"/>
-      <c r="E119" s="21"/>
+      <c r="E119" s="13"/>
       <c r="F119" s="4" t="str">
-        <f>IF(OR(D119="",E119=""),"",D119*E119)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G119" s="4" t="str">
@@ -10521,7 +10500,7 @@
         <v/>
       </c>
       <c r="H119" s="4" t="str">
-        <f>IF(F119="","",F119-G119)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I119" s="3" t="s">
@@ -10537,9 +10516,9 @@
         <v>100</v>
       </c>
       <c r="D120" s="5"/>
-      <c r="E120" s="21"/>
+      <c r="E120" s="13"/>
       <c r="F120" s="4" t="str">
-        <f>IF(OR(D120="",E120=""),"",D120*E120)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G120" s="4" t="str">
@@ -10547,7 +10526,7 @@
         <v/>
       </c>
       <c r="H120" s="4" t="str">
-        <f>IF(F120="","",F120-G120)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I120" s="3" t="s">
@@ -10563,9 +10542,9 @@
         <v>100</v>
       </c>
       <c r="D121" s="5"/>
-      <c r="E121" s="21"/>
+      <c r="E121" s="13"/>
       <c r="F121" s="4" t="str">
-        <f>IF(OR(D121="",E121=""),"",D121*E121)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G121" s="4" t="str">
@@ -10573,7 +10552,7 @@
         <v/>
       </c>
       <c r="H121" s="4" t="str">
-        <f>IF(F121="","",F121-G121)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I121" s="3" t="s">
@@ -10589,9 +10568,9 @@
         <v>100</v>
       </c>
       <c r="D122" s="5"/>
-      <c r="E122" s="21"/>
+      <c r="E122" s="13"/>
       <c r="F122" s="4" t="str">
-        <f>IF(OR(D122="",E122=""),"",D122*E122)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G122" s="4" t="str">
@@ -10599,7 +10578,7 @@
         <v/>
       </c>
       <c r="H122" s="4" t="str">
-        <f>IF(F122="","",F122-G122)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I122" s="3" t="s">
@@ -10615,9 +10594,9 @@
         <v>100</v>
       </c>
       <c r="D123" s="5"/>
-      <c r="E123" s="21"/>
+      <c r="E123" s="13"/>
       <c r="F123" s="4" t="str">
-        <f>IF(OR(D123="",E123=""),"",D123*E123)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G123" s="4" t="str">
@@ -10625,7 +10604,7 @@
         <v/>
       </c>
       <c r="H123" s="4" t="str">
-        <f>IF(F123="","",F123-G123)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I123" s="3" t="s">
@@ -10641,9 +10620,9 @@
         <v>100</v>
       </c>
       <c r="D124" s="5"/>
-      <c r="E124" s="21"/>
+      <c r="E124" s="13"/>
       <c r="F124" s="4" t="str">
-        <f>IF(OR(D124="",E124=""),"",D124*E124)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G124" s="4" t="str">
@@ -10651,7 +10630,7 @@
         <v/>
       </c>
       <c r="H124" s="4" t="str">
-        <f>IF(F124="","",F124-G124)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I124" s="3" t="s">
@@ -10667,9 +10646,9 @@
         <v>100</v>
       </c>
       <c r="D125" s="5"/>
-      <c r="E125" s="21"/>
+      <c r="E125" s="13"/>
       <c r="F125" s="4" t="str">
-        <f>IF(OR(D125="",E125=""),"",D125*E125)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G125" s="4" t="str">
@@ -10677,7 +10656,7 @@
         <v/>
       </c>
       <c r="H125" s="4" t="str">
-        <f>IF(F125="","",F125-G125)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I125" s="3" t="s">
@@ -10693,9 +10672,9 @@
         <v>100</v>
       </c>
       <c r="D126" s="5"/>
-      <c r="E126" s="21"/>
+      <c r="E126" s="13"/>
       <c r="F126" s="4" t="str">
-        <f>IF(OR(D126="",E126=""),"",D126*E126)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G126" s="4" t="str">
@@ -10703,7 +10682,7 @@
         <v/>
       </c>
       <c r="H126" s="4" t="str">
-        <f>IF(F126="","",F126-G126)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I126" s="3" t="s">
@@ -10719,9 +10698,9 @@
         <v>100</v>
       </c>
       <c r="D127" s="5"/>
-      <c r="E127" s="21"/>
+      <c r="E127" s="13"/>
       <c r="F127" s="4" t="str">
-        <f>IF(OR(D127="",E127=""),"",D127*E127)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G127" s="4" t="str">
@@ -10729,7 +10708,7 @@
         <v/>
       </c>
       <c r="H127" s="4" t="str">
-        <f>IF(F127="","",F127-G127)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I127" s="3" t="s">
@@ -10745,9 +10724,9 @@
         <v>100</v>
       </c>
       <c r="D128" s="5"/>
-      <c r="E128" s="21"/>
+      <c r="E128" s="13"/>
       <c r="F128" s="4" t="str">
-        <f>IF(OR(D128="",E128=""),"",D128*E128)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G128" s="4" t="str">
@@ -10755,7 +10734,7 @@
         <v/>
       </c>
       <c r="H128" s="4" t="str">
-        <f>IF(F128="","",F128-G128)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I128" s="3" t="s">
@@ -10771,9 +10750,9 @@
         <v>100</v>
       </c>
       <c r="D129" s="5"/>
-      <c r="E129" s="21"/>
+      <c r="E129" s="13"/>
       <c r="F129" s="4" t="str">
-        <f>IF(OR(D129="",E129=""),"",D129*E129)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G129" s="4" t="str">
@@ -10781,7 +10760,7 @@
         <v/>
       </c>
       <c r="H129" s="4" t="str">
-        <f>IF(F129="","",F129-G129)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I129" s="3" t="s">
@@ -10797,9 +10776,9 @@
         <v>100</v>
       </c>
       <c r="D130" s="5"/>
-      <c r="E130" s="21"/>
+      <c r="E130" s="13"/>
       <c r="F130" s="4" t="str">
-        <f>IF(OR(D130="",E130=""),"",D130*E130)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G130" s="4" t="str">
@@ -10807,7 +10786,7 @@
         <v/>
       </c>
       <c r="H130" s="4" t="str">
-        <f>IF(F130="","",F130-G130)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I130" s="3" t="s">
@@ -10823,9 +10802,9 @@
         <v>100</v>
       </c>
       <c r="D131" s="5"/>
-      <c r="E131" s="21"/>
+      <c r="E131" s="13"/>
       <c r="F131" s="4" t="str">
-        <f>IF(OR(D131="",E131=""),"",D131*E131)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G131" s="4" t="str">
@@ -10833,7 +10812,7 @@
         <v/>
       </c>
       <c r="H131" s="4" t="str">
-        <f>IF(F131="","",F131-G131)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I131" s="3" t="s">
@@ -10849,9 +10828,9 @@
         <v>100</v>
       </c>
       <c r="D132" s="5"/>
-      <c r="E132" s="21"/>
+      <c r="E132" s="13"/>
       <c r="F132" s="4" t="str">
-        <f>IF(OR(D132="",E132=""),"",D132*E132)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G132" s="4" t="str">
@@ -10859,7 +10838,7 @@
         <v/>
       </c>
       <c r="H132" s="4" t="str">
-        <f>IF(F132="","",F132-G132)</f>
+        <f t="shared" ref="H132:H195" si="4">IF(F132="","",F132-G132)</f>
         <v/>
       </c>
       <c r="I132" s="3" t="s">
@@ -10875,9 +10854,9 @@
         <v>100</v>
       </c>
       <c r="D133" s="5"/>
-      <c r="E133" s="21"/>
+      <c r="E133" s="13"/>
       <c r="F133" s="4" t="str">
-        <f>IF(OR(D133="",E133=""),"",D133*E133)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G133" s="4" t="str">
@@ -10885,7 +10864,7 @@
         <v/>
       </c>
       <c r="H133" s="4" t="str">
-        <f>IF(F133="","",F133-G133)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I133" s="3" t="s">
@@ -10901,9 +10880,9 @@
         <v>100</v>
       </c>
       <c r="D134" s="5"/>
-      <c r="E134" s="21"/>
+      <c r="E134" s="13"/>
       <c r="F134" s="4" t="str">
-        <f>IF(OR(D134="",E134=""),"",D134*E134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G134" s="4" t="str">
@@ -10911,7 +10890,7 @@
         <v/>
       </c>
       <c r="H134" s="4" t="str">
-        <f>IF(F134="","",F134-G134)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I134" s="3" t="s">
@@ -10927,9 +10906,9 @@
         <v>100</v>
       </c>
       <c r="D135" s="5"/>
-      <c r="E135" s="21"/>
+      <c r="E135" s="13"/>
       <c r="F135" s="4" t="str">
-        <f>IF(OR(D135="",E135=""),"",D135*E135)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G135" s="4" t="str">
@@ -10937,7 +10916,7 @@
         <v/>
       </c>
       <c r="H135" s="4" t="str">
-        <f>IF(F135="","",F135-G135)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I135" s="3" t="s">
@@ -10953,9 +10932,9 @@
         <v>100</v>
       </c>
       <c r="D136" s="5"/>
-      <c r="E136" s="21"/>
+      <c r="E136" s="13"/>
       <c r="F136" s="4" t="str">
-        <f>IF(OR(D136="",E136=""),"",D136*E136)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G136" s="4" t="str">
@@ -10963,7 +10942,7 @@
         <v/>
       </c>
       <c r="H136" s="4" t="str">
-        <f>IF(F136="","",F136-G136)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I136" s="3" t="s">
@@ -10979,9 +10958,9 @@
         <v>100</v>
       </c>
       <c r="D137" s="5"/>
-      <c r="E137" s="21"/>
+      <c r="E137" s="13"/>
       <c r="F137" s="4" t="str">
-        <f>IF(OR(D137="",E137=""),"",D137*E137)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G137" s="4" t="str">
@@ -10989,7 +10968,7 @@
         <v/>
       </c>
       <c r="H137" s="4" t="str">
-        <f>IF(F137="","",F137-G137)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I137" s="3" t="s">
@@ -11005,9 +10984,9 @@
         <v>100</v>
       </c>
       <c r="D138" s="5"/>
-      <c r="E138" s="21"/>
+      <c r="E138" s="13"/>
       <c r="F138" s="4" t="str">
-        <f>IF(OR(D138="",E138=""),"",D138*E138)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G138" s="4" t="str">
@@ -11015,7 +10994,7 @@
         <v/>
       </c>
       <c r="H138" s="4" t="str">
-        <f>IF(F138="","",F138-G138)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I138" s="3" t="s">
@@ -11031,9 +11010,9 @@
         <v>100</v>
       </c>
       <c r="D139" s="5"/>
-      <c r="E139" s="21"/>
+      <c r="E139" s="13"/>
       <c r="F139" s="4" t="str">
-        <f>IF(OR(D139="",E139=""),"",D139*E139)</f>
+        <f t="shared" ref="F139:F202" si="5">IF(OR(D139="",E139=""),"",D139*E139)</f>
         <v/>
       </c>
       <c r="G139" s="4" t="str">
@@ -11041,7 +11020,7 @@
         <v/>
       </c>
       <c r="H139" s="4" t="str">
-        <f>IF(F139="","",F139-G139)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I139" s="3" t="s">
@@ -11057,9 +11036,9 @@
         <v>100</v>
       </c>
       <c r="D140" s="5"/>
-      <c r="E140" s="21"/>
+      <c r="E140" s="13"/>
       <c r="F140" s="4" t="str">
-        <f>IF(OR(D140="",E140=""),"",D140*E140)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G140" s="4" t="str">
@@ -11067,7 +11046,7 @@
         <v/>
       </c>
       <c r="H140" s="4" t="str">
-        <f>IF(F140="","",F140-G140)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I140" s="3" t="s">
@@ -11083,9 +11062,9 @@
         <v>100</v>
       </c>
       <c r="D141" s="5"/>
-      <c r="E141" s="21"/>
+      <c r="E141" s="13"/>
       <c r="F141" s="4" t="str">
-        <f>IF(OR(D141="",E141=""),"",D141*E141)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G141" s="4" t="str">
@@ -11093,7 +11072,7 @@
         <v/>
       </c>
       <c r="H141" s="4" t="str">
-        <f>IF(F141="","",F141-G141)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I141" s="3" t="s">
@@ -11109,9 +11088,9 @@
         <v>100</v>
       </c>
       <c r="D142" s="5"/>
-      <c r="E142" s="21"/>
+      <c r="E142" s="13"/>
       <c r="F142" s="4" t="str">
-        <f>IF(OR(D142="",E142=""),"",D142*E142)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G142" s="4" t="str">
@@ -11119,7 +11098,7 @@
         <v/>
       </c>
       <c r="H142" s="4" t="str">
-        <f>IF(F142="","",F142-G142)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I142" s="3" t="s">
@@ -11135,9 +11114,9 @@
         <v>100</v>
       </c>
       <c r="D143" s="5"/>
-      <c r="E143" s="21"/>
+      <c r="E143" s="13"/>
       <c r="F143" s="4" t="str">
-        <f>IF(OR(D143="",E143=""),"",D143*E143)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G143" s="4" t="str">
@@ -11145,7 +11124,7 @@
         <v/>
       </c>
       <c r="H143" s="4" t="str">
-        <f>IF(F143="","",F143-G143)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I143" s="3" t="s">
@@ -11161,9 +11140,9 @@
         <v>100</v>
       </c>
       <c r="D144" s="5"/>
-      <c r="E144" s="21"/>
+      <c r="E144" s="13"/>
       <c r="F144" s="4" t="str">
-        <f>IF(OR(D144="",E144=""),"",D144*E144)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G144" s="4" t="str">
@@ -11171,7 +11150,7 @@
         <v/>
       </c>
       <c r="H144" s="4" t="str">
-        <f>IF(F144="","",F144-G144)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I144" s="3" t="s">
@@ -11187,9 +11166,9 @@
         <v>100</v>
       </c>
       <c r="D145" s="5"/>
-      <c r="E145" s="21"/>
+      <c r="E145" s="13"/>
       <c r="F145" s="4" t="str">
-        <f>IF(OR(D145="",E145=""),"",D145*E145)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G145" s="4" t="str">
@@ -11197,7 +11176,7 @@
         <v/>
       </c>
       <c r="H145" s="4" t="str">
-        <f>IF(F145="","",F145-G145)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I145" s="3" t="s">
@@ -11213,9 +11192,9 @@
         <v>100</v>
       </c>
       <c r="D146" s="5"/>
-      <c r="E146" s="21"/>
+      <c r="E146" s="13"/>
       <c r="F146" s="4" t="str">
-        <f>IF(OR(D146="",E146=""),"",D146*E146)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G146" s="4" t="str">
@@ -11223,7 +11202,7 @@
         <v/>
       </c>
       <c r="H146" s="4" t="str">
-        <f>IF(F146="","",F146-G146)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I146" s="3" t="s">
@@ -11239,9 +11218,9 @@
         <v>100</v>
       </c>
       <c r="D147" s="5"/>
-      <c r="E147" s="21"/>
+      <c r="E147" s="13"/>
       <c r="F147" s="4" t="str">
-        <f>IF(OR(D147="",E147=""),"",D147*E147)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G147" s="4" t="str">
@@ -11249,7 +11228,7 @@
         <v/>
       </c>
       <c r="H147" s="4" t="str">
-        <f>IF(F147="","",F147-G147)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I147" s="3" t="s">
@@ -11265,9 +11244,9 @@
         <v>100</v>
       </c>
       <c r="D148" s="5"/>
-      <c r="E148" s="21"/>
+      <c r="E148" s="13"/>
       <c r="F148" s="4" t="str">
-        <f>IF(OR(D148="",E148=""),"",D148*E148)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G148" s="4" t="str">
@@ -11275,7 +11254,7 @@
         <v/>
       </c>
       <c r="H148" s="4" t="str">
-        <f>IF(F148="","",F148-G148)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I148" s="3" t="s">
@@ -11291,9 +11270,9 @@
         <v>100</v>
       </c>
       <c r="D149" s="5"/>
-      <c r="E149" s="21"/>
+      <c r="E149" s="13"/>
       <c r="F149" s="4" t="str">
-        <f>IF(OR(D149="",E149=""),"",D149*E149)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G149" s="4" t="str">
@@ -11301,7 +11280,7 @@
         <v/>
       </c>
       <c r="H149" s="4" t="str">
-        <f>IF(F149="","",F149-G149)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I149" s="3" t="s">
@@ -11317,9 +11296,9 @@
         <v>100</v>
       </c>
       <c r="D150" s="5"/>
-      <c r="E150" s="21"/>
+      <c r="E150" s="13"/>
       <c r="F150" s="4" t="str">
-        <f>IF(OR(D150="",E150=""),"",D150*E150)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G150" s="4" t="str">
@@ -11327,7 +11306,7 @@
         <v/>
       </c>
       <c r="H150" s="4" t="str">
-        <f>IF(F150="","",F150-G150)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I150" s="3" t="s">
@@ -11343,9 +11322,9 @@
         <v>100</v>
       </c>
       <c r="D151" s="5"/>
-      <c r="E151" s="21"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="4" t="str">
-        <f>IF(OR(D151="",E151=""),"",D151*E151)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G151" s="4" t="str">
@@ -11353,7 +11332,7 @@
         <v/>
       </c>
       <c r="H151" s="4" t="str">
-        <f>IF(F151="","",F151-G151)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I151" s="3" t="s">
@@ -11369,9 +11348,9 @@
         <v>100</v>
       </c>
       <c r="D152" s="5"/>
-      <c r="E152" s="21"/>
+      <c r="E152" s="13"/>
       <c r="F152" s="4" t="str">
-        <f>IF(OR(D152="",E152=""),"",D152*E152)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G152" s="4" t="str">
@@ -11379,7 +11358,7 @@
         <v/>
       </c>
       <c r="H152" s="4" t="str">
-        <f>IF(F152="","",F152-G152)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I152" s="3" t="s">
@@ -11395,9 +11374,9 @@
         <v>100</v>
       </c>
       <c r="D153" s="5"/>
-      <c r="E153" s="21"/>
+      <c r="E153" s="13"/>
       <c r="F153" s="4" t="str">
-        <f>IF(OR(D153="",E153=""),"",D153*E153)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G153" s="4" t="str">
@@ -11405,7 +11384,7 @@
         <v/>
       </c>
       <c r="H153" s="4" t="str">
-        <f>IF(F153="","",F153-G153)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I153" s="3" t="s">
@@ -11421,9 +11400,9 @@
         <v>100</v>
       </c>
       <c r="D154" s="5"/>
-      <c r="E154" s="21"/>
+      <c r="E154" s="13"/>
       <c r="F154" s="4" t="str">
-        <f>IF(OR(D154="",E154=""),"",D154*E154)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G154" s="4" t="str">
@@ -11431,7 +11410,7 @@
         <v/>
       </c>
       <c r="H154" s="4" t="str">
-        <f>IF(F154="","",F154-G154)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I154" s="3" t="s">
@@ -11447,9 +11426,9 @@
         <v>100</v>
       </c>
       <c r="D155" s="5"/>
-      <c r="E155" s="21"/>
+      <c r="E155" s="13"/>
       <c r="F155" s="4" t="str">
-        <f>IF(OR(D155="",E155=""),"",D155*E155)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G155" s="4" t="str">
@@ -11457,7 +11436,7 @@
         <v/>
       </c>
       <c r="H155" s="4" t="str">
-        <f>IF(F155="","",F155-G155)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I155" s="3" t="s">
@@ -11473,9 +11452,9 @@
         <v>100</v>
       </c>
       <c r="D156" s="5"/>
-      <c r="E156" s="21"/>
+      <c r="E156" s="13"/>
       <c r="F156" s="4" t="str">
-        <f>IF(OR(D156="",E156=""),"",D156*E156)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G156" s="4" t="str">
@@ -11483,7 +11462,7 @@
         <v/>
       </c>
       <c r="H156" s="4" t="str">
-        <f>IF(F156="","",F156-G156)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I156" s="3" t="s">
@@ -11499,9 +11478,9 @@
         <v>100</v>
       </c>
       <c r="D157" s="5"/>
-      <c r="E157" s="21"/>
+      <c r="E157" s="13"/>
       <c r="F157" s="4" t="str">
-        <f>IF(OR(D157="",E157=""),"",D157*E157)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G157" s="4" t="str">
@@ -11509,7 +11488,7 @@
         <v/>
       </c>
       <c r="H157" s="4" t="str">
-        <f>IF(F157="","",F157-G157)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I157" s="3" t="s">
@@ -11525,9 +11504,9 @@
         <v>100</v>
       </c>
       <c r="D158" s="5"/>
-      <c r="E158" s="21"/>
+      <c r="E158" s="13"/>
       <c r="F158" s="4" t="str">
-        <f>IF(OR(D158="",E158=""),"",D158*E158)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G158" s="4" t="str">
@@ -11535,7 +11514,7 @@
         <v/>
       </c>
       <c r="H158" s="4" t="str">
-        <f>IF(F158="","",F158-G158)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I158" s="3" t="s">
@@ -11551,9 +11530,9 @@
         <v>100</v>
       </c>
       <c r="D159" s="5"/>
-      <c r="E159" s="21"/>
+      <c r="E159" s="13"/>
       <c r="F159" s="4" t="str">
-        <f>IF(OR(D159="",E159=""),"",D159*E159)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G159" s="4" t="str">
@@ -11561,7 +11540,7 @@
         <v/>
       </c>
       <c r="H159" s="4" t="str">
-        <f>IF(F159="","",F159-G159)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I159" s="3" t="s">
@@ -11577,9 +11556,9 @@
         <v>100</v>
       </c>
       <c r="D160" s="5"/>
-      <c r="E160" s="21"/>
+      <c r="E160" s="13"/>
       <c r="F160" s="4" t="str">
-        <f>IF(OR(D160="",E160=""),"",D160*E160)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G160" s="4" t="str">
@@ -11587,7 +11566,7 @@
         <v/>
       </c>
       <c r="H160" s="4" t="str">
-        <f>IF(F160="","",F160-G160)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I160" s="3" t="s">
@@ -11603,9 +11582,9 @@
         <v>100</v>
       </c>
       <c r="D161" s="5"/>
-      <c r="E161" s="21"/>
+      <c r="E161" s="13"/>
       <c r="F161" s="4" t="str">
-        <f>IF(OR(D161="",E161=""),"",D161*E161)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G161" s="4" t="str">
@@ -11613,7 +11592,7 @@
         <v/>
       </c>
       <c r="H161" s="4" t="str">
-        <f>IF(F161="","",F161-G161)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I161" s="3" t="s">
@@ -11629,9 +11608,9 @@
         <v>100</v>
       </c>
       <c r="D162" s="5"/>
-      <c r="E162" s="21"/>
+      <c r="E162" s="13"/>
       <c r="F162" s="4" t="str">
-        <f>IF(OR(D162="",E162=""),"",D162*E162)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G162" s="4" t="str">
@@ -11639,7 +11618,7 @@
         <v/>
       </c>
       <c r="H162" s="4" t="str">
-        <f>IF(F162="","",F162-G162)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I162" s="3" t="s">
@@ -11655,9 +11634,9 @@
         <v>100</v>
       </c>
       <c r="D163" s="5"/>
-      <c r="E163" s="21"/>
+      <c r="E163" s="13"/>
       <c r="F163" s="4" t="str">
-        <f>IF(OR(D163="",E163=""),"",D163*E163)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G163" s="4" t="str">
@@ -11665,7 +11644,7 @@
         <v/>
       </c>
       <c r="H163" s="4" t="str">
-        <f>IF(F163="","",F163-G163)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I163" s="3" t="s">
@@ -11681,9 +11660,9 @@
         <v>100</v>
       </c>
       <c r="D164" s="5"/>
-      <c r="E164" s="21"/>
+      <c r="E164" s="13"/>
       <c r="F164" s="4" t="str">
-        <f>IF(OR(D164="",E164=""),"",D164*E164)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G164" s="4" t="str">
@@ -11691,7 +11670,7 @@
         <v/>
       </c>
       <c r="H164" s="4" t="str">
-        <f>IF(F164="","",F164-G164)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I164" s="3" t="s">
@@ -11707,9 +11686,9 @@
         <v>100</v>
       </c>
       <c r="D165" s="5"/>
-      <c r="E165" s="21"/>
+      <c r="E165" s="13"/>
       <c r="F165" s="4" t="str">
-        <f>IF(OR(D165="",E165=""),"",D165*E165)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G165" s="4" t="str">
@@ -11717,7 +11696,7 @@
         <v/>
       </c>
       <c r="H165" s="4" t="str">
-        <f>IF(F165="","",F165-G165)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I165" s="3" t="s">
@@ -11733,9 +11712,9 @@
         <v>100</v>
       </c>
       <c r="D166" s="5"/>
-      <c r="E166" s="21"/>
+      <c r="E166" s="13"/>
       <c r="F166" s="4" t="str">
-        <f>IF(OR(D166="",E166=""),"",D166*E166)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G166" s="4" t="str">
@@ -11743,7 +11722,7 @@
         <v/>
       </c>
       <c r="H166" s="4" t="str">
-        <f>IF(F166="","",F166-G166)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I166" s="3" t="s">
@@ -11759,9 +11738,9 @@
         <v>100</v>
       </c>
       <c r="D167" s="5"/>
-      <c r="E167" s="21"/>
+      <c r="E167" s="13"/>
       <c r="F167" s="4" t="str">
-        <f>IF(OR(D167="",E167=""),"",D167*E167)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G167" s="4" t="str">
@@ -11769,7 +11748,7 @@
         <v/>
       </c>
       <c r="H167" s="4" t="str">
-        <f>IF(F167="","",F167-G167)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I167" s="3" t="s">
@@ -11785,9 +11764,9 @@
         <v>100</v>
       </c>
       <c r="D168" s="5"/>
-      <c r="E168" s="21"/>
+      <c r="E168" s="13"/>
       <c r="F168" s="4" t="str">
-        <f>IF(OR(D168="",E168=""),"",D168*E168)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G168" s="4" t="str">
@@ -11795,7 +11774,7 @@
         <v/>
       </c>
       <c r="H168" s="4" t="str">
-        <f>IF(F168="","",F168-G168)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I168" s="3" t="s">
@@ -11811,9 +11790,9 @@
         <v>100</v>
       </c>
       <c r="D169" s="5"/>
-      <c r="E169" s="21"/>
+      <c r="E169" s="13"/>
       <c r="F169" s="4" t="str">
-        <f>IF(OR(D169="",E169=""),"",D169*E169)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G169" s="4" t="str">
@@ -11821,7 +11800,7 @@
         <v/>
       </c>
       <c r="H169" s="4" t="str">
-        <f>IF(F169="","",F169-G169)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I169" s="3" t="s">
@@ -11837,9 +11816,9 @@
         <v>100</v>
       </c>
       <c r="D170" s="5"/>
-      <c r="E170" s="21"/>
+      <c r="E170" s="13"/>
       <c r="F170" s="4" t="str">
-        <f>IF(OR(D170="",E170=""),"",D170*E170)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G170" s="4" t="str">
@@ -11847,7 +11826,7 @@
         <v/>
       </c>
       <c r="H170" s="4" t="str">
-        <f>IF(F170="","",F170-G170)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I170" s="3" t="s">
@@ -11863,9 +11842,9 @@
         <v>100</v>
       </c>
       <c r="D171" s="5"/>
-      <c r="E171" s="21"/>
+      <c r="E171" s="13"/>
       <c r="F171" s="4" t="str">
-        <f>IF(OR(D171="",E171=""),"",D171*E171)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G171" s="4" t="str">
@@ -11873,7 +11852,7 @@
         <v/>
       </c>
       <c r="H171" s="4" t="str">
-        <f>IF(F171="","",F171-G171)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I171" s="3" t="s">
@@ -11889,9 +11868,9 @@
         <v>100</v>
       </c>
       <c r="D172" s="5"/>
-      <c r="E172" s="21"/>
+      <c r="E172" s="13"/>
       <c r="F172" s="4" t="str">
-        <f>IF(OR(D172="",E172=""),"",D172*E172)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G172" s="4" t="str">
@@ -11899,7 +11878,7 @@
         <v/>
       </c>
       <c r="H172" s="4" t="str">
-        <f>IF(F172="","",F172-G172)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I172" s="3" t="s">
@@ -11915,9 +11894,9 @@
         <v>100</v>
       </c>
       <c r="D173" s="5"/>
-      <c r="E173" s="21"/>
+      <c r="E173" s="13"/>
       <c r="F173" s="4" t="str">
-        <f>IF(OR(D173="",E173=""),"",D173*E173)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G173" s="4" t="str">
@@ -11925,7 +11904,7 @@
         <v/>
       </c>
       <c r="H173" s="4" t="str">
-        <f>IF(F173="","",F173-G173)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I173" s="3" t="s">
@@ -11941,9 +11920,9 @@
         <v>100</v>
       </c>
       <c r="D174" s="5"/>
-      <c r="E174" s="21"/>
+      <c r="E174" s="13"/>
       <c r="F174" s="4" t="str">
-        <f>IF(OR(D174="",E174=""),"",D174*E174)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G174" s="4" t="str">
@@ -11951,7 +11930,7 @@
         <v/>
       </c>
       <c r="H174" s="4" t="str">
-        <f>IF(F174="","",F174-G174)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I174" s="3" t="s">
@@ -11967,9 +11946,9 @@
         <v>100</v>
       </c>
       <c r="D175" s="5"/>
-      <c r="E175" s="21"/>
+      <c r="E175" s="13"/>
       <c r="F175" s="4" t="str">
-        <f>IF(OR(D175="",E175=""),"",D175*E175)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G175" s="4" t="str">
@@ -11977,7 +11956,7 @@
         <v/>
       </c>
       <c r="H175" s="4" t="str">
-        <f>IF(F175="","",F175-G175)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I175" s="3" t="s">
@@ -11993,9 +11972,9 @@
         <v>100</v>
       </c>
       <c r="D176" s="5"/>
-      <c r="E176" s="21"/>
+      <c r="E176" s="13"/>
       <c r="F176" s="4" t="str">
-        <f>IF(OR(D176="",E176=""),"",D176*E176)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G176" s="4" t="str">
@@ -12003,7 +11982,7 @@
         <v/>
       </c>
       <c r="H176" s="4" t="str">
-        <f>IF(F176="","",F176-G176)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I176" s="3" t="s">
@@ -12019,9 +11998,9 @@
         <v>100</v>
       </c>
       <c r="D177" s="5"/>
-      <c r="E177" s="21"/>
+      <c r="E177" s="13"/>
       <c r="F177" s="4" t="str">
-        <f>IF(OR(D177="",E177=""),"",D177*E177)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G177" s="4" t="str">
@@ -12029,7 +12008,7 @@
         <v/>
       </c>
       <c r="H177" s="4" t="str">
-        <f>IF(F177="","",F177-G177)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I177" s="3" t="s">
@@ -12045,9 +12024,9 @@
         <v>100</v>
       </c>
       <c r="D178" s="5"/>
-      <c r="E178" s="21"/>
+      <c r="E178" s="13"/>
       <c r="F178" s="4" t="str">
-        <f>IF(OR(D178="",E178=""),"",D178*E178)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G178" s="4" t="str">
@@ -12055,7 +12034,7 @@
         <v/>
       </c>
       <c r="H178" s="4" t="str">
-        <f>IF(F178="","",F178-G178)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I178" s="3" t="s">
@@ -12071,9 +12050,9 @@
         <v>100</v>
       </c>
       <c r="D179" s="5"/>
-      <c r="E179" s="21"/>
+      <c r="E179" s="13"/>
       <c r="F179" s="4" t="str">
-        <f>IF(OR(D179="",E179=""),"",D179*E179)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G179" s="4" t="str">
@@ -12081,7 +12060,7 @@
         <v/>
       </c>
       <c r="H179" s="4" t="str">
-        <f>IF(F179="","",F179-G179)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I179" s="3" t="s">
@@ -12097,9 +12076,9 @@
         <v>100</v>
       </c>
       <c r="D180" s="5"/>
-      <c r="E180" s="21"/>
+      <c r="E180" s="13"/>
       <c r="F180" s="4" t="str">
-        <f>IF(OR(D180="",E180=""),"",D180*E180)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G180" s="4" t="str">
@@ -12107,7 +12086,7 @@
         <v/>
       </c>
       <c r="H180" s="4" t="str">
-        <f>IF(F180="","",F180-G180)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I180" s="3" t="s">
@@ -12123,9 +12102,9 @@
         <v>100</v>
       </c>
       <c r="D181" s="5"/>
-      <c r="E181" s="21"/>
+      <c r="E181" s="13"/>
       <c r="F181" s="4" t="str">
-        <f>IF(OR(D181="",E181=""),"",D181*E181)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G181" s="4" t="str">
@@ -12133,7 +12112,7 @@
         <v/>
       </c>
       <c r="H181" s="4" t="str">
-        <f>IF(F181="","",F181-G181)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I181" s="3" t="s">
@@ -12149,9 +12128,9 @@
         <v>100</v>
       </c>
       <c r="D182" s="5"/>
-      <c r="E182" s="21"/>
+      <c r="E182" s="13"/>
       <c r="F182" s="4" t="str">
-        <f>IF(OR(D182="",E182=""),"",D182*E182)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G182" s="4" t="str">
@@ -12159,7 +12138,7 @@
         <v/>
       </c>
       <c r="H182" s="4" t="str">
-        <f>IF(F182="","",F182-G182)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I182" s="3" t="s">
@@ -12175,9 +12154,9 @@
         <v>100</v>
       </c>
       <c r="D183" s="5"/>
-      <c r="E183" s="21"/>
+      <c r="E183" s="13"/>
       <c r="F183" s="4" t="str">
-        <f>IF(OR(D183="",E183=""),"",D183*E183)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G183" s="4" t="str">
@@ -12185,7 +12164,7 @@
         <v/>
       </c>
       <c r="H183" s="4" t="str">
-        <f>IF(F183="","",F183-G183)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I183" s="3" t="s">
@@ -12201,9 +12180,9 @@
         <v>100</v>
       </c>
       <c r="D184" s="5"/>
-      <c r="E184" s="21"/>
+      <c r="E184" s="13"/>
       <c r="F184" s="4" t="str">
-        <f>IF(OR(D184="",E184=""),"",D184*E184)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G184" s="4" t="str">
@@ -12211,7 +12190,7 @@
         <v/>
       </c>
       <c r="H184" s="4" t="str">
-        <f>IF(F184="","",F184-G184)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I184" s="3" t="s">
@@ -12227,9 +12206,9 @@
         <v>100</v>
       </c>
       <c r="D185" s="5"/>
-      <c r="E185" s="21"/>
+      <c r="E185" s="13"/>
       <c r="F185" s="4" t="str">
-        <f>IF(OR(D185="",E185=""),"",D185*E185)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G185" s="4" t="str">
@@ -12237,7 +12216,7 @@
         <v/>
       </c>
       <c r="H185" s="4" t="str">
-        <f>IF(F185="","",F185-G185)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I185" s="3" t="s">
@@ -12253,9 +12232,9 @@
         <v>100</v>
       </c>
       <c r="D186" s="5"/>
-      <c r="E186" s="21"/>
+      <c r="E186" s="13"/>
       <c r="F186" s="4" t="str">
-        <f>IF(OR(D186="",E186=""),"",D186*E186)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G186" s="4" t="str">
@@ -12263,7 +12242,7 @@
         <v/>
       </c>
       <c r="H186" s="4" t="str">
-        <f>IF(F186="","",F186-G186)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I186" s="3" t="s">
@@ -12279,9 +12258,9 @@
         <v>100</v>
       </c>
       <c r="D187" s="5"/>
-      <c r="E187" s="21"/>
+      <c r="E187" s="13"/>
       <c r="F187" s="4" t="str">
-        <f>IF(OR(D187="",E187=""),"",D187*E187)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G187" s="4" t="str">
@@ -12289,7 +12268,7 @@
         <v/>
       </c>
       <c r="H187" s="4" t="str">
-        <f>IF(F187="","",F187-G187)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I187" s="3" t="s">
@@ -12305,9 +12284,9 @@
         <v>100</v>
       </c>
       <c r="D188" s="5"/>
-      <c r="E188" s="21"/>
+      <c r="E188" s="13"/>
       <c r="F188" s="4" t="str">
-        <f>IF(OR(D188="",E188=""),"",D188*E188)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G188" s="4" t="str">
@@ -12315,7 +12294,7 @@
         <v/>
       </c>
       <c r="H188" s="4" t="str">
-        <f>IF(F188="","",F188-G188)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I188" s="3" t="s">
@@ -12331,9 +12310,9 @@
         <v>100</v>
       </c>
       <c r="D189" s="5"/>
-      <c r="E189" s="21"/>
+      <c r="E189" s="13"/>
       <c r="F189" s="4" t="str">
-        <f>IF(OR(D189="",E189=""),"",D189*E189)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G189" s="4" t="str">
@@ -12341,7 +12320,7 @@
         <v/>
       </c>
       <c r="H189" s="4" t="str">
-        <f>IF(F189="","",F189-G189)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I189" s="3" t="s">
@@ -12357,9 +12336,9 @@
         <v>100</v>
       </c>
       <c r="D190" s="5"/>
-      <c r="E190" s="21"/>
+      <c r="E190" s="13"/>
       <c r="F190" s="4" t="str">
-        <f>IF(OR(D190="",E190=""),"",D190*E190)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G190" s="4" t="str">
@@ -12367,7 +12346,7 @@
         <v/>
       </c>
       <c r="H190" s="4" t="str">
-        <f>IF(F190="","",F190-G190)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I190" s="3" t="s">
@@ -12383,9 +12362,9 @@
         <v>100</v>
       </c>
       <c r="D191" s="5"/>
-      <c r="E191" s="21"/>
+      <c r="E191" s="13"/>
       <c r="F191" s="4" t="str">
-        <f>IF(OR(D191="",E191=""),"",D191*E191)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G191" s="4" t="str">
@@ -12393,7 +12372,7 @@
         <v/>
       </c>
       <c r="H191" s="4" t="str">
-        <f>IF(F191="","",F191-G191)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I191" s="3" t="s">
@@ -12409,9 +12388,9 @@
         <v>100</v>
       </c>
       <c r="D192" s="5"/>
-      <c r="E192" s="21"/>
+      <c r="E192" s="13"/>
       <c r="F192" s="4" t="str">
-        <f>IF(OR(D192="",E192=""),"",D192*E192)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G192" s="4" t="str">
@@ -12419,7 +12398,7 @@
         <v/>
       </c>
       <c r="H192" s="4" t="str">
-        <f>IF(F192="","",F192-G192)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I192" s="3" t="s">
@@ -12435,9 +12414,9 @@
         <v>100</v>
       </c>
       <c r="D193" s="5"/>
-      <c r="E193" s="21"/>
+      <c r="E193" s="13"/>
       <c r="F193" s="4" t="str">
-        <f>IF(OR(D193="",E193=""),"",D193*E193)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G193" s="4" t="str">
@@ -12445,7 +12424,7 @@
         <v/>
       </c>
       <c r="H193" s="4" t="str">
-        <f>IF(F193="","",F193-G193)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I193" s="3" t="s">
@@ -12461,9 +12440,9 @@
         <v>100</v>
       </c>
       <c r="D194" s="5"/>
-      <c r="E194" s="21"/>
+      <c r="E194" s="13"/>
       <c r="F194" s="4" t="str">
-        <f>IF(OR(D194="",E194=""),"",D194*E194)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G194" s="4" t="str">
@@ -12471,7 +12450,7 @@
         <v/>
       </c>
       <c r="H194" s="4" t="str">
-        <f>IF(F194="","",F194-G194)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I194" s="3" t="s">
@@ -12487,9 +12466,9 @@
         <v>100</v>
       </c>
       <c r="D195" s="5"/>
-      <c r="E195" s="21"/>
+      <c r="E195" s="13"/>
       <c r="F195" s="4" t="str">
-        <f>IF(OR(D195="",E195=""),"",D195*E195)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G195" s="4" t="str">
@@ -12497,7 +12476,7 @@
         <v/>
       </c>
       <c r="H195" s="4" t="str">
-        <f>IF(F195="","",F195-G195)</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I195" s="3" t="s">
@@ -12513,9 +12492,9 @@
         <v>100</v>
       </c>
       <c r="D196" s="5"/>
-      <c r="E196" s="21"/>
+      <c r="E196" s="13"/>
       <c r="F196" s="4" t="str">
-        <f>IF(OR(D196="",E196=""),"",D196*E196)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G196" s="4" t="str">
@@ -12523,7 +12502,7 @@
         <v/>
       </c>
       <c r="H196" s="4" t="str">
-        <f>IF(F196="","",F196-G196)</f>
+        <f t="shared" ref="H196:H259" si="6">IF(F196="","",F196-G196)</f>
         <v/>
       </c>
       <c r="I196" s="3" t="s">
@@ -12539,9 +12518,9 @@
         <v>100</v>
       </c>
       <c r="D197" s="5"/>
-      <c r="E197" s="21"/>
+      <c r="E197" s="13"/>
       <c r="F197" s="4" t="str">
-        <f>IF(OR(D197="",E197=""),"",D197*E197)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G197" s="4" t="str">
@@ -12549,7 +12528,7 @@
         <v/>
       </c>
       <c r="H197" s="4" t="str">
-        <f>IF(F197="","",F197-G197)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I197" s="3" t="s">
@@ -12565,9 +12544,9 @@
         <v>100</v>
       </c>
       <c r="D198" s="5"/>
-      <c r="E198" s="21"/>
+      <c r="E198" s="13"/>
       <c r="F198" s="4" t="str">
-        <f>IF(OR(D198="",E198=""),"",D198*E198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G198" s="4" t="str">
@@ -12575,7 +12554,7 @@
         <v/>
       </c>
       <c r="H198" s="4" t="str">
-        <f>IF(F198="","",F198-G198)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I198" s="3" t="s">
@@ -12591,9 +12570,9 @@
         <v>100</v>
       </c>
       <c r="D199" s="5"/>
-      <c r="E199" s="21"/>
+      <c r="E199" s="13"/>
       <c r="F199" s="4" t="str">
-        <f>IF(OR(D199="",E199=""),"",D199*E199)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G199" s="4" t="str">
@@ -12601,7 +12580,7 @@
         <v/>
       </c>
       <c r="H199" s="4" t="str">
-        <f>IF(F199="","",F199-G199)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I199" s="3" t="s">
@@ -12617,9 +12596,9 @@
         <v>100</v>
       </c>
       <c r="D200" s="5"/>
-      <c r="E200" s="21"/>
+      <c r="E200" s="13"/>
       <c r="F200" s="4" t="str">
-        <f>IF(OR(D200="",E200=""),"",D200*E200)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G200" s="4" t="str">
@@ -12627,7 +12606,7 @@
         <v/>
       </c>
       <c r="H200" s="4" t="str">
-        <f>IF(F200="","",F200-G200)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I200" s="3" t="s">
@@ -12643,9 +12622,9 @@
         <v>100</v>
       </c>
       <c r="D201" s="5"/>
-      <c r="E201" s="21"/>
+      <c r="E201" s="13"/>
       <c r="F201" s="4" t="str">
-        <f>IF(OR(D201="",E201=""),"",D201*E201)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G201" s="4" t="str">
@@ -12653,7 +12632,7 @@
         <v/>
       </c>
       <c r="H201" s="4" t="str">
-        <f>IF(F201="","",F201-G201)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I201" s="3" t="s">
@@ -12669,9 +12648,9 @@
         <v>100</v>
       </c>
       <c r="D202" s="5"/>
-      <c r="E202" s="21"/>
+      <c r="E202" s="13"/>
       <c r="F202" s="4" t="str">
-        <f>IF(OR(D202="",E202=""),"",D202*E202)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G202" s="4" t="str">
@@ -12679,7 +12658,7 @@
         <v/>
       </c>
       <c r="H202" s="4" t="str">
-        <f>IF(F202="","",F202-G202)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I202" s="3" t="s">
@@ -12695,9 +12674,9 @@
         <v>100</v>
       </c>
       <c r="D203" s="5"/>
-      <c r="E203" s="21"/>
+      <c r="E203" s="13"/>
       <c r="F203" s="4" t="str">
-        <f>IF(OR(D203="",E203=""),"",D203*E203)</f>
+        <f t="shared" ref="F203:F266" si="7">IF(OR(D203="",E203=""),"",D203*E203)</f>
         <v/>
       </c>
       <c r="G203" s="4" t="str">
@@ -12705,7 +12684,7 @@
         <v/>
       </c>
       <c r="H203" s="4" t="str">
-        <f>IF(F203="","",F203-G203)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I203" s="3" t="s">
@@ -12721,9 +12700,9 @@
         <v>100</v>
       </c>
       <c r="D204" s="5"/>
-      <c r="E204" s="21"/>
+      <c r="E204" s="13"/>
       <c r="F204" s="4" t="str">
-        <f>IF(OR(D204="",E204=""),"",D204*E204)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G204" s="4" t="str">
@@ -12731,7 +12710,7 @@
         <v/>
       </c>
       <c r="H204" s="4" t="str">
-        <f>IF(F204="","",F204-G204)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I204" s="3" t="s">
@@ -12747,9 +12726,9 @@
         <v>100</v>
       </c>
       <c r="D205" s="5"/>
-      <c r="E205" s="21"/>
+      <c r="E205" s="13"/>
       <c r="F205" s="4" t="str">
-        <f>IF(OR(D205="",E205=""),"",D205*E205)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G205" s="4" t="str">
@@ -12757,7 +12736,7 @@
         <v/>
       </c>
       <c r="H205" s="4" t="str">
-        <f>IF(F205="","",F205-G205)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I205" s="3" t="s">
@@ -12773,9 +12752,9 @@
         <v>100</v>
       </c>
       <c r="D206" s="5"/>
-      <c r="E206" s="21"/>
+      <c r="E206" s="13"/>
       <c r="F206" s="4" t="str">
-        <f>IF(OR(D206="",E206=""),"",D206*E206)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G206" s="4" t="str">
@@ -12783,7 +12762,7 @@
         <v/>
       </c>
       <c r="H206" s="4" t="str">
-        <f>IF(F206="","",F206-G206)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I206" s="3" t="s">
@@ -12799,9 +12778,9 @@
         <v>100</v>
       </c>
       <c r="D207" s="5"/>
-      <c r="E207" s="21"/>
+      <c r="E207" s="13"/>
       <c r="F207" s="4" t="str">
-        <f>IF(OR(D207="",E207=""),"",D207*E207)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G207" s="4" t="str">
@@ -12809,7 +12788,7 @@
         <v/>
       </c>
       <c r="H207" s="4" t="str">
-        <f>IF(F207="","",F207-G207)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I207" s="3" t="s">
@@ -12825,9 +12804,9 @@
         <v>100</v>
       </c>
       <c r="D208" s="5"/>
-      <c r="E208" s="21"/>
+      <c r="E208" s="13"/>
       <c r="F208" s="4" t="str">
-        <f>IF(OR(D208="",E208=""),"",D208*E208)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G208" s="4" t="str">
@@ -12835,7 +12814,7 @@
         <v/>
       </c>
       <c r="H208" s="4" t="str">
-        <f>IF(F208="","",F208-G208)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I208" s="3" t="s">
@@ -12851,9 +12830,9 @@
         <v>100</v>
       </c>
       <c r="D209" s="5"/>
-      <c r="E209" s="21"/>
+      <c r="E209" s="13"/>
       <c r="F209" s="4" t="str">
-        <f>IF(OR(D209="",E209=""),"",D209*E209)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G209" s="4" t="str">
@@ -12861,7 +12840,7 @@
         <v/>
       </c>
       <c r="H209" s="4" t="str">
-        <f>IF(F209="","",F209-G209)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I209" s="3" t="s">
@@ -12877,9 +12856,9 @@
         <v>100</v>
       </c>
       <c r="D210" s="5"/>
-      <c r="E210" s="21"/>
+      <c r="E210" s="13"/>
       <c r="F210" s="4" t="str">
-        <f>IF(OR(D210="",E210=""),"",D210*E210)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G210" s="4" t="str">
@@ -12887,7 +12866,7 @@
         <v/>
       </c>
       <c r="H210" s="4" t="str">
-        <f>IF(F210="","",F210-G210)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I210" s="3" t="s">
@@ -12903,9 +12882,9 @@
         <v>100</v>
       </c>
       <c r="D211" s="5"/>
-      <c r="E211" s="21"/>
+      <c r="E211" s="13"/>
       <c r="F211" s="4" t="str">
-        <f>IF(OR(D211="",E211=""),"",D211*E211)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G211" s="4" t="str">
@@ -12913,7 +12892,7 @@
         <v/>
       </c>
       <c r="H211" s="4" t="str">
-        <f>IF(F211="","",F211-G211)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I211" s="3" t="s">
@@ -12929,9 +12908,9 @@
         <v>100</v>
       </c>
       <c r="D212" s="5"/>
-      <c r="E212" s="21"/>
+      <c r="E212" s="13"/>
       <c r="F212" s="4" t="str">
-        <f>IF(OR(D212="",E212=""),"",D212*E212)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G212" s="4" t="str">
@@ -12939,7 +12918,7 @@
         <v/>
       </c>
       <c r="H212" s="4" t="str">
-        <f>IF(F212="","",F212-G212)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I212" s="3" t="s">
@@ -12955,9 +12934,9 @@
         <v>100</v>
       </c>
       <c r="D213" s="5"/>
-      <c r="E213" s="21"/>
+      <c r="E213" s="13"/>
       <c r="F213" s="4" t="str">
-        <f>IF(OR(D213="",E213=""),"",D213*E213)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G213" s="4" t="str">
@@ -12965,7 +12944,7 @@
         <v/>
       </c>
       <c r="H213" s="4" t="str">
-        <f>IF(F213="","",F213-G213)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I213" s="3" t="s">
@@ -12981,9 +12960,9 @@
         <v>100</v>
       </c>
       <c r="D214" s="5"/>
-      <c r="E214" s="21"/>
+      <c r="E214" s="13"/>
       <c r="F214" s="4" t="str">
-        <f>IF(OR(D214="",E214=""),"",D214*E214)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G214" s="4" t="str">
@@ -12991,7 +12970,7 @@
         <v/>
       </c>
       <c r="H214" s="4" t="str">
-        <f>IF(F214="","",F214-G214)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I214" s="3" t="s">
@@ -13007,9 +12986,9 @@
         <v>100</v>
       </c>
       <c r="D215" s="5"/>
-      <c r="E215" s="21"/>
+      <c r="E215" s="13"/>
       <c r="F215" s="4" t="str">
-        <f>IF(OR(D215="",E215=""),"",D215*E215)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G215" s="4" t="str">
@@ -13017,7 +12996,7 @@
         <v/>
       </c>
       <c r="H215" s="4" t="str">
-        <f>IF(F215="","",F215-G215)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I215" s="3" t="s">
@@ -13033,9 +13012,9 @@
         <v>100</v>
       </c>
       <c r="D216" s="5"/>
-      <c r="E216" s="21"/>
+      <c r="E216" s="13"/>
       <c r="F216" s="4" t="str">
-        <f>IF(OR(D216="",E216=""),"",D216*E216)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G216" s="4" t="str">
@@ -13043,7 +13022,7 @@
         <v/>
       </c>
       <c r="H216" s="4" t="str">
-        <f>IF(F216="","",F216-G216)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I216" s="3" t="s">
@@ -13059,9 +13038,9 @@
         <v>100</v>
       </c>
       <c r="D217" s="5"/>
-      <c r="E217" s="21"/>
+      <c r="E217" s="13"/>
       <c r="F217" s="4" t="str">
-        <f>IF(OR(D217="",E217=""),"",D217*E217)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G217" s="4" t="str">
@@ -13069,7 +13048,7 @@
         <v/>
       </c>
       <c r="H217" s="4" t="str">
-        <f>IF(F217="","",F217-G217)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I217" s="3" t="s">
@@ -13085,9 +13064,9 @@
         <v>100</v>
       </c>
       <c r="D218" s="5"/>
-      <c r="E218" s="21"/>
+      <c r="E218" s="13"/>
       <c r="F218" s="4" t="str">
-        <f>IF(OR(D218="",E218=""),"",D218*E218)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G218" s="4" t="str">
@@ -13095,7 +13074,7 @@
         <v/>
       </c>
       <c r="H218" s="4" t="str">
-        <f>IF(F218="","",F218-G218)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I218" s="3" t="s">
@@ -13111,9 +13090,9 @@
         <v>100</v>
       </c>
       <c r="D219" s="5"/>
-      <c r="E219" s="21"/>
+      <c r="E219" s="13"/>
       <c r="F219" s="4" t="str">
-        <f>IF(OR(D219="",E219=""),"",D219*E219)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G219" s="4" t="str">
@@ -13121,7 +13100,7 @@
         <v/>
       </c>
       <c r="H219" s="4" t="str">
-        <f>IF(F219="","",F219-G219)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I219" s="3" t="s">
@@ -13137,9 +13116,9 @@
         <v>100</v>
       </c>
       <c r="D220" s="5"/>
-      <c r="E220" s="21"/>
+      <c r="E220" s="13"/>
       <c r="F220" s="4" t="str">
-        <f>IF(OR(D220="",E220=""),"",D220*E220)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G220" s="4" t="str">
@@ -13147,7 +13126,7 @@
         <v/>
       </c>
       <c r="H220" s="4" t="str">
-        <f>IF(F220="","",F220-G220)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I220" s="3" t="s">
@@ -13163,9 +13142,9 @@
         <v>100</v>
       </c>
       <c r="D221" s="5"/>
-      <c r="E221" s="21"/>
+      <c r="E221" s="13"/>
       <c r="F221" s="4" t="str">
-        <f>IF(OR(D221="",E221=""),"",D221*E221)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G221" s="4" t="str">
@@ -13173,7 +13152,7 @@
         <v/>
       </c>
       <c r="H221" s="4" t="str">
-        <f>IF(F221="","",F221-G221)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I221" s="3" t="s">
@@ -13189,9 +13168,9 @@
         <v>100</v>
       </c>
       <c r="D222" s="5"/>
-      <c r="E222" s="21"/>
+      <c r="E222" s="13"/>
       <c r="F222" s="4" t="str">
-        <f>IF(OR(D222="",E222=""),"",D222*E222)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G222" s="4" t="str">
@@ -13199,7 +13178,7 @@
         <v/>
       </c>
       <c r="H222" s="4" t="str">
-        <f>IF(F222="","",F222-G222)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I222" s="3" t="s">
@@ -13215,9 +13194,9 @@
         <v>100</v>
       </c>
       <c r="D223" s="5"/>
-      <c r="E223" s="21"/>
+      <c r="E223" s="13"/>
       <c r="F223" s="4" t="str">
-        <f>IF(OR(D223="",E223=""),"",D223*E223)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G223" s="4" t="str">
@@ -13225,7 +13204,7 @@
         <v/>
       </c>
       <c r="H223" s="4" t="str">
-        <f>IF(F223="","",F223-G223)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I223" s="3" t="s">
@@ -13241,9 +13220,9 @@
         <v>100</v>
       </c>
       <c r="D224" s="5"/>
-      <c r="E224" s="21"/>
+      <c r="E224" s="13"/>
       <c r="F224" s="4" t="str">
-        <f>IF(OR(D224="",E224=""),"",D224*E224)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G224" s="4" t="str">
@@ -13251,7 +13230,7 @@
         <v/>
       </c>
       <c r="H224" s="4" t="str">
-        <f>IF(F224="","",F224-G224)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I224" s="3" t="s">
@@ -13267,9 +13246,9 @@
         <v>100</v>
       </c>
       <c r="D225" s="5"/>
-      <c r="E225" s="21"/>
+      <c r="E225" s="13"/>
       <c r="F225" s="4" t="str">
-        <f>IF(OR(D225="",E225=""),"",D225*E225)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G225" s="4" t="str">
@@ -13277,7 +13256,7 @@
         <v/>
       </c>
       <c r="H225" s="4" t="str">
-        <f>IF(F225="","",F225-G225)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I225" s="3" t="s">
@@ -13293,9 +13272,9 @@
         <v>100</v>
       </c>
       <c r="D226" s="5"/>
-      <c r="E226" s="21"/>
+      <c r="E226" s="13"/>
       <c r="F226" s="4" t="str">
-        <f>IF(OR(D226="",E226=""),"",D226*E226)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G226" s="4" t="str">
@@ -13303,7 +13282,7 @@
         <v/>
       </c>
       <c r="H226" s="4" t="str">
-        <f>IF(F226="","",F226-G226)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I226" s="3" t="s">
@@ -13319,9 +13298,9 @@
         <v>100</v>
       </c>
       <c r="D227" s="5"/>
-      <c r="E227" s="21"/>
+      <c r="E227" s="13"/>
       <c r="F227" s="4" t="str">
-        <f>IF(OR(D227="",E227=""),"",D227*E227)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G227" s="4" t="str">
@@ -13329,7 +13308,7 @@
         <v/>
       </c>
       <c r="H227" s="4" t="str">
-        <f>IF(F227="","",F227-G227)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I227" s="3" t="s">
@@ -13345,9 +13324,9 @@
         <v>100</v>
       </c>
       <c r="D228" s="5"/>
-      <c r="E228" s="21"/>
+      <c r="E228" s="13"/>
       <c r="F228" s="4" t="str">
-        <f>IF(OR(D228="",E228=""),"",D228*E228)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G228" s="4" t="str">
@@ -13355,7 +13334,7 @@
         <v/>
       </c>
       <c r="H228" s="4" t="str">
-        <f>IF(F228="","",F228-G228)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I228" s="3" t="s">
@@ -13371,9 +13350,9 @@
         <v>100</v>
       </c>
       <c r="D229" s="5"/>
-      <c r="E229" s="21"/>
+      <c r="E229" s="13"/>
       <c r="F229" s="4" t="str">
-        <f>IF(OR(D229="",E229=""),"",D229*E229)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G229" s="4" t="str">
@@ -13381,7 +13360,7 @@
         <v/>
       </c>
       <c r="H229" s="4" t="str">
-        <f>IF(F229="","",F229-G229)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I229" s="3" t="s">
@@ -13397,9 +13376,9 @@
         <v>100</v>
       </c>
       <c r="D230" s="5"/>
-      <c r="E230" s="21"/>
+      <c r="E230" s="13"/>
       <c r="F230" s="4" t="str">
-        <f>IF(OR(D230="",E230=""),"",D230*E230)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G230" s="4" t="str">
@@ -13407,7 +13386,7 @@
         <v/>
       </c>
       <c r="H230" s="4" t="str">
-        <f>IF(F230="","",F230-G230)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I230" s="3" t="s">
@@ -13423,9 +13402,9 @@
         <v>100</v>
       </c>
       <c r="D231" s="5"/>
-      <c r="E231" s="21"/>
+      <c r="E231" s="13"/>
       <c r="F231" s="4" t="str">
-        <f>IF(OR(D231="",E231=""),"",D231*E231)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G231" s="4" t="str">
@@ -13433,7 +13412,7 @@
         <v/>
       </c>
       <c r="H231" s="4" t="str">
-        <f>IF(F231="","",F231-G231)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I231" s="3" t="s">
@@ -13449,9 +13428,9 @@
         <v>100</v>
       </c>
       <c r="D232" s="5"/>
-      <c r="E232" s="21"/>
+      <c r="E232" s="13"/>
       <c r="F232" s="4" t="str">
-        <f>IF(OR(D232="",E232=""),"",D232*E232)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G232" s="4" t="str">
@@ -13459,7 +13438,7 @@
         <v/>
       </c>
       <c r="H232" s="4" t="str">
-        <f>IF(F232="","",F232-G232)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I232" s="3" t="s">
@@ -13475,9 +13454,9 @@
         <v>100</v>
       </c>
       <c r="D233" s="5"/>
-      <c r="E233" s="21"/>
+      <c r="E233" s="13"/>
       <c r="F233" s="4" t="str">
-        <f>IF(OR(D233="",E233=""),"",D233*E233)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G233" s="4" t="str">
@@ -13485,7 +13464,7 @@
         <v/>
       </c>
       <c r="H233" s="4" t="str">
-        <f>IF(F233="","",F233-G233)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I233" s="3" t="s">
@@ -13501,9 +13480,9 @@
         <v>100</v>
       </c>
       <c r="D234" s="5"/>
-      <c r="E234" s="21"/>
+      <c r="E234" s="13"/>
       <c r="F234" s="4" t="str">
-        <f>IF(OR(D234="",E234=""),"",D234*E234)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G234" s="4" t="str">
@@ -13511,7 +13490,7 @@
         <v/>
       </c>
       <c r="H234" s="4" t="str">
-        <f>IF(F234="","",F234-G234)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I234" s="3" t="s">
@@ -13527,9 +13506,9 @@
         <v>100</v>
       </c>
       <c r="D235" s="5"/>
-      <c r="E235" s="21"/>
+      <c r="E235" s="13"/>
       <c r="F235" s="4" t="str">
-        <f>IF(OR(D235="",E235=""),"",D235*E235)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G235" s="4" t="str">
@@ -13537,7 +13516,7 @@
         <v/>
       </c>
       <c r="H235" s="4" t="str">
-        <f>IF(F235="","",F235-G235)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I235" s="3" t="s">
@@ -13553,9 +13532,9 @@
         <v>100</v>
       </c>
       <c r="D236" s="5"/>
-      <c r="E236" s="21"/>
+      <c r="E236" s="13"/>
       <c r="F236" s="4" t="str">
-        <f>IF(OR(D236="",E236=""),"",D236*E236)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G236" s="4" t="str">
@@ -13563,7 +13542,7 @@
         <v/>
       </c>
       <c r="H236" s="4" t="str">
-        <f>IF(F236="","",F236-G236)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I236" s="3" t="s">
@@ -13579,9 +13558,9 @@
         <v>100</v>
       </c>
       <c r="D237" s="5"/>
-      <c r="E237" s="21"/>
+      <c r="E237" s="13"/>
       <c r="F237" s="4" t="str">
-        <f>IF(OR(D237="",E237=""),"",D237*E237)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G237" s="4" t="str">
@@ -13589,7 +13568,7 @@
         <v/>
       </c>
       <c r="H237" s="4" t="str">
-        <f>IF(F237="","",F237-G237)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I237" s="3" t="s">
@@ -13605,9 +13584,9 @@
         <v>100</v>
       </c>
       <c r="D238" s="5"/>
-      <c r="E238" s="21"/>
+      <c r="E238" s="13"/>
       <c r="F238" s="4" t="str">
-        <f>IF(OR(D238="",E238=""),"",D238*E238)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G238" s="4" t="str">
@@ -13615,7 +13594,7 @@
         <v/>
       </c>
       <c r="H238" s="4" t="str">
-        <f>IF(F238="","",F238-G238)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I238" s="3" t="s">
@@ -13631,9 +13610,9 @@
         <v>100</v>
       </c>
       <c r="D239" s="5"/>
-      <c r="E239" s="21"/>
+      <c r="E239" s="13"/>
       <c r="F239" s="4" t="str">
-        <f>IF(OR(D239="",E239=""),"",D239*E239)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G239" s="4" t="str">
@@ -13641,7 +13620,7 @@
         <v/>
       </c>
       <c r="H239" s="4" t="str">
-        <f>IF(F239="","",F239-G239)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I239" s="3" t="s">
@@ -13657,9 +13636,9 @@
         <v>100</v>
       </c>
       <c r="D240" s="5"/>
-      <c r="E240" s="21"/>
+      <c r="E240" s="13"/>
       <c r="F240" s="4" t="str">
-        <f>IF(OR(D240="",E240=""),"",D240*E240)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G240" s="4" t="str">
@@ -13667,7 +13646,7 @@
         <v/>
       </c>
       <c r="H240" s="4" t="str">
-        <f>IF(F240="","",F240-G240)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I240" s="3" t="s">
@@ -13683,9 +13662,9 @@
         <v>100</v>
       </c>
       <c r="D241" s="5"/>
-      <c r="E241" s="21"/>
+      <c r="E241" s="13"/>
       <c r="F241" s="4" t="str">
-        <f>IF(OR(D241="",E241=""),"",D241*E241)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G241" s="4" t="str">
@@ -13693,7 +13672,7 @@
         <v/>
       </c>
       <c r="H241" s="4" t="str">
-        <f>IF(F241="","",F241-G241)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I241" s="3" t="s">
@@ -13709,9 +13688,9 @@
         <v>100</v>
       </c>
       <c r="D242" s="5"/>
-      <c r="E242" s="21"/>
+      <c r="E242" s="13"/>
       <c r="F242" s="4" t="str">
-        <f>IF(OR(D242="",E242=""),"",D242*E242)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G242" s="4" t="str">
@@ -13719,7 +13698,7 @@
         <v/>
       </c>
       <c r="H242" s="4" t="str">
-        <f>IF(F242="","",F242-G242)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I242" s="3" t="s">
@@ -13735,9 +13714,9 @@
         <v>100</v>
       </c>
       <c r="D243" s="5"/>
-      <c r="E243" s="21"/>
+      <c r="E243" s="13"/>
       <c r="F243" s="4" t="str">
-        <f>IF(OR(D243="",E243=""),"",D243*E243)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G243" s="4" t="str">
@@ -13745,7 +13724,7 @@
         <v/>
       </c>
       <c r="H243" s="4" t="str">
-        <f>IF(F243="","",F243-G243)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I243" s="3" t="s">
@@ -13761,9 +13740,9 @@
         <v>100</v>
       </c>
       <c r="D244" s="5"/>
-      <c r="E244" s="21"/>
+      <c r="E244" s="13"/>
       <c r="F244" s="4" t="str">
-        <f>IF(OR(D244="",E244=""),"",D244*E244)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G244" s="4" t="str">
@@ -13771,7 +13750,7 @@
         <v/>
       </c>
       <c r="H244" s="4" t="str">
-        <f>IF(F244="","",F244-G244)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I244" s="3" t="s">
@@ -13787,9 +13766,9 @@
         <v>100</v>
       </c>
       <c r="D245" s="5"/>
-      <c r="E245" s="21"/>
+      <c r="E245" s="13"/>
       <c r="F245" s="4" t="str">
-        <f>IF(OR(D245="",E245=""),"",D245*E245)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G245" s="4" t="str">
@@ -13797,7 +13776,7 @@
         <v/>
       </c>
       <c r="H245" s="4" t="str">
-        <f>IF(F245="","",F245-G245)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I245" s="3" t="s">
@@ -13813,9 +13792,9 @@
         <v>100</v>
       </c>
       <c r="D246" s="5"/>
-      <c r="E246" s="21"/>
+      <c r="E246" s="13"/>
       <c r="F246" s="4" t="str">
-        <f>IF(OR(D246="",E246=""),"",D246*E246)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G246" s="4" t="str">
@@ -13823,7 +13802,7 @@
         <v/>
       </c>
       <c r="H246" s="4" t="str">
-        <f>IF(F246="","",F246-G246)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I246" s="3" t="s">
@@ -13839,9 +13818,9 @@
         <v>100</v>
       </c>
       <c r="D247" s="5"/>
-      <c r="E247" s="21"/>
+      <c r="E247" s="13"/>
       <c r="F247" s="4" t="str">
-        <f>IF(OR(D247="",E247=""),"",D247*E247)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G247" s="4" t="str">
@@ -13849,7 +13828,7 @@
         <v/>
       </c>
       <c r="H247" s="4" t="str">
-        <f>IF(F247="","",F247-G247)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I247" s="3" t="s">
@@ -13865,9 +13844,9 @@
         <v>100</v>
       </c>
       <c r="D248" s="5"/>
-      <c r="E248" s="21"/>
+      <c r="E248" s="13"/>
       <c r="F248" s="4" t="str">
-        <f>IF(OR(D248="",E248=""),"",D248*E248)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G248" s="4" t="str">
@@ -13875,7 +13854,7 @@
         <v/>
       </c>
       <c r="H248" s="4" t="str">
-        <f>IF(F248="","",F248-G248)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I248" s="3" t="s">
@@ -13891,9 +13870,9 @@
         <v>100</v>
       </c>
       <c r="D249" s="5"/>
-      <c r="E249" s="21"/>
+      <c r="E249" s="13"/>
       <c r="F249" s="4" t="str">
-        <f>IF(OR(D249="",E249=""),"",D249*E249)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G249" s="4" t="str">
@@ -13901,7 +13880,7 @@
         <v/>
       </c>
       <c r="H249" s="4" t="str">
-        <f>IF(F249="","",F249-G249)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I249" s="3" t="s">
@@ -13917,9 +13896,9 @@
         <v>100</v>
       </c>
       <c r="D250" s="5"/>
-      <c r="E250" s="21"/>
+      <c r="E250" s="13"/>
       <c r="F250" s="4" t="str">
-        <f>IF(OR(D250="",E250=""),"",D250*E250)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G250" s="4" t="str">
@@ -13927,7 +13906,7 @@
         <v/>
       </c>
       <c r="H250" s="4" t="str">
-        <f>IF(F250="","",F250-G250)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I250" s="3" t="s">
@@ -13943,9 +13922,9 @@
         <v>100</v>
       </c>
       <c r="D251" s="5"/>
-      <c r="E251" s="21"/>
+      <c r="E251" s="13"/>
       <c r="F251" s="4" t="str">
-        <f>IF(OR(D251="",E251=""),"",D251*E251)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G251" s="4" t="str">
@@ -13953,7 +13932,7 @@
         <v/>
       </c>
       <c r="H251" s="4" t="str">
-        <f>IF(F251="","",F251-G251)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I251" s="3" t="s">
@@ -13969,9 +13948,9 @@
         <v>100</v>
       </c>
       <c r="D252" s="5"/>
-      <c r="E252" s="21"/>
+      <c r="E252" s="13"/>
       <c r="F252" s="4" t="str">
-        <f>IF(OR(D252="",E252=""),"",D252*E252)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G252" s="4" t="str">
@@ -13979,7 +13958,7 @@
         <v/>
       </c>
       <c r="H252" s="4" t="str">
-        <f>IF(F252="","",F252-G252)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I252" s="3" t="s">
@@ -13995,9 +13974,9 @@
         <v>100</v>
       </c>
       <c r="D253" s="5"/>
-      <c r="E253" s="21"/>
+      <c r="E253" s="13"/>
       <c r="F253" s="4" t="str">
-        <f>IF(OR(D253="",E253=""),"",D253*E253)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G253" s="4" t="str">
@@ -14005,7 +13984,7 @@
         <v/>
       </c>
       <c r="H253" s="4" t="str">
-        <f>IF(F253="","",F253-G253)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I253" s="3" t="s">
@@ -14021,9 +14000,9 @@
         <v>100</v>
       </c>
       <c r="D254" s="5"/>
-      <c r="E254" s="21"/>
+      <c r="E254" s="13"/>
       <c r="F254" s="4" t="str">
-        <f>IF(OR(D254="",E254=""),"",D254*E254)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G254" s="4" t="str">
@@ -14031,7 +14010,7 @@
         <v/>
       </c>
       <c r="H254" s="4" t="str">
-        <f>IF(F254="","",F254-G254)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I254" s="3" t="s">
@@ -14047,9 +14026,9 @@
         <v>100</v>
       </c>
       <c r="D255" s="5"/>
-      <c r="E255" s="21"/>
+      <c r="E255" s="13"/>
       <c r="F255" s="4" t="str">
-        <f>IF(OR(D255="",E255=""),"",D255*E255)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G255" s="4" t="str">
@@ -14057,7 +14036,7 @@
         <v/>
       </c>
       <c r="H255" s="4" t="str">
-        <f>IF(F255="","",F255-G255)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I255" s="3" t="s">
@@ -14073,9 +14052,9 @@
         <v>100</v>
       </c>
       <c r="D256" s="5"/>
-      <c r="E256" s="21"/>
+      <c r="E256" s="13"/>
       <c r="F256" s="4" t="str">
-        <f>IF(OR(D256="",E256=""),"",D256*E256)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G256" s="4" t="str">
@@ -14083,7 +14062,7 @@
         <v/>
       </c>
       <c r="H256" s="4" t="str">
-        <f>IF(F256="","",F256-G256)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I256" s="3" t="s">
@@ -14099,9 +14078,9 @@
         <v>100</v>
       </c>
       <c r="D257" s="5"/>
-      <c r="E257" s="21"/>
+      <c r="E257" s="13"/>
       <c r="F257" s="4" t="str">
-        <f>IF(OR(D257="",E257=""),"",D257*E257)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G257" s="4" t="str">
@@ -14109,7 +14088,7 @@
         <v/>
       </c>
       <c r="H257" s="4" t="str">
-        <f>IF(F257="","",F257-G257)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I257" s="3" t="s">
@@ -14125,9 +14104,9 @@
         <v>100</v>
       </c>
       <c r="D258" s="5"/>
-      <c r="E258" s="21"/>
+      <c r="E258" s="13"/>
       <c r="F258" s="4" t="str">
-        <f>IF(OR(D258="",E258=""),"",D258*E258)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G258" s="4" t="str">
@@ -14135,7 +14114,7 @@
         <v/>
       </c>
       <c r="H258" s="4" t="str">
-        <f>IF(F258="","",F258-G258)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I258" s="3" t="s">
@@ -14151,9 +14130,9 @@
         <v>100</v>
       </c>
       <c r="D259" s="5"/>
-      <c r="E259" s="21"/>
+      <c r="E259" s="13"/>
       <c r="F259" s="4" t="str">
-        <f>IF(OR(D259="",E259=""),"",D259*E259)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G259" s="4" t="str">
@@ -14161,7 +14140,7 @@
         <v/>
       </c>
       <c r="H259" s="4" t="str">
-        <f>IF(F259="","",F259-G259)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I259" s="3" t="s">
@@ -14177,9 +14156,9 @@
         <v>100</v>
       </c>
       <c r="D260" s="5"/>
-      <c r="E260" s="21"/>
+      <c r="E260" s="13"/>
       <c r="F260" s="4" t="str">
-        <f>IF(OR(D260="",E260=""),"",D260*E260)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G260" s="4" t="str">
@@ -14187,7 +14166,7 @@
         <v/>
       </c>
       <c r="H260" s="4" t="str">
-        <f>IF(F260="","",F260-G260)</f>
+        <f t="shared" ref="H260:H323" si="8">IF(F260="","",F260-G260)</f>
         <v/>
       </c>
       <c r="I260" s="3" t="s">
@@ -14203,9 +14182,9 @@
         <v>100</v>
       </c>
       <c r="D261" s="5"/>
-      <c r="E261" s="21"/>
+      <c r="E261" s="13"/>
       <c r="F261" s="4" t="str">
-        <f>IF(OR(D261="",E261=""),"",D261*E261)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G261" s="4" t="str">
@@ -14213,7 +14192,7 @@
         <v/>
       </c>
       <c r="H261" s="4" t="str">
-        <f>IF(F261="","",F261-G261)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I261" s="3" t="s">
@@ -14229,9 +14208,9 @@
         <v>100</v>
       </c>
       <c r="D262" s="5"/>
-      <c r="E262" s="21"/>
+      <c r="E262" s="13"/>
       <c r="F262" s="4" t="str">
-        <f>IF(OR(D262="",E262=""),"",D262*E262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G262" s="4" t="str">
@@ -14239,7 +14218,7 @@
         <v/>
       </c>
       <c r="H262" s="4" t="str">
-        <f>IF(F262="","",F262-G262)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I262" s="3" t="s">
@@ -14255,9 +14234,9 @@
         <v>100</v>
       </c>
       <c r="D263" s="5"/>
-      <c r="E263" s="21"/>
+      <c r="E263" s="13"/>
       <c r="F263" s="4" t="str">
-        <f>IF(OR(D263="",E263=""),"",D263*E263)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G263" s="4" t="str">
@@ -14265,7 +14244,7 @@
         <v/>
       </c>
       <c r="H263" s="4" t="str">
-        <f>IF(F263="","",F263-G263)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I263" s="3" t="s">
@@ -14281,9 +14260,9 @@
         <v>100</v>
       </c>
       <c r="D264" s="5"/>
-      <c r="E264" s="21"/>
+      <c r="E264" s="13"/>
       <c r="F264" s="4" t="str">
-        <f>IF(OR(D264="",E264=""),"",D264*E264)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G264" s="4" t="str">
@@ -14291,7 +14270,7 @@
         <v/>
       </c>
       <c r="H264" s="4" t="str">
-        <f>IF(F264="","",F264-G264)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I264" s="3" t="s">
@@ -14307,9 +14286,9 @@
         <v>100</v>
       </c>
       <c r="D265" s="5"/>
-      <c r="E265" s="21"/>
+      <c r="E265" s="13"/>
       <c r="F265" s="4" t="str">
-        <f>IF(OR(D265="",E265=""),"",D265*E265)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G265" s="4" t="str">
@@ -14317,7 +14296,7 @@
         <v/>
       </c>
       <c r="H265" s="4" t="str">
-        <f>IF(F265="","",F265-G265)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I265" s="3" t="s">
@@ -14333,9 +14312,9 @@
         <v>100</v>
       </c>
       <c r="D266" s="5"/>
-      <c r="E266" s="21"/>
+      <c r="E266" s="13"/>
       <c r="F266" s="4" t="str">
-        <f>IF(OR(D266="",E266=""),"",D266*E266)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G266" s="4" t="str">
@@ -14343,7 +14322,7 @@
         <v/>
       </c>
       <c r="H266" s="4" t="str">
-        <f>IF(F266="","",F266-G266)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I266" s="3" t="s">
@@ -14359,9 +14338,9 @@
         <v>100</v>
       </c>
       <c r="D267" s="5"/>
-      <c r="E267" s="21"/>
+      <c r="E267" s="13"/>
       <c r="F267" s="4" t="str">
-        <f>IF(OR(D267="",E267=""),"",D267*E267)</f>
+        <f t="shared" ref="F267:F330" si="9">IF(OR(D267="",E267=""),"",D267*E267)</f>
         <v/>
       </c>
       <c r="G267" s="4" t="str">
@@ -14369,7 +14348,7 @@
         <v/>
       </c>
       <c r="H267" s="4" t="str">
-        <f>IF(F267="","",F267-G267)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I267" s="3" t="s">
@@ -14385,9 +14364,9 @@
         <v>100</v>
       </c>
       <c r="D268" s="5"/>
-      <c r="E268" s="21"/>
+      <c r="E268" s="13"/>
       <c r="F268" s="4" t="str">
-        <f>IF(OR(D268="",E268=""),"",D268*E268)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G268" s="4" t="str">
@@ -14395,7 +14374,7 @@
         <v/>
       </c>
       <c r="H268" s="4" t="str">
-        <f>IF(F268="","",F268-G268)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I268" s="3" t="s">
@@ -14411,9 +14390,9 @@
         <v>100</v>
       </c>
       <c r="D269" s="5"/>
-      <c r="E269" s="21"/>
+      <c r="E269" s="13"/>
       <c r="F269" s="4" t="str">
-        <f>IF(OR(D269="",E269=""),"",D269*E269)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G269" s="4" t="str">
@@ -14421,7 +14400,7 @@
         <v/>
       </c>
       <c r="H269" s="4" t="str">
-        <f>IF(F269="","",F269-G269)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I269" s="3" t="s">
@@ -14437,9 +14416,9 @@
         <v>100</v>
       </c>
       <c r="D270" s="5"/>
-      <c r="E270" s="21"/>
+      <c r="E270" s="13"/>
       <c r="F270" s="4" t="str">
-        <f>IF(OR(D270="",E270=""),"",D270*E270)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G270" s="4" t="str">
@@ -14447,7 +14426,7 @@
         <v/>
       </c>
       <c r="H270" s="4" t="str">
-        <f>IF(F270="","",F270-G270)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I270" s="3" t="s">
@@ -14463,9 +14442,9 @@
         <v>100</v>
       </c>
       <c r="D271" s="5"/>
-      <c r="E271" s="21"/>
+      <c r="E271" s="13"/>
       <c r="F271" s="4" t="str">
-        <f>IF(OR(D271="",E271=""),"",D271*E271)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G271" s="4" t="str">
@@ -14473,7 +14452,7 @@
         <v/>
       </c>
       <c r="H271" s="4" t="str">
-        <f>IF(F271="","",F271-G271)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I271" s="3" t="s">
@@ -14489,9 +14468,9 @@
         <v>100</v>
       </c>
       <c r="D272" s="5"/>
-      <c r="E272" s="21"/>
+      <c r="E272" s="13"/>
       <c r="F272" s="4" t="str">
-        <f>IF(OR(D272="",E272=""),"",D272*E272)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G272" s="4" t="str">
@@ -14499,7 +14478,7 @@
         <v/>
       </c>
       <c r="H272" s="4" t="str">
-        <f>IF(F272="","",F272-G272)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I272" s="3" t="s">
@@ -14515,9 +14494,9 @@
         <v>100</v>
       </c>
       <c r="D273" s="5"/>
-      <c r="E273" s="21"/>
+      <c r="E273" s="13"/>
       <c r="F273" s="4" t="str">
-        <f>IF(OR(D273="",E273=""),"",D273*E273)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G273" s="4" t="str">
@@ -14525,7 +14504,7 @@
         <v/>
       </c>
       <c r="H273" s="4" t="str">
-        <f>IF(F273="","",F273-G273)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I273" s="3" t="s">
@@ -14541,9 +14520,9 @@
         <v>100</v>
       </c>
       <c r="D274" s="5"/>
-      <c r="E274" s="21"/>
+      <c r="E274" s="13"/>
       <c r="F274" s="4" t="str">
-        <f>IF(OR(D274="",E274=""),"",D274*E274)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G274" s="4" t="str">
@@ -14551,7 +14530,7 @@
         <v/>
       </c>
       <c r="H274" s="4" t="str">
-        <f>IF(F274="","",F274-G274)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I274" s="3" t="s">
@@ -14567,9 +14546,9 @@
         <v>100</v>
       </c>
       <c r="D275" s="5"/>
-      <c r="E275" s="21"/>
+      <c r="E275" s="13"/>
       <c r="F275" s="4" t="str">
-        <f>IF(OR(D275="",E275=""),"",D275*E275)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G275" s="4" t="str">
@@ -14577,7 +14556,7 @@
         <v/>
       </c>
       <c r="H275" s="4" t="str">
-        <f>IF(F275="","",F275-G275)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I275" s="3" t="s">
@@ -14593,9 +14572,9 @@
         <v>100</v>
       </c>
       <c r="D276" s="5"/>
-      <c r="E276" s="21"/>
+      <c r="E276" s="13"/>
       <c r="F276" s="4" t="str">
-        <f>IF(OR(D276="",E276=""),"",D276*E276)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G276" s="4" t="str">
@@ -14603,7 +14582,7 @@
         <v/>
       </c>
       <c r="H276" s="4" t="str">
-        <f>IF(F276="","",F276-G276)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I276" s="3" t="s">
@@ -14619,9 +14598,9 @@
         <v>100</v>
       </c>
       <c r="D277" s="5"/>
-      <c r="E277" s="21"/>
+      <c r="E277" s="13"/>
       <c r="F277" s="4" t="str">
-        <f>IF(OR(D277="",E277=""),"",D277*E277)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G277" s="4" t="str">
@@ -14629,7 +14608,7 @@
         <v/>
       </c>
       <c r="H277" s="4" t="str">
-        <f>IF(F277="","",F277-G277)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I277" s="3" t="s">
@@ -14645,9 +14624,9 @@
         <v>100</v>
       </c>
       <c r="D278" s="5"/>
-      <c r="E278" s="21"/>
+      <c r="E278" s="13"/>
       <c r="F278" s="4" t="str">
-        <f>IF(OR(D278="",E278=""),"",D278*E278)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G278" s="4" t="str">
@@ -14655,7 +14634,7 @@
         <v/>
       </c>
       <c r="H278" s="4" t="str">
-        <f>IF(F278="","",F278-G278)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I278" s="3" t="s">
@@ -14671,9 +14650,9 @@
         <v>100</v>
       </c>
       <c r="D279" s="5"/>
-      <c r="E279" s="21"/>
+      <c r="E279" s="13"/>
       <c r="F279" s="4" t="str">
-        <f>IF(OR(D279="",E279=""),"",D279*E279)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G279" s="4" t="str">
@@ -14681,7 +14660,7 @@
         <v/>
       </c>
       <c r="H279" s="4" t="str">
-        <f>IF(F279="","",F279-G279)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I279" s="3" t="s">
@@ -14697,9 +14676,9 @@
         <v>100</v>
       </c>
       <c r="D280" s="5"/>
-      <c r="E280" s="21"/>
+      <c r="E280" s="13"/>
       <c r="F280" s="4" t="str">
-        <f>IF(OR(D280="",E280=""),"",D280*E280)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G280" s="4" t="str">
@@ -14707,7 +14686,7 @@
         <v/>
       </c>
       <c r="H280" s="4" t="str">
-        <f>IF(F280="","",F280-G280)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I280" s="3" t="s">
@@ -14723,9 +14702,9 @@
         <v>100</v>
       </c>
       <c r="D281" s="5"/>
-      <c r="E281" s="21"/>
+      <c r="E281" s="13"/>
       <c r="F281" s="4" t="str">
-        <f>IF(OR(D281="",E281=""),"",D281*E281)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G281" s="4" t="str">
@@ -14733,7 +14712,7 @@
         <v/>
       </c>
       <c r="H281" s="4" t="str">
-        <f>IF(F281="","",F281-G281)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I281" s="3" t="s">
@@ -14749,9 +14728,9 @@
         <v>100</v>
       </c>
       <c r="D282" s="5"/>
-      <c r="E282" s="21"/>
+      <c r="E282" s="13"/>
       <c r="F282" s="4" t="str">
-        <f>IF(OR(D282="",E282=""),"",D282*E282)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G282" s="4" t="str">
@@ -14759,7 +14738,7 @@
         <v/>
       </c>
       <c r="H282" s="4" t="str">
-        <f>IF(F282="","",F282-G282)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I282" s="3" t="s">
@@ -14775,9 +14754,9 @@
         <v>100</v>
       </c>
       <c r="D283" s="5"/>
-      <c r="E283" s="21"/>
+      <c r="E283" s="13"/>
       <c r="F283" s="4" t="str">
-        <f>IF(OR(D283="",E283=""),"",D283*E283)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G283" s="4" t="str">
@@ -14785,7 +14764,7 @@
         <v/>
       </c>
       <c r="H283" s="4" t="str">
-        <f>IF(F283="","",F283-G283)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I283" s="3" t="s">
@@ -14801,9 +14780,9 @@
         <v>100</v>
       </c>
       <c r="D284" s="5"/>
-      <c r="E284" s="21"/>
+      <c r="E284" s="13"/>
       <c r="F284" s="4" t="str">
-        <f>IF(OR(D284="",E284=""),"",D284*E284)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G284" s="4" t="str">
@@ -14811,7 +14790,7 @@
         <v/>
       </c>
       <c r="H284" s="4" t="str">
-        <f>IF(F284="","",F284-G284)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I284" s="3" t="s">
@@ -14827,9 +14806,9 @@
         <v>100</v>
       </c>
       <c r="D285" s="5"/>
-      <c r="E285" s="21"/>
+      <c r="E285" s="13"/>
       <c r="F285" s="4" t="str">
-        <f>IF(OR(D285="",E285=""),"",D285*E285)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G285" s="4" t="str">
@@ -14837,7 +14816,7 @@
         <v/>
       </c>
       <c r="H285" s="4" t="str">
-        <f>IF(F285="","",F285-G285)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I285" s="3" t="s">
@@ -14853,9 +14832,9 @@
         <v>100</v>
       </c>
       <c r="D286" s="5"/>
-      <c r="E286" s="21"/>
+      <c r="E286" s="13"/>
       <c r="F286" s="4" t="str">
-        <f>IF(OR(D286="",E286=""),"",D286*E286)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G286" s="4" t="str">
@@ -14863,7 +14842,7 @@
         <v/>
       </c>
       <c r="H286" s="4" t="str">
-        <f>IF(F286="","",F286-G286)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I286" s="3" t="s">
@@ -14879,9 +14858,9 @@
         <v>100</v>
       </c>
       <c r="D287" s="5"/>
-      <c r="E287" s="21"/>
+      <c r="E287" s="13"/>
       <c r="F287" s="4" t="str">
-        <f>IF(OR(D287="",E287=""),"",D287*E287)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G287" s="4" t="str">
@@ -14889,7 +14868,7 @@
         <v/>
       </c>
       <c r="H287" s="4" t="str">
-        <f>IF(F287="","",F287-G287)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I287" s="3" t="s">
@@ -14905,9 +14884,9 @@
         <v>100</v>
       </c>
       <c r="D288" s="5"/>
-      <c r="E288" s="21"/>
+      <c r="E288" s="13"/>
       <c r="F288" s="4" t="str">
-        <f>IF(OR(D288="",E288=""),"",D288*E288)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G288" s="4" t="str">
@@ -14915,7 +14894,7 @@
         <v/>
       </c>
       <c r="H288" s="4" t="str">
-        <f>IF(F288="","",F288-G288)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I288" s="3" t="s">
@@ -14931,9 +14910,9 @@
         <v>100</v>
       </c>
       <c r="D289" s="5"/>
-      <c r="E289" s="21"/>
+      <c r="E289" s="13"/>
       <c r="F289" s="4" t="str">
-        <f>IF(OR(D289="",E289=""),"",D289*E289)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G289" s="4" t="str">
@@ -14941,7 +14920,7 @@
         <v/>
       </c>
       <c r="H289" s="4" t="str">
-        <f>IF(F289="","",F289-G289)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I289" s="3" t="s">
@@ -14957,9 +14936,9 @@
         <v>100</v>
       </c>
       <c r="D290" s="5"/>
-      <c r="E290" s="21"/>
+      <c r="E290" s="13"/>
       <c r="F290" s="4" t="str">
-        <f>IF(OR(D290="",E290=""),"",D290*E290)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G290" s="4" t="str">
@@ -14967,7 +14946,7 @@
         <v/>
       </c>
       <c r="H290" s="4" t="str">
-        <f>IF(F290="","",F290-G290)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I290" s="3" t="s">
@@ -14983,9 +14962,9 @@
         <v>100</v>
       </c>
       <c r="D291" s="5"/>
-      <c r="E291" s="21"/>
+      <c r="E291" s="13"/>
       <c r="F291" s="4" t="str">
-        <f>IF(OR(D291="",E291=""),"",D291*E291)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G291" s="4" t="str">
@@ -14993,7 +14972,7 @@
         <v/>
       </c>
       <c r="H291" s="4" t="str">
-        <f>IF(F291="","",F291-G291)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I291" s="3" t="s">
@@ -15009,9 +14988,9 @@
         <v>100</v>
       </c>
       <c r="D292" s="5"/>
-      <c r="E292" s="21"/>
+      <c r="E292" s="13"/>
       <c r="F292" s="4" t="str">
-        <f>IF(OR(D292="",E292=""),"",D292*E292)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G292" s="4" t="str">
@@ -15019,7 +14998,7 @@
         <v/>
       </c>
       <c r="H292" s="4" t="str">
-        <f>IF(F292="","",F292-G292)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I292" s="3" t="s">
@@ -15035,9 +15014,9 @@
         <v>100</v>
       </c>
       <c r="D293" s="5"/>
-      <c r="E293" s="21"/>
+      <c r="E293" s="13"/>
       <c r="F293" s="4" t="str">
-        <f>IF(OR(D293="",E293=""),"",D293*E293)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G293" s="4" t="str">
@@ -15045,7 +15024,7 @@
         <v/>
       </c>
       <c r="H293" s="4" t="str">
-        <f>IF(F293="","",F293-G293)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I293" s="3" t="s">
@@ -15061,9 +15040,9 @@
         <v>100</v>
       </c>
       <c r="D294" s="5"/>
-      <c r="E294" s="21"/>
+      <c r="E294" s="13"/>
       <c r="F294" s="4" t="str">
-        <f>IF(OR(D294="",E294=""),"",D294*E294)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G294" s="4" t="str">
@@ -15071,7 +15050,7 @@
         <v/>
       </c>
       <c r="H294" s="4" t="str">
-        <f>IF(F294="","",F294-G294)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I294" s="3" t="s">
@@ -15087,9 +15066,9 @@
         <v>100</v>
       </c>
       <c r="D295" s="5"/>
-      <c r="E295" s="21"/>
+      <c r="E295" s="13"/>
       <c r="F295" s="4" t="str">
-        <f>IF(OR(D295="",E295=""),"",D295*E295)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G295" s="4" t="str">
@@ -15097,7 +15076,7 @@
         <v/>
       </c>
       <c r="H295" s="4" t="str">
-        <f>IF(F295="","",F295-G295)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I295" s="3" t="s">
@@ -15113,9 +15092,9 @@
         <v>100</v>
       </c>
       <c r="D296" s="5"/>
-      <c r="E296" s="21"/>
+      <c r="E296" s="13"/>
       <c r="F296" s="4" t="str">
-        <f>IF(OR(D296="",E296=""),"",D296*E296)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G296" s="4" t="str">
@@ -15123,7 +15102,7 @@
         <v/>
       </c>
       <c r="H296" s="4" t="str">
-        <f>IF(F296="","",F296-G296)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I296" s="3" t="s">
@@ -15139,9 +15118,9 @@
         <v>100</v>
       </c>
       <c r="D297" s="5"/>
-      <c r="E297" s="21"/>
+      <c r="E297" s="13"/>
       <c r="F297" s="4" t="str">
-        <f>IF(OR(D297="",E297=""),"",D297*E297)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G297" s="4" t="str">
@@ -15149,7 +15128,7 @@
         <v/>
       </c>
       <c r="H297" s="4" t="str">
-        <f>IF(F297="","",F297-G297)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I297" s="3" t="s">
@@ -15165,9 +15144,9 @@
         <v>100</v>
       </c>
       <c r="D298" s="5"/>
-      <c r="E298" s="21"/>
+      <c r="E298" s="13"/>
       <c r="F298" s="4" t="str">
-        <f>IF(OR(D298="",E298=""),"",D298*E298)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G298" s="4" t="str">
@@ -15175,7 +15154,7 @@
         <v/>
       </c>
       <c r="H298" s="4" t="str">
-        <f>IF(F298="","",F298-G298)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I298" s="3" t="s">
@@ -15191,9 +15170,9 @@
         <v>100</v>
       </c>
       <c r="D299" s="5"/>
-      <c r="E299" s="21"/>
+      <c r="E299" s="13"/>
       <c r="F299" s="4" t="str">
-        <f>IF(OR(D299="",E299=""),"",D299*E299)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G299" s="4" t="str">
@@ -15201,7 +15180,7 @@
         <v/>
       </c>
       <c r="H299" s="4" t="str">
-        <f>IF(F299="","",F299-G299)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I299" s="3" t="s">
@@ -15217,9 +15196,9 @@
         <v>100</v>
       </c>
       <c r="D300" s="5"/>
-      <c r="E300" s="21"/>
+      <c r="E300" s="13"/>
       <c r="F300" s="4" t="str">
-        <f>IF(OR(D300="",E300=""),"",D300*E300)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G300" s="4" t="str">
@@ -15227,7 +15206,7 @@
         <v/>
       </c>
       <c r="H300" s="4" t="str">
-        <f>IF(F300="","",F300-G300)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I300" s="3" t="s">
@@ -15243,9 +15222,9 @@
         <v>100</v>
       </c>
       <c r="D301" s="5"/>
-      <c r="E301" s="21"/>
+      <c r="E301" s="13"/>
       <c r="F301" s="4" t="str">
-        <f>IF(OR(D301="",E301=""),"",D301*E301)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G301" s="4" t="str">
@@ -15253,7 +15232,7 @@
         <v/>
       </c>
       <c r="H301" s="4" t="str">
-        <f>IF(F301="","",F301-G301)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I301" s="3" t="s">
@@ -15269,9 +15248,9 @@
         <v>100</v>
       </c>
       <c r="D302" s="5"/>
-      <c r="E302" s="21"/>
+      <c r="E302" s="13"/>
       <c r="F302" s="4" t="str">
-        <f>IF(OR(D302="",E302=""),"",D302*E302)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G302" s="4" t="str">
@@ -15279,7 +15258,7 @@
         <v/>
       </c>
       <c r="H302" s="4" t="str">
-        <f>IF(F302="","",F302-G302)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I302" s="3" t="s">
@@ -15295,9 +15274,9 @@
         <v>100</v>
       </c>
       <c r="D303" s="5"/>
-      <c r="E303" s="21"/>
+      <c r="E303" s="13"/>
       <c r="F303" s="4" t="str">
-        <f>IF(OR(D303="",E303=""),"",D303*E303)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G303" s="4" t="str">
@@ -15305,7 +15284,7 @@
         <v/>
       </c>
       <c r="H303" s="4" t="str">
-        <f>IF(F303="","",F303-G303)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I303" s="3" t="s">
@@ -15319,10 +15298,10 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="I4:I303">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>I4="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>I4="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15375,16 +15354,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -17829,10 +17808,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G203">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>G4="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>G4="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17884,30 +17863,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="H3" s="11" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="H3" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" spans="1:11" ht="16">
       <c r="A4" s="6" t="s">
@@ -17996,7 +17975,7 @@
       </c>
       <c r="B7" s="4">
         <f>MAX(B5-B6,0)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>31</v>
@@ -18188,7 +18167,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>-64</v>
+        <v>-100</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>31</v>
@@ -18222,14 +18201,14 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
@@ -18319,32 +18298,32 @@
     <mergeCell ref="H3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="B14">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>B14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>B16&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>B16&gt;=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>B18&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>B18&gt;=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>LEFT(B20,2)="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>B20="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>B18&lt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>B18&gt;=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18366,12 +18345,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.25" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="3" spans="1:5" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -18386,7 +18365,7 @@
       <c r="D3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="12" t="s">
         <v>161</v>
       </c>
     </row>
@@ -18403,7 +18382,7 @@
       <c r="D4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="11">
         <f>Parametri!$B$7</f>
         <v>15</v>
       </c>
@@ -18421,7 +18400,7 @@
       <c r="D5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="11">
         <f>Parametri!$B$8</f>
         <v>12</v>
       </c>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17AF042D-F245-A246-A359-A85622947A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4FCC6F-0FA1-CB45-A347-0CABCE924F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,6 @@
     <sheet name="Liste" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="196">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -624,6 +623,12 @@
   </si>
   <si>
     <t>Pagata</t>
+  </si>
+  <si>
+    <t>18/06/2026</t>
+  </si>
+  <si>
+    <t>Ragnoli</t>
   </si>
 </sst>
 </file>
@@ -802,8 +807,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -811,13 +816,13 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1635,7 +1640,7 @@
                   <c:v>275</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2214,7 +2219,7 @@
       <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="15"/>
@@ -2265,15 +2270,15 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>Magazzino_Cassa!B14</f>
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
       <c r="J5" s="18">
         <f>Magazzino_Cassa!B12</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
@@ -2323,11 +2328,11 @@
       <c r="C9" s="15"/>
       <c r="D9" s="18">
         <f>Magazzino_Cassa!B13</f>
-        <v>27.900000000000002</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="21" t="str">
+      <c r="G9" s="19" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>11/15</v>
       </c>
@@ -2355,7 +2360,7 @@
       <c r="L10" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="15"/>
@@ -2363,7 +2368,7 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="15"/>
@@ -2432,7 +2437,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>16</v>
@@ -2445,7 +2450,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>19</v>
@@ -2473,7 +2478,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>19</v>
@@ -2572,7 +2577,7 @@
       </c>
       <c r="B21" s="4">
         <f>Magazzino_Cassa!B18</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>16</v>
@@ -2595,7 +2600,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="16" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="15"/>
@@ -2636,6 +2641,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2643,12 +2654,6 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -3043,7 +3048,7 @@
         <v>192</v>
       </c>
       <c r="J4" s="4">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7728,30 +7733,42 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="8"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="4" t="str">
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13">
+        <v>12</v>
+      </c>
+      <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G13" s="4" t="str">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4">
         <f>IF(D13="","",D13*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H13" s="4" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="H13" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="8"/>
@@ -14166,7 +14183,7 @@
         <v/>
       </c>
       <c r="H260" s="4" t="str">
-        <f t="shared" ref="H260:H323" si="8">IF(F260="","",F260-G260)</f>
+        <f t="shared" ref="H260:H303" si="8">IF(F260="","",F260-G260)</f>
         <v/>
       </c>
       <c r="I260" s="3" t="s">
@@ -14340,7 +14357,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="13"/>
       <c r="F267" s="4" t="str">
-        <f t="shared" ref="F267:F330" si="9">IF(OR(D267="",E267=""),"",D267*E267)</f>
+        <f t="shared" ref="F267:F303" si="9">IF(OR(D267="",E267=""),"",D267*E267)</f>
         <v/>
       </c>
       <c r="G267" s="4" t="str">
@@ -17873,7 +17890,7 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="15"/>
@@ -17881,7 +17898,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="16" t="s">
         <v>107</v>
       </c>
       <c r="I3" s="15"/>
@@ -18083,7 +18100,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
@@ -18107,7 +18124,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>31</v>
@@ -18122,7 +18139,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>27.900000000000002</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>31</v>
@@ -18137,7 +18154,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -18194,14 +18211,14 @@
       </c>
       <c r="B18" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$8)</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="16" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="15"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4FCC6F-0FA1-CB45-A347-0CABCE924F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008F78B6-B93B-8142-AAA6-1108E6D228BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="196">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -622,13 +622,13 @@
     <t>Quota effettiva 25 euro; extra 245 euro registrato come anticipo da rimborsare.</t>
   </si>
   <si>
-    <t>Pagata</t>
-  </si>
-  <si>
     <t>18/06/2026</t>
   </si>
   <si>
     <t>Ragnoli</t>
+  </si>
+  <si>
+    <t>19/06/2026</t>
   </si>
 </sst>
 </file>
@@ -807,8 +807,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -816,13 +816,13 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1637,7 +1637,7 @@
                 <c:formatCode>\€\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>275</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>48</c:v>
@@ -1949,8 +1949,12 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="63"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="62"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="60">
+      <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="59">
+      <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="58"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="57"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="56"/>
@@ -2219,7 +2223,7 @@
       <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="15"/>
@@ -2260,17 +2264,17 @@
     <row r="5" spans="1:12" ht="25.5" customHeight="1">
       <c r="A5" s="18">
         <f>Magazzino_Cassa!B16</f>
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="18">
         <f>Magazzino_Cassa!B6</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="21">
+      <c r="G5" s="19">
         <f>Magazzino_Cassa!B14</f>
         <v>183</v>
       </c>
@@ -2332,9 +2336,9 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="19" t="str">
+      <c r="G9" s="21" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
-        <v>11/15</v>
+        <v>12/15</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -2360,7 +2364,7 @@
       <c r="L10" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="15"/>
@@ -2368,7 +2372,7 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="20" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="15"/>
@@ -2409,7 +2413,7 @@
       </c>
       <c r="B15" s="4">
         <f>Magazzino_Cassa!B6</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -2521,7 +2525,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>29</v>
@@ -2600,7 +2604,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="20" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="15"/>
@@ -2641,12 +2645,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2654,6 +2652,12 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -3066,10 +3070,12 @@
         <v>25</v>
       </c>
       <c r="E5" s="4">
+        <f t="shared" ref="E5:E18" si="0">D5-C5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>193</v>
+      <c r="F5" s="3" t="str">
+        <f t="shared" ref="F5:F18" si="1">IF(D5&gt;=C5,"Pagata",IF(D5&gt;0,"Parziale","Da pagare"))</f>
+        <v>Pagata</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>150</v>
@@ -3091,16 +3097,22 @@
         <v>25</v>
       </c>
       <c r="D6" s="4">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E6" s="4">
-        <v>-25</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="3"/>
+      <c r="F6" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:10">
@@ -3118,10 +3130,12 @@
         <v>25</v>
       </c>
       <c r="E7" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>193</v>
+      <c r="F7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>150</v>
@@ -3146,10 +3160,12 @@
         <v>25</v>
       </c>
       <c r="E8" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>193</v>
+      <c r="F8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>150</v>
@@ -3174,10 +3190,12 @@
         <v>0</v>
       </c>
       <c r="E9" s="4">
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>91</v>
+      <c r="F9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Da pagare</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="3"/>
@@ -3198,10 +3216,12 @@
         <v>25</v>
       </c>
       <c r="E10" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>193</v>
+      <c r="F10" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>150</v>
@@ -3226,10 +3246,12 @@
         <v>0</v>
       </c>
       <c r="E11" s="4">
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>91</v>
+      <c r="F11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Da pagare</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="3"/>
@@ -3250,10 +3272,12 @@
         <v>25</v>
       </c>
       <c r="E12" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>193</v>
+      <c r="F12" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>150</v>
@@ -3278,10 +3302,12 @@
         <v>25</v>
       </c>
       <c r="E13" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>193</v>
+      <c r="F13" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>150</v>
@@ -3306,10 +3332,12 @@
         <v>25</v>
       </c>
       <c r="E14" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>193</v>
+      <c r="F14" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>150</v>
@@ -3334,10 +3362,12 @@
         <v>25</v>
       </c>
       <c r="E15" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>193</v>
+      <c r="F15" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>150</v>
@@ -3362,10 +3392,12 @@
         <v>25</v>
       </c>
       <c r="E16" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>193</v>
+      <c r="F16" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>156</v>
@@ -3390,10 +3422,12 @@
         <v>0</v>
       </c>
       <c r="E17" s="4">
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>91</v>
+      <c r="F17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Da pagare</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="3"/>
@@ -3414,10 +3448,12 @@
         <v>25</v>
       </c>
       <c r="E18" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>193</v>
+      <c r="F18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Pagata</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>156</v>
@@ -7734,10 +7770,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>100</v>
@@ -17890,7 +17926,7 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="20" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="15"/>
@@ -17898,7 +17934,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="20" t="s">
         <v>107</v>
       </c>
       <c r="I3" s="15"/>
@@ -17965,7 +18001,7 @@
       </c>
       <c r="B6" s="4">
         <f>SUM(Persone_Quote!D4:D18)</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>31</v>
@@ -17992,7 +18028,7 @@
       </c>
       <c r="B7" s="4">
         <f>MAX(B5-B6,0)</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>31</v>
@@ -18019,7 +18055,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF(Persone_Quote!F4:F18,"Pagata")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>64</v>
@@ -18184,7 +18220,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>31</v>
@@ -18218,7 +18254,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="20" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="15"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008F78B6-B93B-8142-AAA6-1108E6D228BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3ADC2E-A41E-9E43-A6C9-7BE319F6BF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="199">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -559,9 +559,6 @@
     <t>Prezzo esterni - costo unitario</t>
   </si>
   <si>
-    <t>De Matola</t>
-  </si>
-  <si>
     <t>Mimmo</t>
   </si>
   <si>
@@ -629,6 +626,18 @@
   </si>
   <si>
     <t>19/06/2026</t>
+  </si>
+  <si>
+    <t>Marra</t>
+  </si>
+  <si>
+    <t>22/06/2026</t>
+  </si>
+  <si>
+    <t>Lombardo</t>
+  </si>
+  <si>
+    <t>De Rosa</t>
   </si>
 </sst>
 </file>
@@ -803,26 +812,26 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1640,7 +1649,7 @@
                   <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2207,7 +2216,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="15"/>
@@ -2223,7 +2232,7 @@
       <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="15"/>
@@ -2240,49 +2249,49 @@
     </row>
     <row r="3" spans="1:12" ht="32" customHeight="1"/>
     <row r="4" spans="1:12" ht="20" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="17" t="s">
-        <v>176</v>
+      <c r="J4" s="16" t="s">
+        <v>175</v>
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A5" s="18">
+      <c r="A5" s="17">
         <f>Magazzino_Cassa!B16</f>
         <v>-75</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <f>Magazzino_Cassa!B6</f>
         <v>300</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>Magazzino_Cassa!B14</f>
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="18">
+      <c r="J5" s="17">
         <f>Magazzino_Cassa!B12</f>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
@@ -2302,47 +2311,47 @@
       <c r="L6" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>7</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="16" t="s">
         <v>168</v>
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A9" s="18">
+      <c r="A9" s="17">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <f>Magazzino_Cassa!B13</f>
-        <v>37.200000000000003</v>
+        <v>65.100000000000009</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="21" t="str">
+      <c r="G9" s="18" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>12/15</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="18">
+      <c r="J9" s="17">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
@@ -2364,7 +2373,7 @@
       <c r="L10" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="15"/>
@@ -2372,7 +2381,7 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="14" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="15"/>
@@ -2437,24 +2446,24 @@
     </row>
     <row r="16" spans="1:12" ht="32" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>19</v>
@@ -2482,7 +2491,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>19</v>
@@ -2549,7 +2558,7 @@
     </row>
     <row r="20" spans="1:12" ht="30">
       <c r="A20" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B20" s="4">
         <f>Magazzino_Cassa!B17</f>
@@ -2559,10 +2568,10 @@
         <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H20" s="5">
         <f>Magazzino_Cassa!B24</f>
@@ -2572,25 +2581,25 @@
         <v>19</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="30">
       <c r="A21" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B21" s="4">
         <f>Magazzino_Cassa!B18</f>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H21" s="4">
         <f>Parametri!B12</f>
@@ -2600,11 +2609,11 @@
         <v>31</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="14" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="15"/>
@@ -2645,6 +2654,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2652,12 +2667,6 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2684,7 +2693,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="15"/>
@@ -2745,7 +2754,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1">
@@ -2767,7 +2776,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1">
@@ -2802,7 +2811,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>62</v>
       </c>
       <c r="B1" s="15"/>
@@ -2938,7 +2947,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B12" s="4">
         <f>B8-B6</f>
@@ -2948,7 +2957,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +2985,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="15"/>
@@ -3017,7 +3026,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30">
@@ -3049,10 +3058,10 @@
         <v>128</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J4" s="4">
-        <v>197</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3108,7 +3117,7 @@
         <v>Pagata</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>134</v>
@@ -3514,7 +3523,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="15"/>
@@ -7421,7 +7430,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="15"/>
@@ -7735,7 +7744,7 @@
         <v>156</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>100</v>
@@ -7765,15 +7774,15 @@
         <v>128</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>100</v>
@@ -7803,80 +7812,109 @@
         <v>128</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="8"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="4" t="str">
+      <c r="D14" s="5">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
+        <v>24</v>
+      </c>
+      <c r="G14" s="4">
         <f>IF(D14="","",D14*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
+        <v>5.4</v>
+      </c>
+      <c r="H14" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>18.600000000000001</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="8"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="4" t="str">
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G15" s="4" t="str">
+        <v>12</v>
+      </c>
+      <c r="G15" s="4">
         <f>IF(D15="","",D15*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H15" s="4" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="H15" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="8"/>
-      <c r="B16" s="3"/>
+      <c r="A16" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f>IF(D16="","",D16*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13">
+        <v>12</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>101</v>
@@ -7885,24 +7923,29 @@
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="8"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G17" s="4" t="str">
-        <f>IF(D17="","",D17*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="D17" s="5">
+        <v>2</v>
+      </c>
+      <c r="E17" s="13">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>101</v>
@@ -7911,24 +7954,29 @@
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="8"/>
-      <c r="B18" s="3"/>
+      <c r="A18" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="C18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f>IF(D18="","",D18*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="D18" s="5">
+        <v>2</v>
+      </c>
+      <c r="E18" s="13">
+        <v>12</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>101</v>
@@ -7937,24 +7985,29 @@
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="8"/>
-      <c r="B19" s="3"/>
+      <c r="A19" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="C19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G19" s="4" t="str">
-        <f>IF(D19="","",D19*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H19" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="D19" s="5">
+        <v>2</v>
+      </c>
+      <c r="E19" s="13">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>101</v>
@@ -15407,7 +15460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>102</v>
       </c>
       <c r="B1" s="15"/>
@@ -17916,7 +17969,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>105</v>
       </c>
       <c r="B1" s="15"/>
@@ -17926,7 +17979,7 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="14" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="15"/>
@@ -17934,7 +17987,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="14" t="s">
         <v>107</v>
       </c>
       <c r="I3" s="15"/>
@@ -18136,7 +18189,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
@@ -18156,11 +18209,11 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>31</v>
@@ -18171,11 +18224,11 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>37.200000000000003</v>
+        <v>65.100000000000009</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>31</v>
@@ -18190,7 +18243,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -18231,7 +18284,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B17" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$7)</f>
@@ -18243,18 +18296,18 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B18" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$8)</f>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="14" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="15"/>
@@ -18321,19 +18374,19 @@
     </row>
     <row r="24" spans="1:6" ht="60">
       <c r="A24" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B24" s="5">
         <f>IF(Parametri!B8&gt;0,ROUNDUP(B10/Parametri!B8,0),0)</f>
         <v>45</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" s="4">
         <f>Parametri!B12</f>
@@ -18398,7 +18451,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="15"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3ADC2E-A41E-9E43-A6C9-7BE319F6BF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC16C20-90FC-8B42-81C1-5D6B1DBA82FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="199">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -2285,7 +2285,7 @@
       <c r="F5" s="15"/>
       <c r="G5" s="21">
         <f>Magazzino_Cassa!B14</f>
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>19</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>19</v>
@@ -8016,24 +8016,29 @@
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="8"/>
-      <c r="B20" s="3"/>
+      <c r="A20" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="C20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f>IF(D20="","",D20*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="D20" s="5">
+        <v>2</v>
+      </c>
+      <c r="E20" s="13">
+        <v>12</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>101</v>
@@ -8042,24 +8047,29 @@
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="8"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="C21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G21" s="4" t="str">
-        <f>IF(D21="","",D21*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="D21" s="5">
+        <v>2</v>
+      </c>
+      <c r="E21" s="13">
+        <v>12</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>101</v>
@@ -8068,24 +8078,29 @@
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="8"/>
-      <c r="B22" s="3"/>
+      <c r="A22" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="C22" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f>IF(D22="","",D22*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="D22" s="5">
+        <v>2</v>
+      </c>
+      <c r="E22" s="13">
+        <v>12</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>101</v>
@@ -18189,7 +18204,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
@@ -18243,7 +18258,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC16C20-90FC-8B42-81C1-5D6B1DBA82FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052FC36D-EBD4-BB41-9C91-3AE050D4886B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="201">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -638,6 +638,12 @@
   </si>
   <si>
     <t>De Rosa</t>
+  </si>
+  <si>
+    <t>23/06/2026</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
   </si>
 </sst>
 </file>
@@ -812,26 +818,26 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -991,227 +997,6 @@
           <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1585,6 +1370,227 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1646,7 +1652,7 @@
                 <c:formatCode>\€\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>300</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>84</c:v>
@@ -1952,63 +1958,63 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" headerRowDxfId="67" dataDxfId="66" totalsRowDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" headerRowDxfId="53" dataDxfId="52" totalsRowDxfId="51">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="60">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="46">
       <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="59">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="45">
       <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" headerRowDxfId="55" dataDxfId="54" totalsRowDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" headerRowDxfId="41" dataDxfId="40" totalsRowDxfId="39">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" headerRowDxfId="43" dataDxfId="42" totalsRowDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" headerRowDxfId="67" dataDxfId="66" totalsRowDxfId="65">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="59">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="34">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="58">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="33">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="57">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2216,7 +2222,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="15"/>
@@ -2232,7 +2238,7 @@
       <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="15"/>
@@ -2249,47 +2255,47 @@
     </row>
     <row r="3" spans="1:12" ht="32" customHeight="1"/>
     <row r="4" spans="1:12" ht="20" customHeight="1">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="17" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="17" t="s">
         <v>175</v>
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A5" s="17">
+      <c r="A5" s="18">
         <f>Magazzino_Cassa!B16</f>
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>Magazzino_Cassa!B6</f>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="21">
+      <c r="G5" s="19">
         <f>Magazzino_Cassa!B14</f>
         <v>167</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="17">
+      <c r="J5" s="18">
         <f>Magazzino_Cassa!B12</f>
         <v>84</v>
       </c>
@@ -2311,47 +2317,47 @@
       <c r="L6" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="17" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="17" t="s">
         <v>7</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="17" t="s">
         <v>168</v>
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A9" s="17">
+      <c r="A9" s="18">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>Magazzino_Cassa!B13</f>
         <v>65.100000000000009</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="18" t="str">
+      <c r="G9" s="21" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
-        <v>12/15</v>
+        <v>14/15</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="17">
+      <c r="J9" s="18">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
@@ -2373,7 +2379,7 @@
       <c r="L10" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="15"/>
@@ -2381,7 +2387,7 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="20" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="15"/>
@@ -2422,7 +2428,7 @@
       </c>
       <c r="B15" s="4">
         <f>Magazzino_Cassa!B6</f>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -2534,7 +2540,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>29</v>
@@ -2613,7 +2619,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="20" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="15"/>
@@ -2654,12 +2660,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2667,6 +2667,12 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2693,7 +2699,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="15"/>
@@ -2811,7 +2817,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B1" s="15"/>
@@ -2985,7 +2991,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="15"/>
@@ -3252,18 +3258,22 @@
         <v>25</v>
       </c>
       <c r="D11" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Da pagare</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="3"/>
+        <v>Pagata</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:10">
@@ -3428,18 +3438,22 @@
         <v>25</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Da pagare</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="3"/>
+        <v>Pagata</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9">
@@ -3523,7 +3537,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="15"/>
@@ -7430,7 +7444,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="15"/>
@@ -15475,7 +15489,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>102</v>
       </c>
       <c r="B1" s="15"/>
@@ -17984,7 +17998,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>105</v>
       </c>
       <c r="B1" s="15"/>
@@ -17994,7 +18008,7 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="20" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="15"/>
@@ -18002,7 +18016,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="20" t="s">
         <v>107</v>
       </c>
       <c r="I3" s="15"/>
@@ -18069,7 +18083,7 @@
       </c>
       <c r="B6" s="4">
         <f>SUM(Persone_Quote!D4:D18)</f>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>31</v>
@@ -18096,7 +18110,7 @@
       </c>
       <c r="B7" s="4">
         <f>MAX(B5-B6,0)</f>
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>31</v>
@@ -18123,7 +18137,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF(Persone_Quote!F4:F18,"Pagata")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>64</v>
@@ -18288,7 +18302,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>31</v>
@@ -18322,7 +18336,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="20" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="15"/>
@@ -18466,7 +18480,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="15"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052FC36D-EBD4-BB41-9C91-3AE050D4886B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE904600-5148-8840-9508-7FF2B4AF0134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="206">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -559,9 +559,6 @@
     <t>Prezzo esterni - costo unitario</t>
   </si>
   <si>
-    <t>Mimmo</t>
-  </si>
-  <si>
     <t>Margine unitario patch Interni</t>
   </si>
   <si>
@@ -644,6 +641,24 @@
   </si>
   <si>
     <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
+  </si>
+  <si>
+    <t>Faustino</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>Caprara</t>
+  </si>
+  <si>
+    <t>Dati a Mimmo</t>
+  </si>
+  <si>
+    <t>Scalati, ma da dare a mimmo</t>
   </si>
 </sst>
 </file>
@@ -818,26 +833,26 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -997,6 +1012,227 @@
           <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1370,227 +1606,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1652,10 +1667,10 @@
                 <c:formatCode>\€\ #,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>350</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>84</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -1958,63 +1973,63 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" headerRowDxfId="53" dataDxfId="52" totalsRowDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" headerRowDxfId="67" dataDxfId="66" totalsRowDxfId="65">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="60">
       <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="45">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="59">
       <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" headerRowDxfId="41" dataDxfId="40" totalsRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" headerRowDxfId="55" dataDxfId="54" totalsRowDxfId="53">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" headerRowDxfId="67" dataDxfId="66" totalsRowDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" headerRowDxfId="43" dataDxfId="42" totalsRowDxfId="41">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="59">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="35">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="58">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="34">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="57">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="33">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2222,7 +2237,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="15"/>
@@ -2238,7 +2253,7 @@
       <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="15"/>
@@ -2255,49 +2270,49 @@
     </row>
     <row r="3" spans="1:12" ht="32" customHeight="1"/>
     <row r="4" spans="1:12" ht="20" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="17" t="s">
-        <v>175</v>
+      <c r="J4" s="16" t="s">
+        <v>174</v>
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A5" s="18">
+      <c r="A5" s="17">
         <f>Magazzino_Cassa!B16</f>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <f>Magazzino_Cassa!B6</f>
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>Magazzino_Cassa!B14</f>
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="18">
+      <c r="J5" s="17">
         <f>Magazzino_Cassa!B12</f>
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
@@ -2317,47 +2332,47 @@
       <c r="L6" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>7</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="16" t="s">
         <v>168</v>
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A9" s="18">
+      <c r="A9" s="17">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <f>Magazzino_Cassa!B13</f>
-        <v>65.100000000000009</v>
+        <v>132.90000000000003</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="21" t="str">
+      <c r="G9" s="18" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
-        <v>14/15</v>
+        <v>15/15</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="18">
+      <c r="J9" s="17">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
@@ -2379,7 +2394,7 @@
       <c r="L10" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="15"/>
@@ -2387,7 +2402,7 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="14" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="15"/>
@@ -2428,7 +2443,7 @@
       </c>
       <c r="B15" s="4">
         <f>Magazzino_Cassa!B6</f>
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -2452,24 +2467,24 @@
     </row>
     <row r="16" spans="1:12" ht="32" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>19</v>
@@ -2497,7 +2512,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>19</v>
@@ -2540,7 +2555,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>29</v>
@@ -2564,20 +2579,20 @@
     </row>
     <row r="20" spans="1:12" ht="30">
       <c r="A20" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B20" s="4">
         <f>Magazzino_Cassa!B17</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H20" s="5">
         <f>Magazzino_Cassa!B24</f>
@@ -2587,25 +2602,25 @@
         <v>19</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="30">
       <c r="A21" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B21" s="4">
         <f>Magazzino_Cassa!B18</f>
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H21" s="4">
         <f>Parametri!B12</f>
@@ -2615,11 +2630,11 @@
         <v>31</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="14" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="15"/>
@@ -2660,6 +2675,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2667,12 +2688,6 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2699,7 +2714,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="15"/>
@@ -2760,7 +2775,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1">
@@ -2782,7 +2797,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1">
@@ -2817,7 +2832,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>62</v>
       </c>
       <c r="B1" s="15"/>
@@ -2953,7 +2968,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" s="4">
         <f>B8-B6</f>
@@ -2963,7 +2978,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2991,7 +3006,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="15"/>
@@ -3032,7 +3047,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30">
@@ -3064,10 +3079,10 @@
         <v>128</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J4" s="4">
-        <v>161</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3123,7 +3138,7 @@
         <v>Pagata</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>134</v>
@@ -3202,18 +3217,22 @@
         <v>25</v>
       </c>
       <c r="D9" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Da pagare</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="3"/>
+        <v>Pagata</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:10">
@@ -3269,7 +3288,7 @@
         <v>Pagata</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>134</v>
@@ -3449,7 +3468,7 @@
         <v>Pagata</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>134</v>
@@ -3537,7 +3556,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="15"/>
@@ -7444,7 +7463,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="15"/>
@@ -7751,14 +7770,16 @@
       <c r="J11" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="8" t="s">
         <v>156</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>100</v>
@@ -7788,15 +7809,15 @@
         <v>128</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>100</v>
@@ -7826,15 +7847,15 @@
         <v>128</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>100</v>
@@ -7864,15 +7885,15 @@
         <v>128</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>100</v>
@@ -7902,15 +7923,15 @@
         <v>158</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>100</v>
@@ -7938,7 +7959,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>139</v>
@@ -7969,7 +7990,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>137</v>
@@ -8000,7 +8021,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>142</v>
@@ -8031,7 +8052,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>148</v>
@@ -8062,7 +8083,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>149</v>
@@ -8093,7 +8114,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>145</v>
@@ -8123,102 +8144,144 @@
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="8"/>
-      <c r="B23" s="3"/>
+      <c r="A23" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="C23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="4" t="str">
+      <c r="D23" s="5">
+        <v>2</v>
+      </c>
+      <c r="E23" s="13">
+        <v>12</v>
+      </c>
+      <c r="F23" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G23" s="4" t="str">
+        <v>24</v>
+      </c>
+      <c r="G23" s="4">
         <f>IF(D23="","",D23*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H23" s="4" t="str">
+        <v>5.4</v>
+      </c>
+      <c r="H23" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>18.600000000000001</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="8"/>
-      <c r="B24" s="3"/>
+      <c r="A24" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="C24" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="4" t="str">
+      <c r="D24" s="5">
+        <v>3</v>
+      </c>
+      <c r="E24" s="13">
+        <v>15</v>
+      </c>
+      <c r="F24" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="G24" s="4">
         <f>IF(D24="","",D24*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="H24" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>36.9</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="8"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="C25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="4" t="str">
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13">
+        <v>15</v>
+      </c>
+      <c r="F25" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G25" s="4" t="str">
+        <v>15</v>
+      </c>
+      <c r="G25" s="4">
         <f>IF(D25="","",D25*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H25" s="4" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="H25" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>12.3</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="8"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="C26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f>IF(D26="","",D26*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
+      <c r="D26" s="5">
+        <v>2</v>
+      </c>
+      <c r="E26" s="13">
+        <v>12</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>101</v>
@@ -15489,7 +15552,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>102</v>
       </c>
       <c r="B1" s="15"/>
@@ -17998,7 +18061,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>105</v>
       </c>
       <c r="B1" s="15"/>
@@ -18008,7 +18071,7 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="14" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="15"/>
@@ -18016,7 +18079,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="14" t="s">
         <v>107</v>
       </c>
       <c r="I3" s="15"/>
@@ -18083,7 +18146,7 @@
       </c>
       <c r="B6" s="4">
         <f>SUM(Persone_Quote!D4:D18)</f>
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>31</v>
@@ -18110,7 +18173,7 @@
       </c>
       <c r="B7" s="4">
         <f>MAX(B5-B6,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>31</v>
@@ -18137,7 +18200,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF(Persone_Quote!F4:F18,"Pagata")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>64</v>
@@ -18218,7 +18281,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
@@ -18238,11 +18301,11 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>31</v>
@@ -18253,11 +18316,11 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>65.100000000000009</v>
+        <v>132.90000000000003</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>31</v>
@@ -18272,7 +18335,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -18302,7 +18365,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>31</v>
@@ -18313,11 +18376,11 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B17" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$7)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>31</v>
@@ -18325,18 +18388,18 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B18" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$8)</f>
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="14" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="15"/>
@@ -18403,19 +18466,19 @@
     </row>
     <row r="24" spans="1:6" ht="60">
       <c r="A24" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" s="5">
         <f>IF(Parametri!B8&gt;0,ROUNDUP(B10/Parametri!B8,0),0)</f>
         <v>45</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B25" s="4">
         <f>Parametri!B12</f>
@@ -18480,7 +18543,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="15"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE904600-5148-8840-9508-7FF2B4AF0134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFA5960-CAB3-FB45-A44C-5D4B96DC7A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -646,9 +646,6 @@
     <t>30/06/2026</t>
   </si>
   <si>
-    <t>Faustino</t>
-  </si>
-  <si>
     <t>Jimmy</t>
   </si>
   <si>
@@ -659,6 +656,9 @@
   </si>
   <si>
     <t>Scalati, ma da dare a mimmo</t>
+  </si>
+  <si>
+    <t>Rivellino</t>
   </si>
 </sst>
 </file>
@@ -7771,7 +7771,7 @@
         <v>158</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -7809,7 +7809,7 @@
         <v>128</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -7847,7 +7847,7 @@
         <v>128</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -7885,7 +7885,7 @@
         <v>128</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -7923,7 +7923,7 @@
         <v>158</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8148,7 +8148,7 @@
         <v>200</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>100</v>
@@ -8178,7 +8178,7 @@
         <v>134</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -8186,7 +8186,7 @@
         <v>200</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>100</v>
@@ -8216,7 +8216,7 @@
         <v>128</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -8224,7 +8224,7 @@
         <v>200</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>100</v>
@@ -8254,7 +8254,7 @@
         <v>128</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:11">

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFA5960-CAB3-FB45-A44C-5D4B96DC7A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60882843-AC4E-9244-9711-1DDC5CBC9C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="208">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -655,10 +655,16 @@
     <t>Dati a Mimmo</t>
   </si>
   <si>
-    <t>Scalati, ma da dare a mimmo</t>
-  </si>
-  <si>
     <t>Rivellino</t>
+  </si>
+  <si>
+    <t>03/07/2026</t>
+  </si>
+  <si>
+    <t>Radunista</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
   </si>
 </sst>
 </file>
@@ -798,7 +804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -833,27 +839,30 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1012,227 +1021,6 @@
           <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1606,6 +1394,227 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1670,7 +1679,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>168</c:v>
+                  <c:v>278</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -1973,63 +1982,63 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" headerRowDxfId="67" dataDxfId="66" totalsRowDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" headerRowDxfId="53" dataDxfId="52" totalsRowDxfId="51">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="60">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="46">
       <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="59">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="45">
       <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" headerRowDxfId="55" dataDxfId="54" totalsRowDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" headerRowDxfId="41" dataDxfId="40" totalsRowDxfId="39">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" headerRowDxfId="43" dataDxfId="42" totalsRowDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" headerRowDxfId="67" dataDxfId="66" totalsRowDxfId="65">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="59">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="34">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="58">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="33">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="57">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2237,7 +2246,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="15"/>
@@ -2253,7 +2262,7 @@
       <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="15"/>
@@ -2270,49 +2279,49 @@
     </row>
     <row r="3" spans="1:12" ht="32" customHeight="1"/>
     <row r="4" spans="1:12" ht="20" customHeight="1">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="17" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="17" t="s">
         <v>174</v>
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A5" s="17">
+      <c r="A5" s="18">
         <f>Magazzino_Cassa!B16</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>Magazzino_Cassa!B6</f>
         <v>375</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="21">
+      <c r="G5" s="19">
         <f>Magazzino_Cassa!B14</f>
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="17">
+      <c r="J5" s="18">
         <f>Magazzino_Cassa!B12</f>
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
@@ -2332,47 +2341,47 @@
       <c r="L6" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="17" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="17" t="s">
         <v>7</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="17" t="s">
         <v>168</v>
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A9" s="17">
+      <c r="A9" s="18">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>Magazzino_Cassa!B13</f>
-        <v>132.90000000000003</v>
+        <v>224.00000000000006</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="18" t="str">
+      <c r="G9" s="21" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="17">
+      <c r="J9" s="18">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
@@ -2394,7 +2403,7 @@
       <c r="L10" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="15"/>
@@ -2402,7 +2411,7 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="20" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="15"/>
@@ -2471,7 +2480,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>16</v>
@@ -2484,7 +2493,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>19</v>
@@ -2512,7 +2521,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>19</v>
@@ -2555,7 +2564,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>29</v>
@@ -2583,7 +2592,7 @@
       </c>
       <c r="B20" s="4">
         <f>Magazzino_Cassa!B17</f>
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>16</v>
@@ -2634,7 +2643,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="20" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="15"/>
@@ -2675,12 +2684,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2688,6 +2691,12 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2714,7 +2723,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="15"/>
@@ -2832,7 +2841,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B1" s="15"/>
@@ -3006,7 +3015,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="15"/>
@@ -3082,7 +3091,7 @@
         <v>190</v>
       </c>
       <c r="J4" s="4">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3556,7 +3565,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="15"/>
@@ -7463,7 +7472,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="15"/>
@@ -8148,7 +8157,7 @@
         <v>200</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>100</v>
@@ -8178,7 +8187,7 @@
         <v>134</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -8290,85 +8299,120 @@
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="8"/>
-      <c r="B27" s="3"/>
+      <c r="A27" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="4" t="str">
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13">
+        <v>15</v>
+      </c>
+      <c r="F27" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G27" s="4" t="str">
+        <v>15</v>
+      </c>
+      <c r="G27" s="4">
         <f>IF(D27="","",D27*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H27" s="4" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="H27" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>12.3</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="8"/>
-      <c r="B28" s="3"/>
+      <c r="A28" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="C28" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="4" t="str">
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13">
+        <v>15</v>
+      </c>
+      <c r="F28" s="4">
+        <v>20</v>
+      </c>
+      <c r="G28" s="4">
+        <f>IF(D28="","",D28*Parametri!$B$6)</f>
+        <v>2.7</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="0"/>
+        <v>17.3</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="5">
+        <v>5</v>
+      </c>
+      <c r="E29" s="13">
+        <v>15</v>
+      </c>
+      <c r="F29" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f>IF(D28="","",D28*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
+        <v>75</v>
+      </c>
+      <c r="G29" s="4">
+        <f>IF(D29="","",D29*Parametri!$B$6)</f>
+        <v>13.5</v>
+      </c>
+      <c r="H29" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="8"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G29" s="4" t="str">
-        <f>IF(D29="","",D29*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>61.5</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="8"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
         <v>100</v>
@@ -8394,7 +8438,7 @@
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="8"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
         <v>100</v>
@@ -8420,7 +8464,7 @@
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="8"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
         <v>100</v>
@@ -8446,7 +8490,7 @@
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="8"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
         <v>100</v>
@@ -8472,7 +8516,7 @@
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="8"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
         <v>100</v>
@@ -8498,7 +8542,7 @@
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="8"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
         <v>100</v>
@@ -8524,7 +8568,7 @@
       <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="8"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
         <v>100</v>
@@ -8550,7 +8594,7 @@
       <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="8"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
         <v>100</v>
@@ -8576,7 +8620,7 @@
       <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="8"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
         <v>100</v>
@@ -8602,7 +8646,7 @@
       <c r="K38" s="3"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="8"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
         <v>100</v>
@@ -8628,7 +8672,7 @@
       <c r="K39" s="3"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="8"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
         <v>100</v>
@@ -8654,7 +8698,7 @@
       <c r="K40" s="3"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="8"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
         <v>100</v>
@@ -8680,7 +8724,7 @@
       <c r="K41" s="3"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="8"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3" t="s">
         <v>100</v>
@@ -8706,7 +8750,7 @@
       <c r="K42" s="3"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="8"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3" t="s">
         <v>100</v>
@@ -8732,7 +8776,7 @@
       <c r="K43" s="3"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="8"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
         <v>100</v>
@@ -8758,7 +8802,7 @@
       <c r="K44" s="3"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="8"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
         <v>100</v>
@@ -8784,7 +8828,7 @@
       <c r="K45" s="3"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="8"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
         <v>100</v>
@@ -8810,7 +8854,7 @@
       <c r="K46" s="3"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="8"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
         <v>100</v>
@@ -8836,7 +8880,7 @@
       <c r="K47" s="3"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="8"/>
+      <c r="A48" s="22"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
         <v>100</v>
@@ -8862,7 +8906,7 @@
       <c r="K48" s="3"/>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="8"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
         <v>100</v>
@@ -8888,7 +8932,7 @@
       <c r="K49" s="3"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="8"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
         <v>100</v>
@@ -8914,7 +8958,7 @@
       <c r="K50" s="3"/>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="8"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
         <v>100</v>
@@ -8940,7 +8984,7 @@
       <c r="K51" s="3"/>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="8"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
         <v>100</v>
@@ -8966,7 +9010,7 @@
       <c r="K52" s="3"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="8"/>
+      <c r="A53" s="22"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
         <v>100</v>
@@ -8992,7 +9036,7 @@
       <c r="K53" s="3"/>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="8"/>
+      <c r="A54" s="22"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
         <v>100</v>
@@ -9018,7 +9062,7 @@
       <c r="K54" s="3"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="8"/>
+      <c r="A55" s="22"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
         <v>100</v>
@@ -9044,7 +9088,7 @@
       <c r="K55" s="3"/>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="8"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
         <v>100</v>
@@ -9070,7 +9114,7 @@
       <c r="K56" s="3"/>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="8"/>
+      <c r="A57" s="22"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3" t="s">
         <v>100</v>
@@ -9096,7 +9140,7 @@
       <c r="K57" s="3"/>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="8"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
         <v>100</v>
@@ -9122,7 +9166,7 @@
       <c r="K58" s="3"/>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="8"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
         <v>100</v>
@@ -9148,7 +9192,7 @@
       <c r="K59" s="3"/>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" s="8"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
         <v>100</v>
@@ -9174,7 +9218,7 @@
       <c r="K60" s="3"/>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="8"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
         <v>100</v>
@@ -9200,7 +9244,7 @@
       <c r="K61" s="3"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="8"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3" t="s">
         <v>100</v>
@@ -9226,7 +9270,7 @@
       <c r="K62" s="3"/>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="8"/>
+      <c r="A63" s="22"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
         <v>100</v>
@@ -9252,7 +9296,7 @@
       <c r="K63" s="3"/>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="8"/>
+      <c r="A64" s="22"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
         <v>100</v>
@@ -9278,7 +9322,7 @@
       <c r="K64" s="3"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="8"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
         <v>100</v>
@@ -9304,7 +9348,7 @@
       <c r="K65" s="3"/>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="8"/>
+      <c r="A66" s="22"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
         <v>100</v>
@@ -9330,7 +9374,7 @@
       <c r="K66" s="3"/>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="8"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
         <v>100</v>
@@ -9356,7 +9400,7 @@
       <c r="K67" s="3"/>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="8"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3" t="s">
         <v>100</v>
@@ -9382,7 +9426,7 @@
       <c r="K68" s="3"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="8"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3" t="s">
         <v>100</v>
@@ -9408,7 +9452,7 @@
       <c r="K69" s="3"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="8"/>
+      <c r="A70" s="22"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3" t="s">
         <v>100</v>
@@ -9434,7 +9478,7 @@
       <c r="K70" s="3"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="8"/>
+      <c r="A71" s="22"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3" t="s">
         <v>100</v>
@@ -9460,7 +9504,7 @@
       <c r="K71" s="3"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="8"/>
+      <c r="A72" s="22"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3" t="s">
         <v>100</v>
@@ -9486,7 +9530,7 @@
       <c r="K72" s="3"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="8"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3" t="s">
         <v>100</v>
@@ -9512,7 +9556,7 @@
       <c r="K73" s="3"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="8"/>
+      <c r="A74" s="22"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
         <v>100</v>
@@ -9538,7 +9582,7 @@
       <c r="K74" s="3"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="8"/>
+      <c r="A75" s="22"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
         <v>100</v>
@@ -9564,7 +9608,7 @@
       <c r="K75" s="3"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="8"/>
+      <c r="A76" s="22"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3" t="s">
         <v>100</v>
@@ -9590,7 +9634,7 @@
       <c r="K76" s="3"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="8"/>
+      <c r="A77" s="22"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3" t="s">
         <v>100</v>
@@ -9616,7 +9660,7 @@
       <c r="K77" s="3"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="8"/>
+      <c r="A78" s="22"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
         <v>100</v>
@@ -9642,7 +9686,7 @@
       <c r="K78" s="3"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="8"/>
+      <c r="A79" s="22"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3" t="s">
         <v>100</v>
@@ -9668,7 +9712,7 @@
       <c r="K79" s="3"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="8"/>
+      <c r="A80" s="22"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3" t="s">
         <v>100</v>
@@ -9694,7 +9738,7 @@
       <c r="K80" s="3"/>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="8"/>
+      <c r="A81" s="22"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3" t="s">
         <v>100</v>
@@ -9720,7 +9764,7 @@
       <c r="K81" s="3"/>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="8"/>
+      <c r="A82" s="22"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3" t="s">
         <v>100</v>
@@ -9746,7 +9790,7 @@
       <c r="K82" s="3"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="8"/>
+      <c r="A83" s="22"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3" t="s">
         <v>100</v>
@@ -9772,7 +9816,7 @@
       <c r="K83" s="3"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="8"/>
+      <c r="A84" s="22"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3" t="s">
         <v>100</v>
@@ -9798,7 +9842,7 @@
       <c r="K84" s="3"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="8"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
         <v>100</v>
@@ -9824,7 +9868,7 @@
       <c r="K85" s="3"/>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="8"/>
+      <c r="A86" s="22"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
         <v>100</v>
@@ -9850,7 +9894,7 @@
       <c r="K86" s="3"/>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="8"/>
+      <c r="A87" s="22"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3" t="s">
         <v>100</v>
@@ -9876,7 +9920,7 @@
       <c r="K87" s="3"/>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="8"/>
+      <c r="A88" s="22"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3" t="s">
         <v>100</v>
@@ -9902,7 +9946,7 @@
       <c r="K88" s="3"/>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="8"/>
+      <c r="A89" s="22"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3" t="s">
         <v>100</v>
@@ -9928,7 +9972,7 @@
       <c r="K89" s="3"/>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="8"/>
+      <c r="A90" s="22"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3" t="s">
         <v>100</v>
@@ -9954,7 +9998,7 @@
       <c r="K90" s="3"/>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="8"/>
+      <c r="A91" s="22"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3" t="s">
         <v>100</v>
@@ -9980,7 +10024,7 @@
       <c r="K91" s="3"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="8"/>
+      <c r="A92" s="22"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3" t="s">
         <v>100</v>
@@ -10006,7 +10050,7 @@
       <c r="K92" s="3"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="8"/>
+      <c r="A93" s="22"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3" t="s">
         <v>100</v>
@@ -10032,7 +10076,7 @@
       <c r="K93" s="3"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="8"/>
+      <c r="A94" s="22"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3" t="s">
         <v>100</v>
@@ -10058,7 +10102,7 @@
       <c r="K94" s="3"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="8"/>
+      <c r="A95" s="22"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3" t="s">
         <v>100</v>
@@ -10084,7 +10128,7 @@
       <c r="K95" s="3"/>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" s="8"/>
+      <c r="A96" s="22"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3" t="s">
         <v>100</v>
@@ -10110,7 +10154,7 @@
       <c r="K96" s="3"/>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" s="8"/>
+      <c r="A97" s="22"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
         <v>100</v>
@@ -10136,7 +10180,7 @@
       <c r="K97" s="3"/>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" s="8"/>
+      <c r="A98" s="22"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3" t="s">
         <v>100</v>
@@ -10162,7 +10206,7 @@
       <c r="K98" s="3"/>
     </row>
     <row r="99" spans="1:11">
-      <c r="A99" s="8"/>
+      <c r="A99" s="22"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3" t="s">
         <v>100</v>
@@ -10188,7 +10232,7 @@
       <c r="K99" s="3"/>
     </row>
     <row r="100" spans="1:11">
-      <c r="A100" s="8"/>
+      <c r="A100" s="22"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3" t="s">
         <v>100</v>
@@ -10214,7 +10258,7 @@
       <c r="K100" s="3"/>
     </row>
     <row r="101" spans="1:11">
-      <c r="A101" s="8"/>
+      <c r="A101" s="22"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3" t="s">
         <v>100</v>
@@ -10240,7 +10284,7 @@
       <c r="K101" s="3"/>
     </row>
     <row r="102" spans="1:11">
-      <c r="A102" s="8"/>
+      <c r="A102" s="22"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
         <v>100</v>
@@ -10266,7 +10310,7 @@
       <c r="K102" s="3"/>
     </row>
     <row r="103" spans="1:11">
-      <c r="A103" s="8"/>
+      <c r="A103" s="22"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3" t="s">
         <v>100</v>
@@ -10292,7 +10336,7 @@
       <c r="K103" s="3"/>
     </row>
     <row r="104" spans="1:11">
-      <c r="A104" s="8"/>
+      <c r="A104" s="22"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3" t="s">
         <v>100</v>
@@ -10318,7 +10362,7 @@
       <c r="K104" s="3"/>
     </row>
     <row r="105" spans="1:11">
-      <c r="A105" s="8"/>
+      <c r="A105" s="22"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3" t="s">
         <v>100</v>
@@ -10344,7 +10388,7 @@
       <c r="K105" s="3"/>
     </row>
     <row r="106" spans="1:11">
-      <c r="A106" s="8"/>
+      <c r="A106" s="22"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
         <v>100</v>
@@ -10370,7 +10414,7 @@
       <c r="K106" s="3"/>
     </row>
     <row r="107" spans="1:11">
-      <c r="A107" s="8"/>
+      <c r="A107" s="22"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3" t="s">
         <v>100</v>
@@ -10396,7 +10440,7 @@
       <c r="K107" s="3"/>
     </row>
     <row r="108" spans="1:11">
-      <c r="A108" s="8"/>
+      <c r="A108" s="22"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3" t="s">
         <v>100</v>
@@ -10422,7 +10466,7 @@
       <c r="K108" s="3"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="8"/>
+      <c r="A109" s="22"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3" t="s">
         <v>100</v>
@@ -10448,7 +10492,7 @@
       <c r="K109" s="3"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="8"/>
+      <c r="A110" s="22"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3" t="s">
         <v>100</v>
@@ -10474,7 +10518,7 @@
       <c r="K110" s="3"/>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" s="8"/>
+      <c r="A111" s="22"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3" t="s">
         <v>100</v>
@@ -10500,7 +10544,7 @@
       <c r="K111" s="3"/>
     </row>
     <row r="112" spans="1:11">
-      <c r="A112" s="8"/>
+      <c r="A112" s="22"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3" t="s">
         <v>100</v>
@@ -10526,7 +10570,7 @@
       <c r="K112" s="3"/>
     </row>
     <row r="113" spans="1:11">
-      <c r="A113" s="8"/>
+      <c r="A113" s="22"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3" t="s">
         <v>100</v>
@@ -10552,7 +10596,7 @@
       <c r="K113" s="3"/>
     </row>
     <row r="114" spans="1:11">
-      <c r="A114" s="8"/>
+      <c r="A114" s="22"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3" t="s">
         <v>100</v>
@@ -10578,7 +10622,7 @@
       <c r="K114" s="3"/>
     </row>
     <row r="115" spans="1:11">
-      <c r="A115" s="8"/>
+      <c r="A115" s="22"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3" t="s">
         <v>100</v>
@@ -10604,7 +10648,7 @@
       <c r="K115" s="3"/>
     </row>
     <row r="116" spans="1:11">
-      <c r="A116" s="8"/>
+      <c r="A116" s="22"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3" t="s">
         <v>100</v>
@@ -10630,7 +10674,7 @@
       <c r="K116" s="3"/>
     </row>
     <row r="117" spans="1:11">
-      <c r="A117" s="8"/>
+      <c r="A117" s="22"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3" t="s">
         <v>100</v>
@@ -10656,7 +10700,7 @@
       <c r="K117" s="3"/>
     </row>
     <row r="118" spans="1:11">
-      <c r="A118" s="8"/>
+      <c r="A118" s="22"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3" t="s">
         <v>100</v>
@@ -10682,7 +10726,7 @@
       <c r="K118" s="3"/>
     </row>
     <row r="119" spans="1:11">
-      <c r="A119" s="8"/>
+      <c r="A119" s="22"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3" t="s">
         <v>100</v>
@@ -10708,7 +10752,7 @@
       <c r="K119" s="3"/>
     </row>
     <row r="120" spans="1:11">
-      <c r="A120" s="8"/>
+      <c r="A120" s="22"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3" t="s">
         <v>100</v>
@@ -10734,7 +10778,7 @@
       <c r="K120" s="3"/>
     </row>
     <row r="121" spans="1:11">
-      <c r="A121" s="8"/>
+      <c r="A121" s="22"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3" t="s">
         <v>100</v>
@@ -10760,7 +10804,7 @@
       <c r="K121" s="3"/>
     </row>
     <row r="122" spans="1:11">
-      <c r="A122" s="8"/>
+      <c r="A122" s="22"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3" t="s">
         <v>100</v>
@@ -10786,7 +10830,7 @@
       <c r="K122" s="3"/>
     </row>
     <row r="123" spans="1:11">
-      <c r="A123" s="8"/>
+      <c r="A123" s="22"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3" t="s">
         <v>100</v>
@@ -10812,7 +10856,7 @@
       <c r="K123" s="3"/>
     </row>
     <row r="124" spans="1:11">
-      <c r="A124" s="8"/>
+      <c r="A124" s="22"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3" t="s">
         <v>100</v>
@@ -10838,7 +10882,7 @@
       <c r="K124" s="3"/>
     </row>
     <row r="125" spans="1:11">
-      <c r="A125" s="8"/>
+      <c r="A125" s="22"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3" t="s">
         <v>100</v>
@@ -10864,7 +10908,7 @@
       <c r="K125" s="3"/>
     </row>
     <row r="126" spans="1:11">
-      <c r="A126" s="8"/>
+      <c r="A126" s="22"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3" t="s">
         <v>100</v>
@@ -10890,7 +10934,7 @@
       <c r="K126" s="3"/>
     </row>
     <row r="127" spans="1:11">
-      <c r="A127" s="8"/>
+      <c r="A127" s="22"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3" t="s">
         <v>100</v>
@@ -10916,7 +10960,7 @@
       <c r="K127" s="3"/>
     </row>
     <row r="128" spans="1:11">
-      <c r="A128" s="8"/>
+      <c r="A128" s="22"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3" t="s">
         <v>100</v>
@@ -10942,7 +10986,7 @@
       <c r="K128" s="3"/>
     </row>
     <row r="129" spans="1:11">
-      <c r="A129" s="8"/>
+      <c r="A129" s="22"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3" t="s">
         <v>100</v>
@@ -10968,7 +11012,7 @@
       <c r="K129" s="3"/>
     </row>
     <row r="130" spans="1:11">
-      <c r="A130" s="8"/>
+      <c r="A130" s="22"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3" t="s">
         <v>100</v>
@@ -10994,7 +11038,7 @@
       <c r="K130" s="3"/>
     </row>
     <row r="131" spans="1:11">
-      <c r="A131" s="8"/>
+      <c r="A131" s="22"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3" t="s">
         <v>100</v>
@@ -11020,7 +11064,7 @@
       <c r="K131" s="3"/>
     </row>
     <row r="132" spans="1:11">
-      <c r="A132" s="8"/>
+      <c r="A132" s="22"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
         <v>100</v>
@@ -11046,7 +11090,7 @@
       <c r="K132" s="3"/>
     </row>
     <row r="133" spans="1:11">
-      <c r="A133" s="8"/>
+      <c r="A133" s="22"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
         <v>100</v>
@@ -11072,7 +11116,7 @@
       <c r="K133" s="3"/>
     </row>
     <row r="134" spans="1:11">
-      <c r="A134" s="8"/>
+      <c r="A134" s="22"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
         <v>100</v>
@@ -11098,7 +11142,7 @@
       <c r="K134" s="3"/>
     </row>
     <row r="135" spans="1:11">
-      <c r="A135" s="8"/>
+      <c r="A135" s="22"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
         <v>100</v>
@@ -11124,7 +11168,7 @@
       <c r="K135" s="3"/>
     </row>
     <row r="136" spans="1:11">
-      <c r="A136" s="8"/>
+      <c r="A136" s="22"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
         <v>100</v>
@@ -11150,7 +11194,7 @@
       <c r="K136" s="3"/>
     </row>
     <row r="137" spans="1:11">
-      <c r="A137" s="8"/>
+      <c r="A137" s="22"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3" t="s">
         <v>100</v>
@@ -11176,7 +11220,7 @@
       <c r="K137" s="3"/>
     </row>
     <row r="138" spans="1:11">
-      <c r="A138" s="8"/>
+      <c r="A138" s="22"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
         <v>100</v>
@@ -11202,7 +11246,7 @@
       <c r="K138" s="3"/>
     </row>
     <row r="139" spans="1:11">
-      <c r="A139" s="8"/>
+      <c r="A139" s="22"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
         <v>100</v>
@@ -11228,7 +11272,7 @@
       <c r="K139" s="3"/>
     </row>
     <row r="140" spans="1:11">
-      <c r="A140" s="8"/>
+      <c r="A140" s="22"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3" t="s">
         <v>100</v>
@@ -11254,7 +11298,7 @@
       <c r="K140" s="3"/>
     </row>
     <row r="141" spans="1:11">
-      <c r="A141" s="8"/>
+      <c r="A141" s="22"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
         <v>100</v>
@@ -11280,7 +11324,7 @@
       <c r="K141" s="3"/>
     </row>
     <row r="142" spans="1:11">
-      <c r="A142" s="8"/>
+      <c r="A142" s="22"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
         <v>100</v>
@@ -11306,7 +11350,7 @@
       <c r="K142" s="3"/>
     </row>
     <row r="143" spans="1:11">
-      <c r="A143" s="8"/>
+      <c r="A143" s="22"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3" t="s">
         <v>100</v>
@@ -11332,7 +11376,7 @@
       <c r="K143" s="3"/>
     </row>
     <row r="144" spans="1:11">
-      <c r="A144" s="8"/>
+      <c r="A144" s="22"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3" t="s">
         <v>100</v>
@@ -11358,7 +11402,7 @@
       <c r="K144" s="3"/>
     </row>
     <row r="145" spans="1:11">
-      <c r="A145" s="8"/>
+      <c r="A145" s="22"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3" t="s">
         <v>100</v>
@@ -11384,7 +11428,7 @@
       <c r="K145" s="3"/>
     </row>
     <row r="146" spans="1:11">
-      <c r="A146" s="8"/>
+      <c r="A146" s="22"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3" t="s">
         <v>100</v>
@@ -11410,7 +11454,7 @@
       <c r="K146" s="3"/>
     </row>
     <row r="147" spans="1:11">
-      <c r="A147" s="8"/>
+      <c r="A147" s="22"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3" t="s">
         <v>100</v>
@@ -11436,7 +11480,7 @@
       <c r="K147" s="3"/>
     </row>
     <row r="148" spans="1:11">
-      <c r="A148" s="8"/>
+      <c r="A148" s="22"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3" t="s">
         <v>100</v>
@@ -11462,7 +11506,7 @@
       <c r="K148" s="3"/>
     </row>
     <row r="149" spans="1:11">
-      <c r="A149" s="8"/>
+      <c r="A149" s="22"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3" t="s">
         <v>100</v>
@@ -11488,7 +11532,7 @@
       <c r="K149" s="3"/>
     </row>
     <row r="150" spans="1:11">
-      <c r="A150" s="8"/>
+      <c r="A150" s="22"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3" t="s">
         <v>100</v>
@@ -11514,7 +11558,7 @@
       <c r="K150" s="3"/>
     </row>
     <row r="151" spans="1:11">
-      <c r="A151" s="8"/>
+      <c r="A151" s="22"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3" t="s">
         <v>100</v>
@@ -11540,7 +11584,7 @@
       <c r="K151" s="3"/>
     </row>
     <row r="152" spans="1:11">
-      <c r="A152" s="8"/>
+      <c r="A152" s="22"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3" t="s">
         <v>100</v>
@@ -11566,7 +11610,7 @@
       <c r="K152" s="3"/>
     </row>
     <row r="153" spans="1:11">
-      <c r="A153" s="8"/>
+      <c r="A153" s="22"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3" t="s">
         <v>100</v>
@@ -11592,7 +11636,7 @@
       <c r="K153" s="3"/>
     </row>
     <row r="154" spans="1:11">
-      <c r="A154" s="8"/>
+      <c r="A154" s="22"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3" t="s">
         <v>100</v>
@@ -11618,7 +11662,7 @@
       <c r="K154" s="3"/>
     </row>
     <row r="155" spans="1:11">
-      <c r="A155" s="8"/>
+      <c r="A155" s="22"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3" t="s">
         <v>100</v>
@@ -11644,7 +11688,7 @@
       <c r="K155" s="3"/>
     </row>
     <row r="156" spans="1:11">
-      <c r="A156" s="8"/>
+      <c r="A156" s="22"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3" t="s">
         <v>100</v>
@@ -11670,7 +11714,7 @@
       <c r="K156" s="3"/>
     </row>
     <row r="157" spans="1:11">
-      <c r="A157" s="8"/>
+      <c r="A157" s="22"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3" t="s">
         <v>100</v>
@@ -11696,7 +11740,7 @@
       <c r="K157" s="3"/>
     </row>
     <row r="158" spans="1:11">
-      <c r="A158" s="8"/>
+      <c r="A158" s="22"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3" t="s">
         <v>100</v>
@@ -11722,7 +11766,7 @@
       <c r="K158" s="3"/>
     </row>
     <row r="159" spans="1:11">
-      <c r="A159" s="8"/>
+      <c r="A159" s="22"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3" t="s">
         <v>100</v>
@@ -11748,7 +11792,7 @@
       <c r="K159" s="3"/>
     </row>
     <row r="160" spans="1:11">
-      <c r="A160" s="8"/>
+      <c r="A160" s="22"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3" t="s">
         <v>100</v>
@@ -11774,7 +11818,7 @@
       <c r="K160" s="3"/>
     </row>
     <row r="161" spans="1:11">
-      <c r="A161" s="8"/>
+      <c r="A161" s="22"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3" t="s">
         <v>100</v>
@@ -11800,7 +11844,7 @@
       <c r="K161" s="3"/>
     </row>
     <row r="162" spans="1:11">
-      <c r="A162" s="8"/>
+      <c r="A162" s="22"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3" t="s">
         <v>100</v>
@@ -11826,7 +11870,7 @@
       <c r="K162" s="3"/>
     </row>
     <row r="163" spans="1:11">
-      <c r="A163" s="8"/>
+      <c r="A163" s="22"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3" t="s">
         <v>100</v>
@@ -11852,7 +11896,7 @@
       <c r="K163" s="3"/>
     </row>
     <row r="164" spans="1:11">
-      <c r="A164" s="8"/>
+      <c r="A164" s="22"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3" t="s">
         <v>100</v>
@@ -11878,7 +11922,7 @@
       <c r="K164" s="3"/>
     </row>
     <row r="165" spans="1:11">
-      <c r="A165" s="8"/>
+      <c r="A165" s="22"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3" t="s">
         <v>100</v>
@@ -11904,7 +11948,7 @@
       <c r="K165" s="3"/>
     </row>
     <row r="166" spans="1:11">
-      <c r="A166" s="8"/>
+      <c r="A166" s="22"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3" t="s">
         <v>100</v>
@@ -11930,7 +11974,7 @@
       <c r="K166" s="3"/>
     </row>
     <row r="167" spans="1:11">
-      <c r="A167" s="8"/>
+      <c r="A167" s="22"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3" t="s">
         <v>100</v>
@@ -11956,7 +12000,7 @@
       <c r="K167" s="3"/>
     </row>
     <row r="168" spans="1:11">
-      <c r="A168" s="8"/>
+      <c r="A168" s="22"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3" t="s">
         <v>100</v>
@@ -11982,7 +12026,7 @@
       <c r="K168" s="3"/>
     </row>
     <row r="169" spans="1:11">
-      <c r="A169" s="8"/>
+      <c r="A169" s="22"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3" t="s">
         <v>100</v>
@@ -12008,7 +12052,7 @@
       <c r="K169" s="3"/>
     </row>
     <row r="170" spans="1:11">
-      <c r="A170" s="8"/>
+      <c r="A170" s="22"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3" t="s">
         <v>100</v>
@@ -12034,7 +12078,7 @@
       <c r="K170" s="3"/>
     </row>
     <row r="171" spans="1:11">
-      <c r="A171" s="8"/>
+      <c r="A171" s="22"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3" t="s">
         <v>100</v>
@@ -12060,7 +12104,7 @@
       <c r="K171" s="3"/>
     </row>
     <row r="172" spans="1:11">
-      <c r="A172" s="8"/>
+      <c r="A172" s="22"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3" t="s">
         <v>100</v>
@@ -12086,7 +12130,7 @@
       <c r="K172" s="3"/>
     </row>
     <row r="173" spans="1:11">
-      <c r="A173" s="8"/>
+      <c r="A173" s="22"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3" t="s">
         <v>100</v>
@@ -12112,7 +12156,7 @@
       <c r="K173" s="3"/>
     </row>
     <row r="174" spans="1:11">
-      <c r="A174" s="8"/>
+      <c r="A174" s="22"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3" t="s">
         <v>100</v>
@@ -12138,7 +12182,7 @@
       <c r="K174" s="3"/>
     </row>
     <row r="175" spans="1:11">
-      <c r="A175" s="8"/>
+      <c r="A175" s="22"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3" t="s">
         <v>100</v>
@@ -12164,7 +12208,7 @@
       <c r="K175" s="3"/>
     </row>
     <row r="176" spans="1:11">
-      <c r="A176" s="8"/>
+      <c r="A176" s="22"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3" t="s">
         <v>100</v>
@@ -12190,7 +12234,7 @@
       <c r="K176" s="3"/>
     </row>
     <row r="177" spans="1:11">
-      <c r="A177" s="8"/>
+      <c r="A177" s="22"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3" t="s">
         <v>100</v>
@@ -12216,7 +12260,7 @@
       <c r="K177" s="3"/>
     </row>
     <row r="178" spans="1:11">
-      <c r="A178" s="8"/>
+      <c r="A178" s="22"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3" t="s">
         <v>100</v>
@@ -12242,7 +12286,7 @@
       <c r="K178" s="3"/>
     </row>
     <row r="179" spans="1:11">
-      <c r="A179" s="8"/>
+      <c r="A179" s="22"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3" t="s">
         <v>100</v>
@@ -12268,7 +12312,7 @@
       <c r="K179" s="3"/>
     </row>
     <row r="180" spans="1:11">
-      <c r="A180" s="8"/>
+      <c r="A180" s="22"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3" t="s">
         <v>100</v>
@@ -12294,7 +12338,7 @@
       <c r="K180" s="3"/>
     </row>
     <row r="181" spans="1:11">
-      <c r="A181" s="8"/>
+      <c r="A181" s="22"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3" t="s">
         <v>100</v>
@@ -12320,7 +12364,7 @@
       <c r="K181" s="3"/>
     </row>
     <row r="182" spans="1:11">
-      <c r="A182" s="8"/>
+      <c r="A182" s="22"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3" t="s">
         <v>100</v>
@@ -12346,7 +12390,7 @@
       <c r="K182" s="3"/>
     </row>
     <row r="183" spans="1:11">
-      <c r="A183" s="8"/>
+      <c r="A183" s="22"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3" t="s">
         <v>100</v>
@@ -12372,7 +12416,7 @@
       <c r="K183" s="3"/>
     </row>
     <row r="184" spans="1:11">
-      <c r="A184" s="8"/>
+      <c r="A184" s="22"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3" t="s">
         <v>100</v>
@@ -12398,7 +12442,7 @@
       <c r="K184" s="3"/>
     </row>
     <row r="185" spans="1:11">
-      <c r="A185" s="8"/>
+      <c r="A185" s="22"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3" t="s">
         <v>100</v>
@@ -12424,7 +12468,7 @@
       <c r="K185" s="3"/>
     </row>
     <row r="186" spans="1:11">
-      <c r="A186" s="8"/>
+      <c r="A186" s="22"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3" t="s">
         <v>100</v>
@@ -12450,7 +12494,7 @@
       <c r="K186" s="3"/>
     </row>
     <row r="187" spans="1:11">
-      <c r="A187" s="8"/>
+      <c r="A187" s="22"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3" t="s">
         <v>100</v>
@@ -12476,7 +12520,7 @@
       <c r="K187" s="3"/>
     </row>
     <row r="188" spans="1:11">
-      <c r="A188" s="8"/>
+      <c r="A188" s="22"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3" t="s">
         <v>100</v>
@@ -12502,7 +12546,7 @@
       <c r="K188" s="3"/>
     </row>
     <row r="189" spans="1:11">
-      <c r="A189" s="8"/>
+      <c r="A189" s="22"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3" t="s">
         <v>100</v>
@@ -12528,7 +12572,7 @@
       <c r="K189" s="3"/>
     </row>
     <row r="190" spans="1:11">
-      <c r="A190" s="8"/>
+      <c r="A190" s="22"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3" t="s">
         <v>100</v>
@@ -12554,7 +12598,7 @@
       <c r="K190" s="3"/>
     </row>
     <row r="191" spans="1:11">
-      <c r="A191" s="8"/>
+      <c r="A191" s="22"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3" t="s">
         <v>100</v>
@@ -12580,7 +12624,7 @@
       <c r="K191" s="3"/>
     </row>
     <row r="192" spans="1:11">
-      <c r="A192" s="8"/>
+      <c r="A192" s="22"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3" t="s">
         <v>100</v>
@@ -12606,7 +12650,7 @@
       <c r="K192" s="3"/>
     </row>
     <row r="193" spans="1:11">
-      <c r="A193" s="8"/>
+      <c r="A193" s="22"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3" t="s">
         <v>100</v>
@@ -12632,7 +12676,7 @@
       <c r="K193" s="3"/>
     </row>
     <row r="194" spans="1:11">
-      <c r="A194" s="8"/>
+      <c r="A194" s="22"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3" t="s">
         <v>100</v>
@@ -12658,7 +12702,7 @@
       <c r="K194" s="3"/>
     </row>
     <row r="195" spans="1:11">
-      <c r="A195" s="8"/>
+      <c r="A195" s="22"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3" t="s">
         <v>100</v>
@@ -12684,7 +12728,7 @@
       <c r="K195" s="3"/>
     </row>
     <row r="196" spans="1:11">
-      <c r="A196" s="8"/>
+      <c r="A196" s="22"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3" t="s">
         <v>100</v>
@@ -12710,7 +12754,7 @@
       <c r="K196" s="3"/>
     </row>
     <row r="197" spans="1:11">
-      <c r="A197" s="8"/>
+      <c r="A197" s="22"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3" t="s">
         <v>100</v>
@@ -12736,7 +12780,7 @@
       <c r="K197" s="3"/>
     </row>
     <row r="198" spans="1:11">
-      <c r="A198" s="8"/>
+      <c r="A198" s="22"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3" t="s">
         <v>100</v>
@@ -15552,7 +15596,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>102</v>
       </c>
       <c r="B1" s="15"/>
@@ -18061,7 +18105,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>105</v>
       </c>
       <c r="B1" s="15"/>
@@ -18071,7 +18115,7 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="32" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="20" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="15"/>
@@ -18079,7 +18123,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="20" t="s">
         <v>107</v>
       </c>
       <c r="I3" s="15"/>
@@ -18281,7 +18325,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
@@ -18305,7 +18349,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>31</v>
@@ -18320,7 +18364,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>132.90000000000003</v>
+        <v>224.00000000000006</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>31</v>
@@ -18335,7 +18379,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -18365,7 +18409,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>31</v>
@@ -18380,7 +18424,7 @@
       </c>
       <c r="B17" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$7)</f>
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>31</v>
@@ -18399,7 +18443,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="20" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="15"/>
@@ -18543,7 +18587,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="15"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0d6326f5f2c34ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="2" r:id="R4530ee0cbbf24d38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametri" sheetId="3" r:id="R3b945633529a4b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persone_Quote" sheetId="4" r:id="R125d03550e6d4ccc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisti_Patch" sheetId="5" r:id="R4550e452985c4ae8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendite_Patch" sheetId="6" r:id="R534ab63ffae54b76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spese_Categoria" sheetId="7" r:id="Rbae4cfaf1ffc4b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magazzino_Cassa" sheetId="8" r:id="Ra7d8da550e41432c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liste" sheetId="9" r:id="R920da7b190a4415a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Affidamenti_Patch" sheetId="10" r:id="R862f6891bd0b4e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ra25f54df89444676"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="2" r:id="Rc24f2c3c8ebd4ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametri" sheetId="3" r:id="R10128236b66f45b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persone_Quote" sheetId="4" r:id="R89538b0c07a943e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisti_Patch" sheetId="5" r:id="Ra63aa00fcbe04517"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendite_Patch" sheetId="6" r:id="Rdc8652a562ad482c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spese_Categoria" sheetId="7" r:id="R81d3810f50a14c3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magazzino_Cassa" sheetId="8" r:id="R75a21954f5cb4865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liste" sheetId="9" r:id="Rba124f79ade74446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Affidamenti_Patch" sheetId="10" r:id="Rba0df0b5f7774190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venditori_Affidatari" sheetId="11" r:id="Rf85801af9e494c09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -633,7 +634,7 @@
     <x:numFmt numFmtId="167" formatCode="0.0%"/>
     <x:numFmt numFmtId="200" formatCode="#,##0"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -716,8 +717,14 @@
       <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -762,6 +769,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7ED"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -861,7 +888,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="76">
+  <x:cellXfs count="94">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1047,6 +1074,48 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1873,7 +1942,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8ed3830dcf534dbf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reeb5144390e04c66"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1908,7 +1977,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R76b70b901cb449ef"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf3df260e30a14f94"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2009,6 +2078,17 @@
     <x:tableColumn id="8" name="Versato in cassa"/>
     <x:tableColumn id="9" name="Denaro da versare"/>
     <x:tableColumn id="10" name="Stato / Note"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TabellaVenditoriAffidatari" displayName="TabellaVenditoriAffidatari" ref="A3:C103" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="3">
+    <x:tableColumn id="1" name="Tipo"/>
+    <x:tableColumn id="2" name="Nome / Cognome"/>
+    <x:tableColumn id="3" name="Note"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -2638,7 +2718,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R155fbdaf98ff40d7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5c1f14340e14e9c"/>
 </x:worksheet>
 </file>
 
@@ -6729,7 +6809,7 @@
       <x:formula2>2100-12-31</x:formula2>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="B4:B203">
-      <x:formula1>'Persone_Quote'!$B$4:$B$18</x:formula1>
+      <x:formula1>'Venditori_Affidatari'!$B$4:$B$103</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C4:C203">
       <x:formula1>0</x:formula1>
@@ -6743,7 +6823,828 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50a70dec9ab64fe8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c1dcd57791c4a2f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="78" t="str">
+        <x:v>Elenco venditori affidatari</x:v>
+      </x:c>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="82" t="str">
+        <x:v>I componenti sono riportati automaticamente. Per aggiungere colleghi o amici, scrivi il loro nome nelle righe della sezione Esterni.</x:v>
+      </x:c>
+      <x:c r="B2" s="82"/>
+      <x:c r="C2" s="82"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="87" t="str">
+        <x:v>Tipo</x:v>
+      </x:c>
+      <x:c r="B3" s="87" t="str">
+        <x:v>Nome / Cognome</x:v>
+      </x:c>
+      <x:c r="C3" s="87" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="55" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:f>'Persone_Quote'!B4</x:f>
+        <x:v>Capodanno</x:v>
+      </x:c>
+      <x:c r="C4" s="57" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B5" s="59" t="str">
+        <x:f>'Persone_Quote'!B5</x:f>
+        <x:v>Caggia</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B6" s="59" t="str">
+        <x:f>'Persone_Quote'!B6</x:f>
+        <x:v>Marchesani</x:v>
+      </x:c>
+      <x:c r="C6" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="22" customHeight="1">
+      <x:c r="A7" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B7" s="59" t="str">
+        <x:f>'Persone_Quote'!B7</x:f>
+        <x:v>Zubenko</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
+      <x:c r="A8" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B8" s="59" t="str">
+        <x:f>'Persone_Quote'!B8</x:f>
+        <x:v>Losito</x:v>
+      </x:c>
+      <x:c r="C8" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B9" s="59" t="str">
+        <x:f>'Persone_Quote'!B9</x:f>
+        <x:v>Di Stefano</x:v>
+      </x:c>
+      <x:c r="C9" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B10" s="59" t="str">
+        <x:f>'Persone_Quote'!B10</x:f>
+        <x:v>Palladino</x:v>
+      </x:c>
+      <x:c r="C10" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B11" s="59" t="str">
+        <x:f>'Persone_Quote'!B11</x:f>
+        <x:v>Locorotondo</x:v>
+      </x:c>
+      <x:c r="C11" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B12" s="59" t="str">
+        <x:f>'Persone_Quote'!B12</x:f>
+        <x:v>Pertosa</x:v>
+      </x:c>
+      <x:c r="C12" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B13" s="59" t="str">
+        <x:f>'Persone_Quote'!B13</x:f>
+        <x:v>Ottaiano</x:v>
+      </x:c>
+      <x:c r="C13" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B14" s="59" t="str">
+        <x:f>'Persone_Quote'!B14</x:f>
+        <x:v>Fragnito</x:v>
+      </x:c>
+      <x:c r="C14" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B15" s="59" t="str">
+        <x:f>'Persone_Quote'!B15</x:f>
+        <x:v>Murolo</x:v>
+      </x:c>
+      <x:c r="C15" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B16" s="59" t="str">
+        <x:f>'Persone_Quote'!B16</x:f>
+        <x:v>Palma</x:v>
+      </x:c>
+      <x:c r="C16" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B17" s="59" t="str">
+        <x:f>'Persone_Quote'!B17</x:f>
+        <x:v>Babele</x:v>
+      </x:c>
+      <x:c r="C17" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="58" t="str">
+        <x:v>Componente</x:v>
+      </x:c>
+      <x:c r="B18" s="59" t="str">
+        <x:f>'Persone_Quote'!B18</x:f>
+        <x:v>Torrente</x:v>
+      </x:c>
+      <x:c r="C18" s="60" t="str">
+        <x:v>Elenco automatico dei componenti</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B19" s="89"/>
+      <x:c r="C19" s="90"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B20" s="89"/>
+      <x:c r="C20" s="90"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B21" s="89"/>
+      <x:c r="C21" s="90"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B22" s="89"/>
+      <x:c r="C22" s="90"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B23" s="89"/>
+      <x:c r="C23" s="90"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B24" s="89"/>
+      <x:c r="C24" s="90"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B25" s="89"/>
+      <x:c r="C25" s="90"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B26" s="89"/>
+      <x:c r="C26" s="90"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B27" s="89"/>
+      <x:c r="C27" s="90"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B28" s="89"/>
+      <x:c r="C28" s="90"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B29" s="89"/>
+      <x:c r="C29" s="90"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B30" s="89"/>
+      <x:c r="C30" s="90"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B31" s="89"/>
+      <x:c r="C31" s="90"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B32" s="89"/>
+      <x:c r="C32" s="90"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B33" s="89"/>
+      <x:c r="C33" s="90"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B34" s="89"/>
+      <x:c r="C34" s="90"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B35" s="89"/>
+      <x:c r="C35" s="90"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B36" s="89"/>
+      <x:c r="C36" s="90"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B37" s="89"/>
+      <x:c r="C37" s="90"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B38" s="89"/>
+      <x:c r="C38" s="90"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B39" s="89"/>
+      <x:c r="C39" s="90"/>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B40" s="89"/>
+      <x:c r="C40" s="90"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B41" s="89"/>
+      <x:c r="C41" s="90"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B42" s="89"/>
+      <x:c r="C42" s="90"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B43" s="89"/>
+      <x:c r="C43" s="90"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B44" s="89"/>
+      <x:c r="C44" s="90"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B45" s="89"/>
+      <x:c r="C45" s="90"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B46" s="89"/>
+      <x:c r="C46" s="90"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B47" s="89"/>
+      <x:c r="C47" s="90"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B48" s="89"/>
+      <x:c r="C48" s="90"/>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B49" s="89"/>
+      <x:c r="C49" s="90"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B50" s="89"/>
+      <x:c r="C50" s="90"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B51" s="89"/>
+      <x:c r="C51" s="90"/>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B52" s="89"/>
+      <x:c r="C52" s="90"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B53" s="89"/>
+      <x:c r="C53" s="90"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B54" s="89"/>
+      <x:c r="C54" s="90"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B55" s="89"/>
+      <x:c r="C55" s="90"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B56" s="89"/>
+      <x:c r="C56" s="90"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B57" s="89"/>
+      <x:c r="C57" s="90"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B58" s="89"/>
+      <x:c r="C58" s="90"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B59" s="89"/>
+      <x:c r="C59" s="90"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B60" s="89"/>
+      <x:c r="C60" s="90"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B61" s="89"/>
+      <x:c r="C61" s="90"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B62" s="89"/>
+      <x:c r="C62" s="90"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B63" s="89"/>
+      <x:c r="C63" s="90"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B64" s="89"/>
+      <x:c r="C64" s="90"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B65" s="89"/>
+      <x:c r="C65" s="90"/>
+    </x:row>
+    <x:row r="66" ht="22" customHeight="1">
+      <x:c r="A66" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B66" s="89"/>
+      <x:c r="C66" s="90"/>
+    </x:row>
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B67" s="89"/>
+      <x:c r="C67" s="90"/>
+    </x:row>
+    <x:row r="68" ht="22" customHeight="1">
+      <x:c r="A68" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B68" s="89"/>
+      <x:c r="C68" s="90"/>
+    </x:row>
+    <x:row r="69" ht="22" customHeight="1">
+      <x:c r="A69" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B69" s="89"/>
+      <x:c r="C69" s="90"/>
+    </x:row>
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B70" s="89"/>
+      <x:c r="C70" s="90"/>
+    </x:row>
+    <x:row r="71" ht="22" customHeight="1">
+      <x:c r="A71" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B71" s="89"/>
+      <x:c r="C71" s="90"/>
+    </x:row>
+    <x:row r="72" ht="22" customHeight="1">
+      <x:c r="A72" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B72" s="89"/>
+      <x:c r="C72" s="90"/>
+    </x:row>
+    <x:row r="73" ht="22" customHeight="1">
+      <x:c r="A73" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B73" s="89"/>
+      <x:c r="C73" s="90"/>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B74" s="89"/>
+      <x:c r="C74" s="90"/>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B75" s="89"/>
+      <x:c r="C75" s="90"/>
+    </x:row>
+    <x:row r="76" ht="22" customHeight="1">
+      <x:c r="A76" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B76" s="89"/>
+      <x:c r="C76" s="90"/>
+    </x:row>
+    <x:row r="77" ht="22" customHeight="1">
+      <x:c r="A77" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B77" s="89"/>
+      <x:c r="C77" s="90"/>
+    </x:row>
+    <x:row r="78" ht="22" customHeight="1">
+      <x:c r="A78" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B78" s="89"/>
+      <x:c r="C78" s="90"/>
+    </x:row>
+    <x:row r="79" ht="22" customHeight="1">
+      <x:c r="A79" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B79" s="89"/>
+      <x:c r="C79" s="90"/>
+    </x:row>
+    <x:row r="80" ht="22" customHeight="1">
+      <x:c r="A80" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B80" s="89"/>
+      <x:c r="C80" s="90"/>
+    </x:row>
+    <x:row r="81" ht="22" customHeight="1">
+      <x:c r="A81" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B81" s="89"/>
+      <x:c r="C81" s="90"/>
+    </x:row>
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B82" s="89"/>
+      <x:c r="C82" s="90"/>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B83" s="89"/>
+      <x:c r="C83" s="90"/>
+    </x:row>
+    <x:row r="84" ht="22" customHeight="1">
+      <x:c r="A84" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B84" s="89"/>
+      <x:c r="C84" s="90"/>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B85" s="89"/>
+      <x:c r="C85" s="90"/>
+    </x:row>
+    <x:row r="86" ht="22" customHeight="1">
+      <x:c r="A86" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B86" s="89"/>
+      <x:c r="C86" s="90"/>
+    </x:row>
+    <x:row r="87" ht="22" customHeight="1">
+      <x:c r="A87" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B87" s="89"/>
+      <x:c r="C87" s="90"/>
+    </x:row>
+    <x:row r="88" ht="22" customHeight="1">
+      <x:c r="A88" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B88" s="89"/>
+      <x:c r="C88" s="90"/>
+    </x:row>
+    <x:row r="89" ht="22" customHeight="1">
+      <x:c r="A89" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B89" s="89"/>
+      <x:c r="C89" s="90"/>
+    </x:row>
+    <x:row r="90" ht="22" customHeight="1">
+      <x:c r="A90" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B90" s="89"/>
+      <x:c r="C90" s="90"/>
+    </x:row>
+    <x:row r="91" ht="22" customHeight="1">
+      <x:c r="A91" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B91" s="89"/>
+      <x:c r="C91" s="90"/>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B92" s="89"/>
+      <x:c r="C92" s="90"/>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B93" s="89"/>
+      <x:c r="C93" s="90"/>
+    </x:row>
+    <x:row r="94" ht="22" customHeight="1">
+      <x:c r="A94" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B94" s="89"/>
+      <x:c r="C94" s="90"/>
+    </x:row>
+    <x:row r="95" ht="22" customHeight="1">
+      <x:c r="A95" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B95" s="89"/>
+      <x:c r="C95" s="90"/>
+    </x:row>
+    <x:row r="96" ht="22" customHeight="1">
+      <x:c r="A96" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B96" s="89"/>
+      <x:c r="C96" s="90"/>
+    </x:row>
+    <x:row r="97" ht="22" customHeight="1">
+      <x:c r="A97" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B97" s="89"/>
+      <x:c r="C97" s="90"/>
+    </x:row>
+    <x:row r="98" ht="22" customHeight="1">
+      <x:c r="A98" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B98" s="89"/>
+      <x:c r="C98" s="90"/>
+    </x:row>
+    <x:row r="99" ht="22" customHeight="1">
+      <x:c r="A99" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B99" s="89"/>
+      <x:c r="C99" s="90"/>
+    </x:row>
+    <x:row r="100" ht="22" customHeight="1">
+      <x:c r="A100" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B100" s="89"/>
+      <x:c r="C100" s="90"/>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B101" s="89"/>
+      <x:c r="C101" s="90"/>
+    </x:row>
+    <x:row r="102" ht="22" customHeight="1">
+      <x:c r="A102" s="88" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B102" s="89"/>
+      <x:c r="C102" s="90"/>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" s="91" t="str">
+        <x:v>Esterno</x:v>
+      </x:c>
+      <x:c r="B103" s="92"/>
+      <x:c r="C103" s="93"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A2:C2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49d14cd067fb4f9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6830,8 +7731,8 @@
       <x:c r="B8" s="74" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C8" s="74" t="s">
-        <x:v>68</x:v>
+      <x:c r="C8" s="74" t="str">
+        <x:v>Registra ogni affidatario in Affidamenti_Patch. Per colleghi o amici, aggiungi prima il nome in Venditori_Affidatari; poi selezionalo nei menu di affidamenti e vendite.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
@@ -7575,7 +8476,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07922a4f70bf4b27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7562d3e5bc974a38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11067,7 +11968,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45ad750f3dfb4a8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R509b329d3f0f47b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18655,12 +19556,12 @@
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="L4:L303">
-      <x:formula1>'Persone_Quote'!$B$4:$B$18</x:formula1>
+      <x:formula1>'Venditori_Affidatari'!$B$4:$B$103</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8e61bf009e94c5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddf3658dfe98453a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21144,7 +22045,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b002e42db17492a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6137faf510e4799"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21629,7 +22530,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3b429e6e9b24d13"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R762d04446f30420e"/>
 </x:worksheet>
 </file>
 

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80E10AD-95CA-4E4F-8E69-E34043508D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1782389B-8D95-F448-9562-CB91EA444644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="226">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -1131,26 +1131,26 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1741,7 +1741,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>278</c:v>
+                  <c:v>203</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2336,7 +2336,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -2352,7 +2352,7 @@
       <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -2369,49 +2369,49 @@
     </row>
     <row r="3" spans="1:12" ht="42.75" customHeight="1"/>
     <row r="4" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="41" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="39"/>
       <c r="I4" s="39"/>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="41" t="s">
         <v>5</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="39"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1">
-      <c r="A5" s="41">
+      <c r="A5" s="42">
         <f>Magazzino_Cassa!B16</f>
-        <v>33</v>
+        <v>-42</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
-      <c r="D5" s="41">
+      <c r="D5" s="42">
         <f>Magazzino_Cassa!B6</f>
         <v>375</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
-      <c r="G5" s="45">
+      <c r="G5" s="43">
         <f>Magazzino_Cassa!B14</f>
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H5" s="39"/>
       <c r="I5" s="39"/>
-      <c r="J5" s="41">
+      <c r="J5" s="42">
         <f>Magazzino_Cassa!B12</f>
-        <v>278</v>
+        <v>203</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="39"/>
@@ -2431,47 +2431,47 @@
       <c r="L6" s="39"/>
     </row>
     <row r="8" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="41" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="41" t="s">
         <v>8</v>
       </c>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="40" t="s">
+      <c r="J8" s="41" t="s">
         <v>9</v>
       </c>
       <c r="K8" s="39"/>
       <c r="L8" s="39"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1">
-      <c r="A9" s="41">
+      <c r="A9" s="42">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
-      <c r="D9" s="41">
+      <c r="D9" s="42">
         <f>Magazzino_Cassa!B13</f>
-        <v>224.00000000000006</v>
+        <v>162.50000000000006</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
-      <c r="G9" s="42" t="str">
+      <c r="G9" s="45" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="41">
+      <c r="J9" s="42">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="L10" s="39"/>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="39"/>
@@ -2501,7 +2501,7 @@
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="44" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="39"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>278</v>
+        <v>203</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>33</v>
+        <v>-42</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>34</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B20" s="4">
         <f>Magazzino_Cassa!B17</f>
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>18</v>
@@ -2733,7 +2733,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="44" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="39"/>
@@ -2774,12 +2774,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2787,6 +2781,12 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2804,7 +2804,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="E196" s="25"/>
       <c r="F196" s="25" t="str">
-        <f t="shared" ref="F196:F227" si="12">IF(B196="","",MAX(C196-D196-E196,0))</f>
+        <f t="shared" ref="F196:F203" si="12">IF(B196="","",MAX(C196-D196-E196,0))</f>
         <v/>
       </c>
       <c r="G196" s="28" t="str">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="H196" s="28"/>
       <c r="I196" s="28" t="str">
-        <f t="shared" ref="I196:I227" si="13">IF(B196="","",MAX(G196-H196,0))</f>
+        <f t="shared" ref="I196:I203" si="13">IF(B196="","",MAX(G196-H196,0))</f>
         <v/>
       </c>
       <c r="J196" s="21"/>
@@ -7728,7 +7728,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -8563,7 +8563,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="39"/>
@@ -8692,7 +8692,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="39"/>
@@ -8865,7 +8865,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="39"/>
@@ -9402,7 +9402,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="39"/>
@@ -13298,7 +13298,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>138</v>
       </c>
       <c r="B1" s="39"/>
@@ -14206,42 +14206,30 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="A29" s="14"/>
+      <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="5">
-        <v>5</v>
-      </c>
-      <c r="E29" s="13">
-        <v>15</v>
-      </c>
-      <c r="F29" s="4">
+      <c r="D29" s="5"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="G29" s="4">
+        <v/>
+      </c>
+      <c r="G29" s="4" t="str">
         <f>IF(D29="","",D29*Parametri!$B$6)</f>
-        <v>13.5</v>
-      </c>
-      <c r="H29" s="4">
+        <v/>
+      </c>
+      <c r="H29" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>61.5</v>
+        <v/>
       </c>
       <c r="I29" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>151</v>
-      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="14"/>
@@ -21416,7 +21404,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>164</v>
       </c>
       <c r="B1" s="39"/>
@@ -23901,7 +23889,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>170</v>
       </c>
       <c r="B1" s="39"/>
@@ -23911,7 +23899,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="44" t="s">
         <v>171</v>
       </c>
       <c r="B3" s="39"/>
@@ -23919,7 +23907,7 @@
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="44" t="s">
         <v>172</v>
       </c>
       <c r="I3" s="39"/>
@@ -24121,7 +24109,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -24145,7 +24133,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>278</v>
+        <v>203</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -24160,7 +24148,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>224.00000000000006</v>
+        <v>162.50000000000006</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -24175,7 +24163,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -24205,7 +24193,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>33</v>
+        <v>-42</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
@@ -24220,7 +24208,7 @@
       </c>
       <c r="B17" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$7)</f>
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>36</v>
@@ -24239,7 +24227,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="44" t="s">
         <v>186</v>
       </c>
       <c r="B19" s="39"/>
@@ -24383,7 +24371,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>193</v>
       </c>
       <c r="B1" s="39"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1782389B-8D95-F448-9562-CB91EA444644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169BD435-8290-5942-B861-E73C68216DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="227">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -722,6 +722,9 @@
   <si>
     <t>Per Scuotto</t>
   </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1131,38 +1134,38 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1741,7 +1744,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>203</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2336,179 +2339,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
     </row>
     <row r="2" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
     </row>
     <row r="3" spans="1:12" ht="42.75" customHeight="1"/>
     <row r="4" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="41" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="41" t="s">
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="41" t="s">
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1">
-      <c r="A5" s="42">
+      <c r="A5" s="43">
         <f>Magazzino_Cassa!B16</f>
-        <v>-42</v>
-      </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="42">
+        <v>-30</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="43">
         <f>Magazzino_Cassa!B6</f>
         <v>375</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="43">
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="47">
         <f>Magazzino_Cassa!B14</f>
-        <v>157</v>
-      </c>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="42">
+        <v>156</v>
+      </c>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="43">
         <f>Magazzino_Cassa!B12</f>
-        <v>203</v>
-      </c>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
+        <v>215</v>
+      </c>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
     </row>
     <row r="8" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="41" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="41" t="s">
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="41" t="s">
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1">
-      <c r="A9" s="42">
+      <c r="A9" s="43">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="42">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="43">
         <f>Magazzino_Cassa!B13</f>
-        <v>162.50000000000006</v>
-      </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="45" t="str">
+        <v>171.80000000000007</v>
+      </c>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="44" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="42">
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="43">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="44" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
     </row>
     <row r="14" spans="1:12" ht="26.75" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -2570,7 +2573,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
@@ -2583,7 +2586,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -2611,7 +2614,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -2654,7 +2657,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>-42</v>
+        <v>-30</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>34</v>
@@ -2710,7 +2713,7 @@
       </c>
       <c r="B21" s="4">
         <f>Magazzino_Cassa!B18</f>
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
@@ -2733,20 +2736,20 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
     </row>
     <row r="24" spans="1:12" ht="85.25" customHeight="1">
       <c r="A24" s="6" t="s">
@@ -2774,6 +2777,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2781,12 +2790,6 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2816,32 +2819,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:10" ht="34" customHeight="1">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
     </row>
     <row r="3" spans="1:10" ht="38" customHeight="1">
       <c r="A3" s="15" t="s">
@@ -7736,18 +7739,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
     </row>
     <row r="2" spans="1:3" ht="38" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
     </row>
     <row r="3" spans="1:3" ht="28" customHeight="1">
       <c r="A3" s="31" t="s">
@@ -8563,14 +8566,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
     </row>
     <row r="3" spans="1:6" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -8692,12 +8695,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -8865,17 +8868,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -9402,17 +9405,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="3" spans="1:9" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -13298,19 +13301,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
       <c r="L1" t="s">
         <v>205</v>
       </c>
@@ -14206,29 +14209,39 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="14"/>
-      <c r="B29" s="3"/>
+      <c r="A29" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="C29" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="4" t="str">
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13">
+        <v>12</v>
+      </c>
+      <c r="F29" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G29" s="4" t="str">
+        <v>12</v>
+      </c>
+      <c r="G29" s="4">
         <f>IF(D29="","",D29*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H29" s="4" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="H29" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11">
@@ -21404,16 +21417,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -23889,30 +23902,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="H3" s="44" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="H3" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="16">
       <c r="A4" s="6" t="s">
@@ -24109,7 +24122,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -24133,7 +24146,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -24148,7 +24161,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>162.50000000000006</v>
+        <v>171.80000000000007</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -24163,7 +24176,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -24193,7 +24206,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>-42</v>
+        <v>-30</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
@@ -24220,21 +24233,21 @@
       </c>
       <c r="B18" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$8)</f>
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
@@ -24371,12 +24384,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169BD435-8290-5942-B861-E73C68216DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185FC19D-A221-CA4B-A46F-2E2B146718F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="229">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -725,6 +725,12 @@
   <si>
     <t>15/07/2026</t>
   </si>
+  <si>
+    <t>19/07/2026</t>
+  </si>
+  <si>
+    <t>Scuotto</t>
+  </si>
 </sst>
 </file>
 
@@ -1134,38 +1140,38 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1429,35 +1435,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1618,6 +1595,35 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1744,7 +1750,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>215</c:v>
+                  <c:v>365</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2066,63 +2072,63 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="47">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="54">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="42">
       <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="53">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="41">
       <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="37">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="59">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="53">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="32">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="52">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="31">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="51">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2339,179 +2345,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:12" ht="42.75" customHeight="1"/>
     <row r="4" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="42" t="s">
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="42" t="s">
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1">
-      <c r="A5" s="43">
+      <c r="A5" s="42">
         <f>Magazzino_Cassa!B16</f>
-        <v>-30</v>
-      </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="43">
+        <v>120</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="42">
         <f>Magazzino_Cassa!B6</f>
         <v>375</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="47">
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="43">
         <f>Magazzino_Cassa!B14</f>
-        <v>156</v>
-      </c>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="43">
+        <v>146</v>
+      </c>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="42">
         <f>Magazzino_Cassa!B12</f>
-        <v>215</v>
-      </c>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
+        <v>365</v>
+      </c>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
     </row>
     <row r="8" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="42" t="s">
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="42" t="s">
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1">
-      <c r="A9" s="43">
+      <c r="A9" s="42">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="43">
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="42">
         <f>Magazzino_Cassa!B13</f>
-        <v>171.80000000000007</v>
-      </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="44" t="str">
+        <v>294.80000000000007</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="45" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="43">
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="42">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="40" t="s">
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
     </row>
     <row r="14" spans="1:12" ht="26.75" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -2573,7 +2579,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>215</v>
+        <v>365</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
@@ -2586,7 +2592,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -2614,7 +2620,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -2657,7 +2663,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>-30</v>
+        <v>120</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>34</v>
@@ -2685,7 +2691,7 @@
       </c>
       <c r="B20" s="4">
         <f>Magazzino_Cassa!B17</f>
-        <v>95</v>
+        <v>245</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>18</v>
@@ -2736,20 +2742,20 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
     </row>
     <row r="24" spans="1:12" ht="85.25" customHeight="1">
       <c r="A24" s="6" t="s">
@@ -2777,12 +2783,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2790,6 +2790,12 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2807,7 +2813,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2819,32 +2825,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="46" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="34" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="47" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="1:10" ht="38" customHeight="1">
       <c r="A3" s="15" t="s">
@@ -2890,18 +2896,20 @@
       </c>
       <c r="D4" s="24">
         <f>IF(B4="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B4))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="24">
         <f t="shared" ref="F4:F35" si="0">IF(B4="","",MAX(C4-D4-E4,0))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4" s="27">
         <f>IF(B4="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B4,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="27"/>
+        <v>150</v>
+      </c>
+      <c r="H4" s="27">
+        <v>150</v>
+      </c>
       <c r="I4" s="27">
         <f t="shared" ref="I4:I35" si="1">IF(B4="","",MAX(G4-H4,0))</f>
         <v>0</v>
@@ -7731,7 +7739,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -7739,18 +7747,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
     </row>
     <row r="2" spans="1:3" ht="38" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="3" spans="1:3" ht="28" customHeight="1">
       <c r="A3" s="31" t="s">
@@ -8566,14 +8574,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -8695,12 +8703,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="3" spans="1:4" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -8868,17 +8876,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -9405,17 +9413,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -13301,19 +13309,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
       <c r="L1" t="s">
         <v>205</v>
       </c>
@@ -13801,7 +13809,7 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:12">
       <c r="A17" s="8" t="s">
         <v>155</v>
       </c>
@@ -13832,7 +13840,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:12">
       <c r="A18" s="8" t="s">
         <v>155</v>
       </c>
@@ -13863,7 +13871,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:12">
       <c r="A19" s="8" t="s">
         <v>155</v>
       </c>
@@ -13894,7 +13902,7 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:12">
       <c r="A20" s="8" t="s">
         <v>155</v>
       </c>
@@ -13925,7 +13933,7 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:12">
       <c r="A21" s="8" t="s">
         <v>155</v>
       </c>
@@ -13956,7 +13964,7 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:12">
       <c r="A22" s="8" t="s">
         <v>155</v>
       </c>
@@ -13987,7 +13995,7 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:12">
       <c r="A23" s="8" t="s">
         <v>111</v>
       </c>
@@ -14025,7 +14033,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:12">
       <c r="A24" s="8" t="s">
         <v>111</v>
       </c>
@@ -14063,7 +14071,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:12">
       <c r="A25" s="8" t="s">
         <v>111</v>
       </c>
@@ -14101,7 +14109,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:12">
       <c r="A26" s="8" t="s">
         <v>111</v>
       </c>
@@ -14133,7 +14141,7 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:12">
       <c r="A27" s="14" t="s">
         <v>161</v>
       </c>
@@ -14171,7 +14179,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:12">
       <c r="A28" s="14" t="s">
         <v>163</v>
       </c>
@@ -14208,7 +14216,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:12">
       <c r="A29" s="14" t="s">
         <v>226</v>
       </c>
@@ -14244,33 +14252,46 @@
       </c>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="14"/>
-      <c r="B30" s="3"/>
+    <row r="30" spans="1:12">
+      <c r="A30" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="C30" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="4" t="str">
+      <c r="D30" s="5">
+        <v>10</v>
+      </c>
+      <c r="E30" s="13">
+        <v>15</v>
+      </c>
+      <c r="F30" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="G30" s="4">
         <f>IF(D30="","",D30*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
+        <v>27</v>
+      </c>
+      <c r="H30" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>123</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J30" s="3"/>
+      <c r="J30" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="14"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
@@ -14296,7 +14317,7 @@
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:12">
       <c r="A32" s="14"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
@@ -21417,16 +21438,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -23902,30 +23923,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="H3" s="40" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="H3" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" ht="16">
       <c r="A4" s="6" t="s">
@@ -24122,7 +24143,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -24146,7 +24167,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>215</v>
+        <v>365</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -24161,7 +24182,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>171.80000000000007</v>
+        <v>294.80000000000007</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -24176,7 +24197,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -24206,7 +24227,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>-30</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
@@ -24221,7 +24242,7 @@
       </c>
       <c r="B17" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$7)</f>
-        <v>95</v>
+        <v>245</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>36</v>
@@ -24240,14 +24261,14 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
@@ -24384,12 +24405,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="49.75" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
